--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB60299-3FBD-4FB5-B9D7-71814D86E22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415AF05E-8993-4B2B-AD7C-A910D8800FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blank Issue Tracking'!$B$7:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Example Issue Tracking'!$B$2:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Example Issue Tracking'!$C$2:$H$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Blank Issue Tracking'!$B$2:$L$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Example Issue Tracking'!$B$1:$G$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Example Issue Tracking'!$C$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="34">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>must match</t>
+  </si>
+  <si>
+    <t>Issue No</t>
+  </si>
+  <si>
+    <t>iss01</t>
   </si>
 </sst>
 </file>
@@ -497,12 +503,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -561,6 +561,12 @@
     <xf numFmtId="7" fontId="18" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1151,4817 +1157,5271 @@
     <tabColor theme="3" tint="0.89999084444715716"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N710"/>
+  <dimension ref="A1:O710"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="34" customWidth="1"/>
-    <col min="2" max="2" width="15" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="45" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="37" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="45" customWidth="1"/>
-    <col min="6" max="6" width="61.25" style="37" customWidth="1"/>
-    <col min="7" max="7" width="41.125" style="37" customWidth="1"/>
-    <col min="8" max="8" width="3.625" style="34" customWidth="1"/>
-    <col min="9" max="14" width="11" style="34"/>
-    <col min="15" max="16384" width="11" style="37"/>
+    <col min="1" max="1" width="3.625" style="32" customWidth="1"/>
+    <col min="2" max="3" width="15" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
+    <col min="7" max="7" width="61.25" style="35" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="35" customWidth="1"/>
+    <col min="9" max="9" width="3.625" style="32" customWidth="1"/>
+    <col min="10" max="15" width="11" style="32"/>
+    <col min="16" max="16384" width="11" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-    </row>
-    <row r="2" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38"/>
-      <c r="B2" s="47" t="s">
+    <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+    </row>
+    <row r="2" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36"/>
+      <c r="B2" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="E2" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="F2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="G2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="49" t="s">
+      <c r="H2" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-    </row>
-    <row r="3" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38"/>
-      <c r="B3" s="42" t="s">
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+    </row>
+    <row r="3" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="36"/>
+      <c r="B3" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="E3" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="G3" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="H3" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-    </row>
-    <row r="4" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="50" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+    </row>
+    <row r="4" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="50" t="s">
+      <c r="E4" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="F4" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="41"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-    </row>
-    <row r="5" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="50" t="s">
+      <c r="G4" s="39"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+    </row>
+    <row r="5" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="E5" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="F5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-    </row>
-    <row r="6" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="50" t="s">
+      <c r="G5" s="39"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+    </row>
+    <row r="6" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="E6" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="F6" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-    </row>
-    <row r="7" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="50" t="s">
+      <c r="G6" s="39"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+    </row>
+    <row r="7" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="E7" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="F7" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-    </row>
-    <row r="8" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="50" t="s">
+      <c r="G7" s="39"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+    </row>
+    <row r="8" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="36"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="E8" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="F8" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-    </row>
-    <row r="9" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="50" t="s">
+      <c r="G8" s="39"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+    </row>
+    <row r="9" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="E9" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="F9" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="41"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-    </row>
-    <row r="10" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="50" t="s">
+      <c r="G9" s="39"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+    </row>
+    <row r="10" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="E10" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="F10" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-    </row>
-    <row r="11" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="50" t="s">
+      <c r="G10" s="39"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+    </row>
+    <row r="11" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="36"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="E11" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="F11" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-    </row>
-    <row r="12" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="50" t="s">
+      <c r="G11" s="39"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+    </row>
+    <row r="12" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="36"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="E12" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="F12" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-    </row>
-    <row r="13" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="50" t="s">
+      <c r="G12" s="39"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+    </row>
+    <row r="13" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="36"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="E13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="F13" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-    </row>
-    <row r="14" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="50" t="s">
+      <c r="G13" s="39"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+    </row>
+    <row r="14" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="36"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="E14" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="F14" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-    </row>
-    <row r="15" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="50" t="s">
+      <c r="G14" s="39"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+    </row>
+    <row r="15" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="E15" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="F15" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-    </row>
-    <row r="16" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="50" t="s">
+      <c r="G15" s="39"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+    </row>
+    <row r="16" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="E16" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="F16" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-    </row>
-    <row r="17" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="50" t="s">
+      <c r="G16" s="39"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+    </row>
+    <row r="17" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="E17" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="F17" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="41"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-    </row>
-    <row r="18" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="50" t="s">
+      <c r="G17" s="39"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+    </row>
+    <row r="18" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="E18" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="F18" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-    </row>
-    <row r="19" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="50" t="s">
+      <c r="G18" s="39"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+    </row>
+    <row r="19" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="E19" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="F19" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-    </row>
-    <row r="20" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="50" t="s">
+      <c r="G19" s="39"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+    </row>
+    <row r="20" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="36"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="E20" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="F20" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-    </row>
-    <row r="21" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="50" t="s">
+      <c r="G20" s="39"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+    </row>
+    <row r="21" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="36"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="E21" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="F21" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="41"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-    </row>
-    <row r="22" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="50" t="s">
+      <c r="G21" s="39"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+    </row>
+    <row r="22" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="E22" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="F22" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-    </row>
-    <row r="23" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="38"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="50" t="s">
+      <c r="G22" s="39"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+    </row>
+    <row r="23" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="36"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="E23" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="F23" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-    </row>
-    <row r="24" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="50" t="s">
+      <c r="G23" s="39"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="36"/>
+    </row>
+    <row r="24" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="50" t="s">
+      <c r="E24" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="F24" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="41"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-    </row>
-    <row r="25" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="38"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="50" t="s">
+      <c r="G24" s="39"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+    </row>
+    <row r="25" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="E25" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="F25" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="41"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-    </row>
-    <row r="26" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="38"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="50" t="s">
+      <c r="G25" s="39"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+    </row>
+    <row r="26" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="50" t="s">
+      <c r="E26" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="F26" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="41"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-    </row>
-    <row r="27" spans="1:14" s="39" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="50" t="s">
+      <c r="G26" s="39"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+    </row>
+    <row r="27" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="36"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="E27" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="F27" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="41"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-      <c r="L27" s="38"/>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-    </row>
-    <row r="28" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="34"/>
-      <c r="C28" s="36"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+    </row>
+    <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
       <c r="D28" s="34"/>
-      <c r="E28" s="36"/>
+      <c r="E28" s="32"/>
       <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-    </row>
-    <row r="29" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="34"/>
-      <c r="C29" s="36"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+    </row>
+    <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
       <c r="D29" s="34"/>
-      <c r="E29" s="36"/>
+      <c r="E29" s="32"/>
       <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-    </row>
-    <row r="30" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="34"/>
-      <c r="C30" s="36"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+    </row>
+    <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="34"/>
-      <c r="E30" s="36"/>
+      <c r="E30" s="32"/>
       <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-    </row>
-    <row r="31" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="34"/>
-      <c r="C31" s="36"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+    </row>
+    <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="34"/>
-      <c r="E31" s="36"/>
+      <c r="E31" s="32"/>
       <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-    </row>
-    <row r="32" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="34"/>
-      <c r="C32" s="36"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+    </row>
+    <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="34"/>
-      <c r="E32" s="36"/>
+      <c r="E32" s="32"/>
       <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-    </row>
-    <row r="33" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="34"/>
-      <c r="C33" s="36"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+    </row>
+    <row r="33" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
       <c r="D33" s="34"/>
-      <c r="E33" s="36"/>
+      <c r="E33" s="32"/>
       <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-    </row>
-    <row r="34" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="34"/>
-      <c r="C34" s="36"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+    </row>
+    <row r="34" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
       <c r="D34" s="34"/>
-      <c r="E34" s="36"/>
+      <c r="E34" s="32"/>
       <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-    </row>
-    <row r="35" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="34"/>
-      <c r="C35" s="36"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+    </row>
+    <row r="35" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
       <c r="D35" s="34"/>
-      <c r="E35" s="36"/>
+      <c r="E35" s="32"/>
       <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-    </row>
-    <row r="36" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="34"/>
-      <c r="C36" s="36"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+    </row>
+    <row r="36" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="36"/>
+      <c r="E36" s="32"/>
       <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-    </row>
-    <row r="37" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="34"/>
-      <c r="C37" s="36"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+    </row>
+    <row r="37" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="36"/>
+      <c r="E37" s="32"/>
       <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-    </row>
-    <row r="38" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="34"/>
-      <c r="C38" s="36"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+    </row>
+    <row r="38" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
       <c r="D38" s="34"/>
-      <c r="E38" s="36"/>
+      <c r="E38" s="32"/>
       <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-    </row>
-    <row r="39" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="34"/>
-      <c r="C39" s="36"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+    </row>
+    <row r="39" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
       <c r="D39" s="34"/>
-      <c r="E39" s="36"/>
+      <c r="E39" s="32"/>
       <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-    </row>
-    <row r="40" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="34"/>
-      <c r="C40" s="36"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+    </row>
+    <row r="40" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
       <c r="D40" s="34"/>
-      <c r="E40" s="36"/>
+      <c r="E40" s="32"/>
       <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-    </row>
-    <row r="41" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="34"/>
-      <c r="C41" s="36"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+    </row>
+    <row r="41" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
       <c r="D41" s="34"/>
-      <c r="E41" s="36"/>
+      <c r="E41" s="32"/>
       <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-    </row>
-    <row r="42" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="34"/>
-      <c r="C42" s="36"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+    </row>
+    <row r="42" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="36"/>
+      <c r="E42" s="32"/>
       <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-    </row>
-    <row r="43" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="34"/>
-      <c r="C43" s="36"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+    </row>
+    <row r="43" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="36"/>
+      <c r="E43" s="32"/>
       <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-    </row>
-    <row r="44" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="34"/>
-      <c r="C44" s="36"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+    </row>
+    <row r="44" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="36"/>
+      <c r="E44" s="32"/>
       <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-    </row>
-    <row r="45" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="34"/>
-      <c r="C45" s="36"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+    </row>
+    <row r="45" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="36"/>
+      <c r="E45" s="32"/>
       <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-    </row>
-    <row r="46" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="34"/>
-      <c r="C46" s="36"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+    </row>
+    <row r="46" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="36"/>
+      <c r="E46" s="32"/>
       <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-    </row>
-    <row r="47" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="34"/>
-      <c r="C47" s="36"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+    </row>
+    <row r="47" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="36"/>
+      <c r="E47" s="32"/>
       <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-    </row>
-    <row r="48" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="34"/>
-      <c r="C48" s="36"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+    </row>
+    <row r="48" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="36"/>
+      <c r="E48" s="32"/>
       <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-    </row>
-    <row r="49" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="34"/>
-      <c r="C49" s="36"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+    </row>
+    <row r="49" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="36"/>
+      <c r="E49" s="32"/>
       <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-    </row>
-    <row r="50" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="34"/>
-      <c r="C50" s="36"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+    </row>
+    <row r="50" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="36"/>
+      <c r="E50" s="32"/>
       <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-    </row>
-    <row r="51" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="34"/>
-      <c r="C51" s="36"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+    </row>
+    <row r="51" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="36"/>
+      <c r="E51" s="32"/>
       <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-    </row>
-    <row r="52" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="34"/>
-      <c r="C52" s="36"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+    </row>
+    <row r="52" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="36"/>
+      <c r="E52" s="32"/>
       <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-    </row>
-    <row r="53" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="34"/>
-      <c r="C53" s="36"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+    </row>
+    <row r="53" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
       <c r="D53" s="34"/>
-      <c r="E53" s="36"/>
+      <c r="E53" s="32"/>
       <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-    </row>
-    <row r="54" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="34"/>
-      <c r="C54" s="36"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+    </row>
+    <row r="54" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
       <c r="D54" s="34"/>
-      <c r="E54" s="36"/>
+      <c r="E54" s="32"/>
       <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-    </row>
-    <row r="55" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="34"/>
-      <c r="C55" s="36"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+    </row>
+    <row r="55" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="36"/>
+      <c r="E55" s="32"/>
       <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-    </row>
-    <row r="56" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="34"/>
-      <c r="C56" s="36"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+    </row>
+    <row r="56" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="36"/>
+      <c r="E56" s="32"/>
       <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-    </row>
-    <row r="57" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="34"/>
-      <c r="C57" s="36"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+    </row>
+    <row r="57" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="36"/>
+      <c r="E57" s="32"/>
       <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-    </row>
-    <row r="58" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="34"/>
-      <c r="C58" s="36"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+    </row>
+    <row r="58" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="36"/>
+      <c r="E58" s="32"/>
       <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-    </row>
-    <row r="59" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="34"/>
-      <c r="C59" s="36"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+    </row>
+    <row r="59" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="36"/>
+      <c r="E59" s="32"/>
       <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-    </row>
-    <row r="60" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="34"/>
-      <c r="C60" s="36"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+    </row>
+    <row r="60" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="36"/>
+      <c r="E60" s="32"/>
       <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-    </row>
-    <row r="61" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="34"/>
-      <c r="C61" s="36"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+    </row>
+    <row r="61" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="36"/>
+      <c r="E61" s="32"/>
       <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-    </row>
-    <row r="62" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="34"/>
-      <c r="C62" s="36"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+    </row>
+    <row r="62" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="36"/>
+      <c r="E62" s="32"/>
       <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-    </row>
-    <row r="63" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="34"/>
-      <c r="C63" s="36"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+    </row>
+    <row r="63" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
       <c r="D63" s="34"/>
-      <c r="E63" s="36"/>
+      <c r="E63" s="32"/>
       <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-    </row>
-    <row r="64" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="34"/>
-      <c r="C64" s="36"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+    </row>
+    <row r="64" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
       <c r="D64" s="34"/>
-      <c r="E64" s="36"/>
+      <c r="E64" s="32"/>
       <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-    </row>
-    <row r="65" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="34"/>
-      <c r="C65" s="36"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+    </row>
+    <row r="65" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="32"/>
+      <c r="C65" s="32"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="36"/>
+      <c r="E65" s="32"/>
       <c r="F65" s="34"/>
-      <c r="G65" s="34"/>
-    </row>
-    <row r="66" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="34"/>
-      <c r="C66" s="36"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+    </row>
+    <row r="66" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="36"/>
+      <c r="E66" s="32"/>
       <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
-    </row>
-    <row r="67" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="34"/>
-      <c r="C67" s="36"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+    </row>
+    <row r="67" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="36"/>
+      <c r="E67" s="32"/>
       <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-    </row>
-    <row r="68" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="34"/>
-      <c r="C68" s="36"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+    </row>
+    <row r="68" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="36"/>
+      <c r="E68" s="32"/>
       <c r="F68" s="34"/>
-      <c r="G68" s="34"/>
-    </row>
-    <row r="69" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="34"/>
-      <c r="C69" s="36"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+    </row>
+    <row r="69" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="32"/>
+      <c r="C69" s="32"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="36"/>
+      <c r="E69" s="32"/>
       <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-    </row>
-    <row r="70" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="34"/>
-      <c r="C70" s="36"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+    </row>
+    <row r="70" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="36"/>
+      <c r="E70" s="32"/>
       <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-    </row>
-    <row r="71" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="34"/>
-      <c r="C71" s="36"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+    </row>
+    <row r="71" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="36"/>
+      <c r="E71" s="32"/>
       <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-    </row>
-    <row r="72" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="34"/>
-      <c r="C72" s="36"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+    </row>
+    <row r="72" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="32"/>
+      <c r="C72" s="32"/>
       <c r="D72" s="34"/>
-      <c r="E72" s="36"/>
+      <c r="E72" s="32"/>
       <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
-    </row>
-    <row r="73" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="34"/>
-      <c r="C73" s="36"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+    </row>
+    <row r="73" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
       <c r="D73" s="34"/>
-      <c r="E73" s="36"/>
+      <c r="E73" s="32"/>
       <c r="F73" s="34"/>
-      <c r="G73" s="34"/>
-    </row>
-    <row r="74" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="34"/>
-      <c r="C74" s="36"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+    </row>
+    <row r="74" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
       <c r="D74" s="34"/>
-      <c r="E74" s="36"/>
+      <c r="E74" s="32"/>
       <c r="F74" s="34"/>
-      <c r="G74" s="34"/>
-    </row>
-    <row r="75" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="34"/>
-      <c r="C75" s="36"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+    </row>
+    <row r="75" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
       <c r="D75" s="34"/>
-      <c r="E75" s="36"/>
+      <c r="E75" s="32"/>
       <c r="F75" s="34"/>
-      <c r="G75" s="34"/>
-    </row>
-    <row r="76" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="34"/>
-      <c r="C76" s="36"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+    </row>
+    <row r="76" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
       <c r="D76" s="34"/>
-      <c r="E76" s="36"/>
+      <c r="E76" s="32"/>
       <c r="F76" s="34"/>
-      <c r="G76" s="34"/>
-    </row>
-    <row r="77" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="34"/>
-      <c r="C77" s="36"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+    </row>
+    <row r="77" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="32"/>
+      <c r="C77" s="32"/>
       <c r="D77" s="34"/>
-      <c r="E77" s="36"/>
+      <c r="E77" s="32"/>
       <c r="F77" s="34"/>
-      <c r="G77" s="34"/>
-    </row>
-    <row r="78" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="34"/>
-      <c r="C78" s="36"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+    </row>
+    <row r="78" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="32"/>
+      <c r="C78" s="32"/>
       <c r="D78" s="34"/>
-      <c r="E78" s="36"/>
+      <c r="E78" s="32"/>
       <c r="F78" s="34"/>
-      <c r="G78" s="34"/>
-    </row>
-    <row r="79" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="34"/>
-      <c r="C79" s="36"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+    </row>
+    <row r="79" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
       <c r="D79" s="34"/>
-      <c r="E79" s="36"/>
+      <c r="E79" s="32"/>
       <c r="F79" s="34"/>
-      <c r="G79" s="34"/>
-    </row>
-    <row r="80" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="34"/>
-      <c r="C80" s="36"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+    </row>
+    <row r="80" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
       <c r="D80" s="34"/>
-      <c r="E80" s="36"/>
+      <c r="E80" s="32"/>
       <c r="F80" s="34"/>
-      <c r="G80" s="34"/>
-    </row>
-    <row r="81" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="34"/>
-      <c r="C81" s="36"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+    </row>
+    <row r="81" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="32"/>
+      <c r="C81" s="32"/>
       <c r="D81" s="34"/>
-      <c r="E81" s="36"/>
+      <c r="E81" s="32"/>
       <c r="F81" s="34"/>
-      <c r="G81" s="34"/>
-    </row>
-    <row r="82" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="34"/>
-      <c r="C82" s="36"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+    </row>
+    <row r="82" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
       <c r="D82" s="34"/>
-      <c r="E82" s="36"/>
+      <c r="E82" s="32"/>
       <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-    </row>
-    <row r="83" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="34"/>
-      <c r="C83" s="36"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+    </row>
+    <row r="83" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
       <c r="D83" s="34"/>
-      <c r="E83" s="36"/>
+      <c r="E83" s="32"/>
       <c r="F83" s="34"/>
-      <c r="G83" s="34"/>
-    </row>
-    <row r="84" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="34"/>
-      <c r="C84" s="36"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+    </row>
+    <row r="84" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
       <c r="D84" s="34"/>
-      <c r="E84" s="36"/>
+      <c r="E84" s="32"/>
       <c r="F84" s="34"/>
-      <c r="G84" s="34"/>
-    </row>
-    <row r="85" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="34"/>
-      <c r="C85" s="36"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+    </row>
+    <row r="85" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="32"/>
+      <c r="C85" s="32"/>
       <c r="D85" s="34"/>
-      <c r="E85" s="36"/>
+      <c r="E85" s="32"/>
       <c r="F85" s="34"/>
-      <c r="G85" s="34"/>
-    </row>
-    <row r="86" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="34"/>
-      <c r="C86" s="36"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+    </row>
+    <row r="86" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
       <c r="D86" s="34"/>
-      <c r="E86" s="36"/>
+      <c r="E86" s="32"/>
       <c r="F86" s="34"/>
-      <c r="G86" s="34"/>
-    </row>
-    <row r="87" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="34"/>
-      <c r="C87" s="36"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+    </row>
+    <row r="87" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
       <c r="D87" s="34"/>
-      <c r="E87" s="36"/>
+      <c r="E87" s="32"/>
       <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-    </row>
-    <row r="88" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="34"/>
-      <c r="C88" s="36"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+    </row>
+    <row r="88" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
       <c r="D88" s="34"/>
-      <c r="E88" s="36"/>
+      <c r="E88" s="32"/>
       <c r="F88" s="34"/>
-      <c r="G88" s="34"/>
-    </row>
-    <row r="89" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B89" s="34"/>
-      <c r="C89" s="36"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+    </row>
+    <row r="89" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="32"/>
+      <c r="C89" s="32"/>
       <c r="D89" s="34"/>
-      <c r="E89" s="36"/>
+      <c r="E89" s="32"/>
       <c r="F89" s="34"/>
-      <c r="G89" s="34"/>
-    </row>
-    <row r="90" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="34"/>
-      <c r="C90" s="36"/>
+      <c r="G89" s="32"/>
+      <c r="H89" s="32"/>
+    </row>
+    <row r="90" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="32"/>
+      <c r="C90" s="32"/>
       <c r="D90" s="34"/>
-      <c r="E90" s="36"/>
+      <c r="E90" s="32"/>
       <c r="F90" s="34"/>
-      <c r="G90" s="34"/>
-    </row>
-    <row r="91" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="34"/>
-      <c r="C91" s="36"/>
+      <c r="G90" s="32"/>
+      <c r="H90" s="32"/>
+    </row>
+    <row r="91" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
       <c r="D91" s="34"/>
-      <c r="E91" s="36"/>
+      <c r="E91" s="32"/>
       <c r="F91" s="34"/>
-      <c r="G91" s="34"/>
-    </row>
-    <row r="92" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="34"/>
-      <c r="C92" s="36"/>
+      <c r="G91" s="32"/>
+      <c r="H91" s="32"/>
+    </row>
+    <row r="92" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
       <c r="D92" s="34"/>
-      <c r="E92" s="36"/>
+      <c r="E92" s="32"/>
       <c r="F92" s="34"/>
-      <c r="G92" s="34"/>
-    </row>
-    <row r="93" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B93" s="34"/>
-      <c r="C93" s="36"/>
+      <c r="G92" s="32"/>
+      <c r="H92" s="32"/>
+    </row>
+    <row r="93" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="32"/>
+      <c r="C93" s="32"/>
       <c r="D93" s="34"/>
-      <c r="E93" s="36"/>
+      <c r="E93" s="32"/>
       <c r="F93" s="34"/>
-      <c r="G93" s="34"/>
-    </row>
-    <row r="94" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="34"/>
-      <c r="C94" s="36"/>
+      <c r="G93" s="32"/>
+      <c r="H93" s="32"/>
+    </row>
+    <row r="94" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="32"/>
+      <c r="C94" s="32"/>
       <c r="D94" s="34"/>
-      <c r="E94" s="36"/>
+      <c r="E94" s="32"/>
       <c r="F94" s="34"/>
-      <c r="G94" s="34"/>
-    </row>
-    <row r="95" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B95" s="34"/>
-      <c r="C95" s="36"/>
+      <c r="G94" s="32"/>
+      <c r="H94" s="32"/>
+    </row>
+    <row r="95" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="32"/>
+      <c r="C95" s="32"/>
       <c r="D95" s="34"/>
-      <c r="E95" s="36"/>
+      <c r="E95" s="32"/>
       <c r="F95" s="34"/>
-      <c r="G95" s="34"/>
-    </row>
-    <row r="96" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="34"/>
-      <c r="C96" s="36"/>
+      <c r="G95" s="32"/>
+      <c r="H95" s="32"/>
+    </row>
+    <row r="96" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="32"/>
+      <c r="C96" s="32"/>
       <c r="D96" s="34"/>
-      <c r="E96" s="36"/>
+      <c r="E96" s="32"/>
       <c r="F96" s="34"/>
-      <c r="G96" s="34"/>
-    </row>
-    <row r="97" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="34"/>
-      <c r="C97" s="36"/>
+      <c r="G96" s="32"/>
+      <c r="H96" s="32"/>
+    </row>
+    <row r="97" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="32"/>
+      <c r="C97" s="32"/>
       <c r="D97" s="34"/>
-      <c r="E97" s="36"/>
+      <c r="E97" s="32"/>
       <c r="F97" s="34"/>
-      <c r="G97" s="34"/>
-    </row>
-    <row r="98" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="34"/>
-      <c r="C98" s="36"/>
+      <c r="G97" s="32"/>
+      <c r="H97" s="32"/>
+    </row>
+    <row r="98" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
       <c r="D98" s="34"/>
-      <c r="E98" s="36"/>
+      <c r="E98" s="32"/>
       <c r="F98" s="34"/>
-      <c r="G98" s="34"/>
-    </row>
-    <row r="99" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="34"/>
-      <c r="C99" s="36"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="32"/>
+    </row>
+    <row r="99" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
       <c r="D99" s="34"/>
-      <c r="E99" s="36"/>
+      <c r="E99" s="32"/>
       <c r="F99" s="34"/>
-      <c r="G99" s="34"/>
-    </row>
-    <row r="100" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="34"/>
-      <c r="C100" s="36"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+    </row>
+    <row r="100" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
       <c r="D100" s="34"/>
-      <c r="E100" s="36"/>
+      <c r="E100" s="32"/>
       <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-    </row>
-    <row r="101" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="34"/>
-      <c r="C101" s="36"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+    </row>
+    <row r="101" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
       <c r="D101" s="34"/>
-      <c r="E101" s="36"/>
+      <c r="E101" s="32"/>
       <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-    </row>
-    <row r="102" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="34"/>
-      <c r="C102" s="36"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+    </row>
+    <row r="102" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
       <c r="D102" s="34"/>
-      <c r="E102" s="36"/>
+      <c r="E102" s="32"/>
       <c r="F102" s="34"/>
-      <c r="G102" s="34"/>
-    </row>
-    <row r="103" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B103" s="34"/>
-      <c r="C103" s="36"/>
+      <c r="G102" s="32"/>
+      <c r="H102" s="32"/>
+    </row>
+    <row r="103" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="32"/>
+      <c r="C103" s="32"/>
       <c r="D103" s="34"/>
-      <c r="E103" s="36"/>
+      <c r="E103" s="32"/>
       <c r="F103" s="34"/>
-      <c r="G103" s="34"/>
-    </row>
-    <row r="104" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="34"/>
-      <c r="C104" s="36"/>
+      <c r="G103" s="32"/>
+      <c r="H103" s="32"/>
+    </row>
+    <row r="104" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
       <c r="D104" s="34"/>
-      <c r="E104" s="36"/>
+      <c r="E104" s="32"/>
       <c r="F104" s="34"/>
-      <c r="G104" s="34"/>
-    </row>
-    <row r="105" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="34"/>
-      <c r="C105" s="36"/>
+      <c r="G104" s="32"/>
+      <c r="H104" s="32"/>
+    </row>
+    <row r="105" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="32"/>
+      <c r="C105" s="32"/>
       <c r="D105" s="34"/>
-      <c r="E105" s="36"/>
+      <c r="E105" s="32"/>
       <c r="F105" s="34"/>
-      <c r="G105" s="34"/>
-    </row>
-    <row r="106" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="34"/>
-      <c r="C106" s="36"/>
+      <c r="G105" s="32"/>
+      <c r="H105" s="32"/>
+    </row>
+    <row r="106" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="32"/>
+      <c r="C106" s="32"/>
       <c r="D106" s="34"/>
-      <c r="E106" s="36"/>
+      <c r="E106" s="32"/>
       <c r="F106" s="34"/>
-      <c r="G106" s="34"/>
-    </row>
-    <row r="107" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="34"/>
-      <c r="C107" s="36"/>
+      <c r="G106" s="32"/>
+      <c r="H106" s="32"/>
+    </row>
+    <row r="107" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="32"/>
+      <c r="C107" s="32"/>
       <c r="D107" s="34"/>
-      <c r="E107" s="36"/>
+      <c r="E107" s="32"/>
       <c r="F107" s="34"/>
-      <c r="G107" s="34"/>
-    </row>
-    <row r="108" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="34"/>
-      <c r="C108" s="36"/>
+      <c r="G107" s="32"/>
+      <c r="H107" s="32"/>
+    </row>
+    <row r="108" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="32"/>
+      <c r="C108" s="32"/>
       <c r="D108" s="34"/>
-      <c r="E108" s="36"/>
+      <c r="E108" s="32"/>
       <c r="F108" s="34"/>
-      <c r="G108" s="34"/>
-    </row>
-    <row r="109" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="34"/>
-      <c r="C109" s="36"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
+    </row>
+    <row r="109" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="32"/>
+      <c r="C109" s="32"/>
       <c r="D109" s="34"/>
-      <c r="E109" s="36"/>
+      <c r="E109" s="32"/>
       <c r="F109" s="34"/>
-      <c r="G109" s="34"/>
-    </row>
-    <row r="110" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="34"/>
-      <c r="C110" s="36"/>
+      <c r="G109" s="32"/>
+      <c r="H109" s="32"/>
+    </row>
+    <row r="110" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B110" s="32"/>
+      <c r="C110" s="32"/>
       <c r="D110" s="34"/>
-      <c r="E110" s="36"/>
+      <c r="E110" s="32"/>
       <c r="F110" s="34"/>
-      <c r="G110" s="34"/>
-    </row>
-    <row r="111" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="34"/>
-      <c r="C111" s="36"/>
+      <c r="G110" s="32"/>
+      <c r="H110" s="32"/>
+    </row>
+    <row r="111" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="32"/>
+      <c r="C111" s="32"/>
       <c r="D111" s="34"/>
-      <c r="E111" s="36"/>
+      <c r="E111" s="32"/>
       <c r="F111" s="34"/>
-      <c r="G111" s="34"/>
-    </row>
-    <row r="112" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="34"/>
-      <c r="C112" s="36"/>
+      <c r="G111" s="32"/>
+      <c r="H111" s="32"/>
+    </row>
+    <row r="112" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="32"/>
+      <c r="C112" s="32"/>
       <c r="D112" s="34"/>
-      <c r="E112" s="36"/>
+      <c r="E112" s="32"/>
       <c r="F112" s="34"/>
-      <c r="G112" s="34"/>
-    </row>
-    <row r="113" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="34"/>
-      <c r="C113" s="36"/>
+      <c r="G112" s="32"/>
+      <c r="H112" s="32"/>
+    </row>
+    <row r="113" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="32"/>
+      <c r="C113" s="32"/>
       <c r="D113" s="34"/>
-      <c r="E113" s="36"/>
+      <c r="E113" s="32"/>
       <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-    </row>
-    <row r="114" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="34"/>
-      <c r="C114" s="36"/>
+      <c r="G113" s="32"/>
+      <c r="H113" s="32"/>
+    </row>
+    <row r="114" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="32"/>
+      <c r="C114" s="32"/>
       <c r="D114" s="34"/>
-      <c r="E114" s="36"/>
+      <c r="E114" s="32"/>
       <c r="F114" s="34"/>
-      <c r="G114" s="34"/>
-    </row>
-    <row r="115" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="34"/>
-      <c r="C115" s="36"/>
+      <c r="G114" s="32"/>
+      <c r="H114" s="32"/>
+    </row>
+    <row r="115" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="32"/>
+      <c r="C115" s="32"/>
       <c r="D115" s="34"/>
-      <c r="E115" s="36"/>
+      <c r="E115" s="32"/>
       <c r="F115" s="34"/>
-      <c r="G115" s="34"/>
-    </row>
-    <row r="116" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="34"/>
-      <c r="C116" s="36"/>
+      <c r="G115" s="32"/>
+      <c r="H115" s="32"/>
+    </row>
+    <row r="116" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B116" s="32"/>
+      <c r="C116" s="32"/>
       <c r="D116" s="34"/>
-      <c r="E116" s="36"/>
+      <c r="E116" s="32"/>
       <c r="F116" s="34"/>
-      <c r="G116" s="34"/>
-    </row>
-    <row r="117" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="34"/>
-      <c r="C117" s="36"/>
+      <c r="G116" s="32"/>
+      <c r="H116" s="32"/>
+    </row>
+    <row r="117" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="32"/>
+      <c r="C117" s="32"/>
       <c r="D117" s="34"/>
-      <c r="E117" s="36"/>
+      <c r="E117" s="32"/>
       <c r="F117" s="34"/>
-      <c r="G117" s="34"/>
-    </row>
-    <row r="118" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="34"/>
-      <c r="C118" s="36"/>
+      <c r="G117" s="32"/>
+      <c r="H117" s="32"/>
+    </row>
+    <row r="118" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="32"/>
+      <c r="C118" s="32"/>
       <c r="D118" s="34"/>
-      <c r="E118" s="36"/>
+      <c r="E118" s="32"/>
       <c r="F118" s="34"/>
-      <c r="G118" s="34"/>
-    </row>
-    <row r="119" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="34"/>
-      <c r="C119" s="36"/>
+      <c r="G118" s="32"/>
+      <c r="H118" s="32"/>
+    </row>
+    <row r="119" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="32"/>
+      <c r="C119" s="32"/>
       <c r="D119" s="34"/>
-      <c r="E119" s="36"/>
+      <c r="E119" s="32"/>
       <c r="F119" s="34"/>
-      <c r="G119" s="34"/>
-    </row>
-    <row r="120" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="34"/>
-      <c r="C120" s="36"/>
+      <c r="G119" s="32"/>
+      <c r="H119" s="32"/>
+    </row>
+    <row r="120" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="32"/>
+      <c r="C120" s="32"/>
       <c r="D120" s="34"/>
-      <c r="E120" s="36"/>
+      <c r="E120" s="32"/>
       <c r="F120" s="34"/>
-      <c r="G120" s="34"/>
-    </row>
-    <row r="121" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="34"/>
-      <c r="C121" s="36"/>
+      <c r="G120" s="32"/>
+      <c r="H120" s="32"/>
+    </row>
+    <row r="121" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="32"/>
+      <c r="C121" s="32"/>
       <c r="D121" s="34"/>
-      <c r="E121" s="36"/>
+      <c r="E121" s="32"/>
       <c r="F121" s="34"/>
-      <c r="G121" s="34"/>
-    </row>
-    <row r="122" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="34"/>
-      <c r="C122" s="36"/>
+      <c r="G121" s="32"/>
+      <c r="H121" s="32"/>
+    </row>
+    <row r="122" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B122" s="32"/>
+      <c r="C122" s="32"/>
       <c r="D122" s="34"/>
-      <c r="E122" s="36"/>
+      <c r="E122" s="32"/>
       <c r="F122" s="34"/>
-      <c r="G122" s="34"/>
-    </row>
-    <row r="123" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="34"/>
-      <c r="C123" s="36"/>
+      <c r="G122" s="32"/>
+      <c r="H122" s="32"/>
+    </row>
+    <row r="123" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="32"/>
+      <c r="C123" s="32"/>
       <c r="D123" s="34"/>
-      <c r="E123" s="36"/>
+      <c r="E123" s="32"/>
       <c r="F123" s="34"/>
-      <c r="G123" s="34"/>
-    </row>
-    <row r="124" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="34"/>
-      <c r="C124" s="36"/>
+      <c r="G123" s="32"/>
+      <c r="H123" s="32"/>
+    </row>
+    <row r="124" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="32"/>
+      <c r="C124" s="32"/>
       <c r="D124" s="34"/>
-      <c r="E124" s="36"/>
+      <c r="E124" s="32"/>
       <c r="F124" s="34"/>
-      <c r="G124" s="34"/>
-    </row>
-    <row r="125" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="34"/>
-      <c r="C125" s="36"/>
+      <c r="G124" s="32"/>
+      <c r="H124" s="32"/>
+    </row>
+    <row r="125" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="32"/>
+      <c r="C125" s="32"/>
       <c r="D125" s="34"/>
-      <c r="E125" s="36"/>
+      <c r="E125" s="32"/>
       <c r="F125" s="34"/>
-      <c r="G125" s="34"/>
-    </row>
-    <row r="126" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="34"/>
-      <c r="C126" s="36"/>
+      <c r="G125" s="32"/>
+      <c r="H125" s="32"/>
+    </row>
+    <row r="126" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="32"/>
+      <c r="C126" s="32"/>
       <c r="D126" s="34"/>
-      <c r="E126" s="36"/>
+      <c r="E126" s="32"/>
       <c r="F126" s="34"/>
-      <c r="G126" s="34"/>
-    </row>
-    <row r="127" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="34"/>
-      <c r="C127" s="36"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="32"/>
+    </row>
+    <row r="127" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="32"/>
+      <c r="C127" s="32"/>
       <c r="D127" s="34"/>
-      <c r="E127" s="36"/>
+      <c r="E127" s="32"/>
       <c r="F127" s="34"/>
-      <c r="G127" s="34"/>
-    </row>
-    <row r="128" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="34"/>
-      <c r="C128" s="36"/>
+      <c r="G127" s="32"/>
+      <c r="H127" s="32"/>
+    </row>
+    <row r="128" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B128" s="32"/>
+      <c r="C128" s="32"/>
       <c r="D128" s="34"/>
-      <c r="E128" s="36"/>
+      <c r="E128" s="32"/>
       <c r="F128" s="34"/>
-      <c r="G128" s="34"/>
-    </row>
-    <row r="129" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="34"/>
-      <c r="C129" s="36"/>
+      <c r="G128" s="32"/>
+      <c r="H128" s="32"/>
+    </row>
+    <row r="129" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="32"/>
+      <c r="C129" s="32"/>
       <c r="D129" s="34"/>
-      <c r="E129" s="36"/>
+      <c r="E129" s="32"/>
       <c r="F129" s="34"/>
-      <c r="G129" s="34"/>
-    </row>
-    <row r="130" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="34"/>
-      <c r="C130" s="36"/>
+      <c r="G129" s="32"/>
+      <c r="H129" s="32"/>
+    </row>
+    <row r="130" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="32"/>
+      <c r="C130" s="32"/>
       <c r="D130" s="34"/>
-      <c r="E130" s="36"/>
+      <c r="E130" s="32"/>
       <c r="F130" s="34"/>
-      <c r="G130" s="34"/>
-    </row>
-    <row r="131" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="34"/>
-      <c r="C131" s="36"/>
+      <c r="G130" s="32"/>
+      <c r="H130" s="32"/>
+    </row>
+    <row r="131" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="32"/>
+      <c r="C131" s="32"/>
       <c r="D131" s="34"/>
-      <c r="E131" s="36"/>
+      <c r="E131" s="32"/>
       <c r="F131" s="34"/>
-      <c r="G131" s="34"/>
-    </row>
-    <row r="132" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="34"/>
-      <c r="C132" s="36"/>
+      <c r="G131" s="32"/>
+      <c r="H131" s="32"/>
+    </row>
+    <row r="132" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="32"/>
+      <c r="C132" s="32"/>
       <c r="D132" s="34"/>
-      <c r="E132" s="36"/>
+      <c r="E132" s="32"/>
       <c r="F132" s="34"/>
-      <c r="G132" s="34"/>
-    </row>
-    <row r="133" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="34"/>
-      <c r="C133" s="36"/>
+      <c r="G132" s="32"/>
+      <c r="H132" s="32"/>
+    </row>
+    <row r="133" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="32"/>
+      <c r="C133" s="32"/>
       <c r="D133" s="34"/>
-      <c r="E133" s="36"/>
+      <c r="E133" s="32"/>
       <c r="F133" s="34"/>
-      <c r="G133" s="34"/>
-    </row>
-    <row r="134" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B134" s="34"/>
-      <c r="C134" s="36"/>
+      <c r="G133" s="32"/>
+      <c r="H133" s="32"/>
+    </row>
+    <row r="134" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B134" s="32"/>
+      <c r="C134" s="32"/>
       <c r="D134" s="34"/>
-      <c r="E134" s="36"/>
+      <c r="E134" s="32"/>
       <c r="F134" s="34"/>
-      <c r="G134" s="34"/>
-    </row>
-    <row r="135" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B135" s="34"/>
-      <c r="C135" s="36"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+    </row>
+    <row r="135" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B135" s="32"/>
+      <c r="C135" s="32"/>
       <c r="D135" s="34"/>
-      <c r="E135" s="36"/>
+      <c r="E135" s="32"/>
       <c r="F135" s="34"/>
-      <c r="G135" s="34"/>
-    </row>
-    <row r="136" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B136" s="34"/>
-      <c r="C136" s="36"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+    </row>
+    <row r="136" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B136" s="32"/>
+      <c r="C136" s="32"/>
       <c r="D136" s="34"/>
-      <c r="E136" s="36"/>
+      <c r="E136" s="32"/>
       <c r="F136" s="34"/>
-      <c r="G136" s="34"/>
-    </row>
-    <row r="137" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B137" s="34"/>
-      <c r="C137" s="36"/>
+      <c r="G136" s="32"/>
+      <c r="H136" s="32"/>
+    </row>
+    <row r="137" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B137" s="32"/>
+      <c r="C137" s="32"/>
       <c r="D137" s="34"/>
-      <c r="E137" s="36"/>
+      <c r="E137" s="32"/>
       <c r="F137" s="34"/>
-      <c r="G137" s="34"/>
-    </row>
-    <row r="138" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B138" s="34"/>
-      <c r="C138" s="36"/>
+      <c r="G137" s="32"/>
+      <c r="H137" s="32"/>
+    </row>
+    <row r="138" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B138" s="32"/>
+      <c r="C138" s="32"/>
       <c r="D138" s="34"/>
-      <c r="E138" s="36"/>
+      <c r="E138" s="32"/>
       <c r="F138" s="34"/>
-      <c r="G138" s="34"/>
-    </row>
-    <row r="139" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="34"/>
-      <c r="C139" s="36"/>
+      <c r="G138" s="32"/>
+      <c r="H138" s="32"/>
+    </row>
+    <row r="139" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B139" s="32"/>
+      <c r="C139" s="32"/>
       <c r="D139" s="34"/>
-      <c r="E139" s="36"/>
+      <c r="E139" s="32"/>
       <c r="F139" s="34"/>
-      <c r="G139" s="34"/>
-    </row>
-    <row r="140" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B140" s="34"/>
-      <c r="C140" s="36"/>
+      <c r="G139" s="32"/>
+      <c r="H139" s="32"/>
+    </row>
+    <row r="140" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B140" s="32"/>
+      <c r="C140" s="32"/>
       <c r="D140" s="34"/>
-      <c r="E140" s="36"/>
+      <c r="E140" s="32"/>
       <c r="F140" s="34"/>
-      <c r="G140" s="34"/>
-    </row>
-    <row r="141" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B141" s="34"/>
-      <c r="C141" s="36"/>
+      <c r="G140" s="32"/>
+      <c r="H140" s="32"/>
+    </row>
+    <row r="141" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B141" s="32"/>
+      <c r="C141" s="32"/>
       <c r="D141" s="34"/>
-      <c r="E141" s="36"/>
+      <c r="E141" s="32"/>
       <c r="F141" s="34"/>
-      <c r="G141" s="34"/>
-    </row>
-    <row r="142" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B142" s="34"/>
-      <c r="C142" s="36"/>
+      <c r="G141" s="32"/>
+      <c r="H141" s="32"/>
+    </row>
+    <row r="142" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="32"/>
+      <c r="C142" s="32"/>
       <c r="D142" s="34"/>
-      <c r="E142" s="36"/>
+      <c r="E142" s="32"/>
       <c r="F142" s="34"/>
-      <c r="G142" s="34"/>
-    </row>
-    <row r="143" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="34"/>
-      <c r="C143" s="36"/>
+      <c r="G142" s="32"/>
+      <c r="H142" s="32"/>
+    </row>
+    <row r="143" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B143" s="32"/>
+      <c r="C143" s="32"/>
       <c r="D143" s="34"/>
-      <c r="E143" s="36"/>
+      <c r="E143" s="32"/>
       <c r="F143" s="34"/>
-      <c r="G143" s="34"/>
-    </row>
-    <row r="144" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B144" s="34"/>
-      <c r="C144" s="36"/>
+      <c r="G143" s="32"/>
+      <c r="H143" s="32"/>
+    </row>
+    <row r="144" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B144" s="32"/>
+      <c r="C144" s="32"/>
       <c r="D144" s="34"/>
-      <c r="E144" s="36"/>
+      <c r="E144" s="32"/>
       <c r="F144" s="34"/>
-      <c r="G144" s="34"/>
-    </row>
-    <row r="145" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B145" s="34"/>
-      <c r="C145" s="36"/>
+      <c r="G144" s="32"/>
+      <c r="H144" s="32"/>
+    </row>
+    <row r="145" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B145" s="32"/>
+      <c r="C145" s="32"/>
       <c r="D145" s="34"/>
-      <c r="E145" s="36"/>
+      <c r="E145" s="32"/>
       <c r="F145" s="34"/>
-      <c r="G145" s="34"/>
-    </row>
-    <row r="146" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B146" s="34"/>
-      <c r="C146" s="36"/>
+      <c r="G145" s="32"/>
+      <c r="H145" s="32"/>
+    </row>
+    <row r="146" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B146" s="32"/>
+      <c r="C146" s="32"/>
       <c r="D146" s="34"/>
-      <c r="E146" s="36"/>
+      <c r="E146" s="32"/>
       <c r="F146" s="34"/>
-      <c r="G146" s="34"/>
-    </row>
-    <row r="147" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B147" s="34"/>
-      <c r="C147" s="36"/>
+      <c r="G146" s="32"/>
+      <c r="H146" s="32"/>
+    </row>
+    <row r="147" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B147" s="32"/>
+      <c r="C147" s="32"/>
       <c r="D147" s="34"/>
-      <c r="E147" s="36"/>
+      <c r="E147" s="32"/>
       <c r="F147" s="34"/>
-      <c r="G147" s="34"/>
-    </row>
-    <row r="148" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B148" s="34"/>
-      <c r="C148" s="36"/>
+      <c r="G147" s="32"/>
+      <c r="H147" s="32"/>
+    </row>
+    <row r="148" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B148" s="32"/>
+      <c r="C148" s="32"/>
       <c r="D148" s="34"/>
-      <c r="E148" s="36"/>
+      <c r="E148" s="32"/>
       <c r="F148" s="34"/>
-      <c r="G148" s="34"/>
-    </row>
-    <row r="149" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B149" s="34"/>
-      <c r="C149" s="36"/>
+      <c r="G148" s="32"/>
+      <c r="H148" s="32"/>
+    </row>
+    <row r="149" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B149" s="32"/>
+      <c r="C149" s="32"/>
       <c r="D149" s="34"/>
-      <c r="E149" s="36"/>
+      <c r="E149" s="32"/>
       <c r="F149" s="34"/>
-      <c r="G149" s="34"/>
-    </row>
-    <row r="150" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="34"/>
-      <c r="C150" s="36"/>
+      <c r="G149" s="32"/>
+      <c r="H149" s="32"/>
+    </row>
+    <row r="150" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B150" s="32"/>
+      <c r="C150" s="32"/>
       <c r="D150" s="34"/>
-      <c r="E150" s="36"/>
+      <c r="E150" s="32"/>
       <c r="F150" s="34"/>
-      <c r="G150" s="34"/>
-    </row>
-    <row r="151" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B151" s="34"/>
-      <c r="C151" s="36"/>
+      <c r="G150" s="32"/>
+      <c r="H150" s="32"/>
+    </row>
+    <row r="151" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B151" s="32"/>
+      <c r="C151" s="32"/>
       <c r="D151" s="34"/>
-      <c r="E151" s="36"/>
+      <c r="E151" s="32"/>
       <c r="F151" s="34"/>
-      <c r="G151" s="34"/>
-    </row>
-    <row r="152" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="34"/>
-      <c r="C152" s="36"/>
+      <c r="G151" s="32"/>
+      <c r="H151" s="32"/>
+    </row>
+    <row r="152" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B152" s="32"/>
+      <c r="C152" s="32"/>
       <c r="D152" s="34"/>
-      <c r="E152" s="36"/>
+      <c r="E152" s="32"/>
       <c r="F152" s="34"/>
-      <c r="G152" s="34"/>
-    </row>
-    <row r="153" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="34"/>
-      <c r="C153" s="36"/>
+      <c r="G152" s="32"/>
+      <c r="H152" s="32"/>
+    </row>
+    <row r="153" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="32"/>
+      <c r="C153" s="32"/>
       <c r="D153" s="34"/>
-      <c r="E153" s="36"/>
+      <c r="E153" s="32"/>
       <c r="F153" s="34"/>
-      <c r="G153" s="34"/>
-    </row>
-    <row r="154" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B154" s="34"/>
-      <c r="C154" s="36"/>
+      <c r="G153" s="32"/>
+      <c r="H153" s="32"/>
+    </row>
+    <row r="154" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B154" s="32"/>
+      <c r="C154" s="32"/>
       <c r="D154" s="34"/>
-      <c r="E154" s="36"/>
+      <c r="E154" s="32"/>
       <c r="F154" s="34"/>
-      <c r="G154" s="34"/>
-    </row>
-    <row r="155" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B155" s="34"/>
-      <c r="C155" s="36"/>
+      <c r="G154" s="32"/>
+      <c r="H154" s="32"/>
+    </row>
+    <row r="155" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B155" s="32"/>
+      <c r="C155" s="32"/>
       <c r="D155" s="34"/>
-      <c r="E155" s="36"/>
+      <c r="E155" s="32"/>
       <c r="F155" s="34"/>
-      <c r="G155" s="34"/>
-    </row>
-    <row r="156" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B156" s="34"/>
-      <c r="C156" s="36"/>
+      <c r="G155" s="32"/>
+      <c r="H155" s="32"/>
+    </row>
+    <row r="156" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B156" s="32"/>
+      <c r="C156" s="32"/>
       <c r="D156" s="34"/>
-      <c r="E156" s="36"/>
+      <c r="E156" s="32"/>
       <c r="F156" s="34"/>
-      <c r="G156" s="34"/>
-    </row>
-    <row r="157" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B157" s="34"/>
-      <c r="C157" s="36"/>
+      <c r="G156" s="32"/>
+      <c r="H156" s="32"/>
+    </row>
+    <row r="157" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B157" s="32"/>
+      <c r="C157" s="32"/>
       <c r="D157" s="34"/>
-      <c r="E157" s="36"/>
+      <c r="E157" s="32"/>
       <c r="F157" s="34"/>
-      <c r="G157" s="34"/>
-    </row>
-    <row r="158" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B158" s="34"/>
-      <c r="C158" s="36"/>
+      <c r="G157" s="32"/>
+      <c r="H157" s="32"/>
+    </row>
+    <row r="158" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B158" s="32"/>
+      <c r="C158" s="32"/>
       <c r="D158" s="34"/>
-      <c r="E158" s="36"/>
+      <c r="E158" s="32"/>
       <c r="F158" s="34"/>
-      <c r="G158" s="34"/>
-    </row>
-    <row r="159" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B159" s="34"/>
-      <c r="C159" s="36"/>
+      <c r="G158" s="32"/>
+      <c r="H158" s="32"/>
+    </row>
+    <row r="159" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B159" s="32"/>
+      <c r="C159" s="32"/>
       <c r="D159" s="34"/>
-      <c r="E159" s="36"/>
+      <c r="E159" s="32"/>
       <c r="F159" s="34"/>
-      <c r="G159" s="34"/>
-    </row>
-    <row r="160" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B160" s="34"/>
-      <c r="C160" s="36"/>
+      <c r="G159" s="32"/>
+      <c r="H159" s="32"/>
+    </row>
+    <row r="160" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B160" s="32"/>
+      <c r="C160" s="32"/>
       <c r="D160" s="34"/>
-      <c r="E160" s="36"/>
+      <c r="E160" s="32"/>
       <c r="F160" s="34"/>
-      <c r="G160" s="34"/>
-    </row>
-    <row r="161" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B161" s="34"/>
-      <c r="C161" s="36"/>
+      <c r="G160" s="32"/>
+      <c r="H160" s="32"/>
+    </row>
+    <row r="161" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B161" s="32"/>
+      <c r="C161" s="32"/>
       <c r="D161" s="34"/>
-      <c r="E161" s="36"/>
+      <c r="E161" s="32"/>
       <c r="F161" s="34"/>
-      <c r="G161" s="34"/>
-    </row>
-    <row r="162" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B162" s="34"/>
-      <c r="C162" s="36"/>
+      <c r="G161" s="32"/>
+      <c r="H161" s="32"/>
+    </row>
+    <row r="162" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B162" s="32"/>
+      <c r="C162" s="32"/>
       <c r="D162" s="34"/>
-      <c r="E162" s="36"/>
+      <c r="E162" s="32"/>
       <c r="F162" s="34"/>
-      <c r="G162" s="34"/>
-    </row>
-    <row r="163" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B163" s="34"/>
-      <c r="C163" s="36"/>
+      <c r="G162" s="32"/>
+      <c r="H162" s="32"/>
+    </row>
+    <row r="163" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B163" s="32"/>
+      <c r="C163" s="32"/>
       <c r="D163" s="34"/>
-      <c r="E163" s="36"/>
+      <c r="E163" s="32"/>
       <c r="F163" s="34"/>
-      <c r="G163" s="34"/>
-    </row>
-    <row r="164" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B164" s="34"/>
-      <c r="C164" s="36"/>
+      <c r="G163" s="32"/>
+      <c r="H163" s="32"/>
+    </row>
+    <row r="164" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B164" s="32"/>
+      <c r="C164" s="32"/>
       <c r="D164" s="34"/>
-      <c r="E164" s="36"/>
+      <c r="E164" s="32"/>
       <c r="F164" s="34"/>
-      <c r="G164" s="34"/>
-    </row>
-    <row r="165" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B165" s="34"/>
-      <c r="C165" s="36"/>
+      <c r="G164" s="32"/>
+      <c r="H164" s="32"/>
+    </row>
+    <row r="165" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B165" s="32"/>
+      <c r="C165" s="32"/>
       <c r="D165" s="34"/>
-      <c r="E165" s="36"/>
+      <c r="E165" s="32"/>
       <c r="F165" s="34"/>
-      <c r="G165" s="34"/>
-    </row>
-    <row r="166" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B166" s="34"/>
-      <c r="C166" s="36"/>
+      <c r="G165" s="32"/>
+      <c r="H165" s="32"/>
+    </row>
+    <row r="166" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B166" s="32"/>
+      <c r="C166" s="32"/>
       <c r="D166" s="34"/>
-      <c r="E166" s="36"/>
+      <c r="E166" s="32"/>
       <c r="F166" s="34"/>
-      <c r="G166" s="34"/>
-    </row>
-    <row r="167" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B167" s="34"/>
-      <c r="C167" s="36"/>
+      <c r="G166" s="32"/>
+      <c r="H166" s="32"/>
+    </row>
+    <row r="167" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B167" s="32"/>
+      <c r="C167" s="32"/>
       <c r="D167" s="34"/>
-      <c r="E167" s="36"/>
+      <c r="E167" s="32"/>
       <c r="F167" s="34"/>
-      <c r="G167" s="34"/>
-    </row>
-    <row r="168" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="34"/>
-      <c r="C168" s="36"/>
+      <c r="G167" s="32"/>
+      <c r="H167" s="32"/>
+    </row>
+    <row r="168" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B168" s="32"/>
+      <c r="C168" s="32"/>
       <c r="D168" s="34"/>
-      <c r="E168" s="36"/>
+      <c r="E168" s="32"/>
       <c r="F168" s="34"/>
-      <c r="G168" s="34"/>
-    </row>
-    <row r="169" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B169" s="34"/>
-      <c r="C169" s="36"/>
+      <c r="G168" s="32"/>
+      <c r="H168" s="32"/>
+    </row>
+    <row r="169" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B169" s="32"/>
+      <c r="C169" s="32"/>
       <c r="D169" s="34"/>
-      <c r="E169" s="36"/>
+      <c r="E169" s="32"/>
       <c r="F169" s="34"/>
-      <c r="G169" s="34"/>
-    </row>
-    <row r="170" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B170" s="34"/>
-      <c r="C170" s="36"/>
+      <c r="G169" s="32"/>
+      <c r="H169" s="32"/>
+    </row>
+    <row r="170" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B170" s="32"/>
+      <c r="C170" s="32"/>
       <c r="D170" s="34"/>
-      <c r="E170" s="36"/>
+      <c r="E170" s="32"/>
       <c r="F170" s="34"/>
-      <c r="G170" s="34"/>
-    </row>
-    <row r="171" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B171" s="34"/>
-      <c r="C171" s="36"/>
+      <c r="G170" s="32"/>
+      <c r="H170" s="32"/>
+    </row>
+    <row r="171" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B171" s="32"/>
+      <c r="C171" s="32"/>
       <c r="D171" s="34"/>
-      <c r="E171" s="36"/>
+      <c r="E171" s="32"/>
       <c r="F171" s="34"/>
-      <c r="G171" s="34"/>
-    </row>
-    <row r="172" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B172" s="34"/>
-      <c r="C172" s="36"/>
+      <c r="G171" s="32"/>
+      <c r="H171" s="32"/>
+    </row>
+    <row r="172" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B172" s="32"/>
+      <c r="C172" s="32"/>
       <c r="D172" s="34"/>
-      <c r="E172" s="36"/>
+      <c r="E172" s="32"/>
       <c r="F172" s="34"/>
-      <c r="G172" s="34"/>
-    </row>
-    <row r="173" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B173" s="34"/>
-      <c r="C173" s="36"/>
+      <c r="G172" s="32"/>
+      <c r="H172" s="32"/>
+    </row>
+    <row r="173" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B173" s="32"/>
+      <c r="C173" s="32"/>
       <c r="D173" s="34"/>
-      <c r="E173" s="36"/>
+      <c r="E173" s="32"/>
       <c r="F173" s="34"/>
-      <c r="G173" s="34"/>
-    </row>
-    <row r="174" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B174" s="34"/>
-      <c r="C174" s="36"/>
+      <c r="G173" s="32"/>
+      <c r="H173" s="32"/>
+    </row>
+    <row r="174" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B174" s="32"/>
+      <c r="C174" s="32"/>
       <c r="D174" s="34"/>
-      <c r="E174" s="36"/>
+      <c r="E174" s="32"/>
       <c r="F174" s="34"/>
-      <c r="G174" s="34"/>
-    </row>
-    <row r="175" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B175" s="34"/>
-      <c r="C175" s="36"/>
+      <c r="G174" s="32"/>
+      <c r="H174" s="32"/>
+    </row>
+    <row r="175" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B175" s="32"/>
+      <c r="C175" s="32"/>
       <c r="D175" s="34"/>
-      <c r="E175" s="36"/>
+      <c r="E175" s="32"/>
       <c r="F175" s="34"/>
-      <c r="G175" s="34"/>
-    </row>
-    <row r="176" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B176" s="34"/>
-      <c r="C176" s="36"/>
+      <c r="G175" s="32"/>
+      <c r="H175" s="32"/>
+    </row>
+    <row r="176" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B176" s="32"/>
+      <c r="C176" s="32"/>
       <c r="D176" s="34"/>
-      <c r="E176" s="36"/>
+      <c r="E176" s="32"/>
       <c r="F176" s="34"/>
-      <c r="G176" s="34"/>
-    </row>
-    <row r="177" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B177" s="34"/>
-      <c r="C177" s="36"/>
+      <c r="G176" s="32"/>
+      <c r="H176" s="32"/>
+    </row>
+    <row r="177" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B177" s="32"/>
+      <c r="C177" s="32"/>
       <c r="D177" s="34"/>
-      <c r="E177" s="36"/>
+      <c r="E177" s="32"/>
       <c r="F177" s="34"/>
-      <c r="G177" s="34"/>
-    </row>
-    <row r="178" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B178" s="34"/>
-      <c r="C178" s="36"/>
+      <c r="G177" s="32"/>
+      <c r="H177" s="32"/>
+    </row>
+    <row r="178" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B178" s="32"/>
+      <c r="C178" s="32"/>
       <c r="D178" s="34"/>
-      <c r="E178" s="36"/>
+      <c r="E178" s="32"/>
       <c r="F178" s="34"/>
-      <c r="G178" s="34"/>
-    </row>
-    <row r="179" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B179" s="34"/>
-      <c r="C179" s="36"/>
+      <c r="G178" s="32"/>
+      <c r="H178" s="32"/>
+    </row>
+    <row r="179" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B179" s="32"/>
+      <c r="C179" s="32"/>
       <c r="D179" s="34"/>
-      <c r="E179" s="36"/>
+      <c r="E179" s="32"/>
       <c r="F179" s="34"/>
-      <c r="G179" s="34"/>
-    </row>
-    <row r="180" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B180" s="34"/>
-      <c r="C180" s="36"/>
+      <c r="G179" s="32"/>
+      <c r="H179" s="32"/>
+    </row>
+    <row r="180" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B180" s="32"/>
+      <c r="C180" s="32"/>
       <c r="D180" s="34"/>
-      <c r="E180" s="36"/>
+      <c r="E180" s="32"/>
       <c r="F180" s="34"/>
-      <c r="G180" s="34"/>
-    </row>
-    <row r="181" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B181" s="34"/>
-      <c r="C181" s="36"/>
+      <c r="G180" s="32"/>
+      <c r="H180" s="32"/>
+    </row>
+    <row r="181" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B181" s="32"/>
+      <c r="C181" s="32"/>
       <c r="D181" s="34"/>
-      <c r="E181" s="36"/>
+      <c r="E181" s="32"/>
       <c r="F181" s="34"/>
-      <c r="G181" s="34"/>
-    </row>
-    <row r="182" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B182" s="34"/>
-      <c r="C182" s="36"/>
+      <c r="G181" s="32"/>
+      <c r="H181" s="32"/>
+    </row>
+    <row r="182" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B182" s="32"/>
+      <c r="C182" s="32"/>
       <c r="D182" s="34"/>
-      <c r="E182" s="36"/>
+      <c r="E182" s="32"/>
       <c r="F182" s="34"/>
-      <c r="G182" s="34"/>
-    </row>
-    <row r="183" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B183" s="34"/>
-      <c r="C183" s="36"/>
+      <c r="G182" s="32"/>
+      <c r="H182" s="32"/>
+    </row>
+    <row r="183" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B183" s="32"/>
+      <c r="C183" s="32"/>
       <c r="D183" s="34"/>
-      <c r="E183" s="36"/>
+      <c r="E183" s="32"/>
       <c r="F183" s="34"/>
-      <c r="G183" s="34"/>
-    </row>
-    <row r="184" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B184" s="34"/>
-      <c r="C184" s="36"/>
+      <c r="G183" s="32"/>
+      <c r="H183" s="32"/>
+    </row>
+    <row r="184" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B184" s="32"/>
+      <c r="C184" s="32"/>
       <c r="D184" s="34"/>
-      <c r="E184" s="36"/>
+      <c r="E184" s="32"/>
       <c r="F184" s="34"/>
-      <c r="G184" s="34"/>
-    </row>
-    <row r="185" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B185" s="34"/>
-      <c r="C185" s="36"/>
+      <c r="G184" s="32"/>
+      <c r="H184" s="32"/>
+    </row>
+    <row r="185" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B185" s="32"/>
+      <c r="C185" s="32"/>
       <c r="D185" s="34"/>
-      <c r="E185" s="36"/>
+      <c r="E185" s="32"/>
       <c r="F185" s="34"/>
-      <c r="G185" s="34"/>
-    </row>
-    <row r="186" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B186" s="34"/>
-      <c r="C186" s="36"/>
+      <c r="G185" s="32"/>
+      <c r="H185" s="32"/>
+    </row>
+    <row r="186" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B186" s="32"/>
+      <c r="C186" s="32"/>
       <c r="D186" s="34"/>
-      <c r="E186" s="36"/>
+      <c r="E186" s="32"/>
       <c r="F186" s="34"/>
-      <c r="G186" s="34"/>
-    </row>
-    <row r="187" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B187" s="34"/>
-      <c r="C187" s="36"/>
+      <c r="G186" s="32"/>
+      <c r="H186" s="32"/>
+    </row>
+    <row r="187" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B187" s="32"/>
+      <c r="C187" s="32"/>
       <c r="D187" s="34"/>
-      <c r="E187" s="36"/>
+      <c r="E187" s="32"/>
       <c r="F187" s="34"/>
-      <c r="G187" s="34"/>
-    </row>
-    <row r="188" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B188" s="34"/>
-      <c r="C188" s="36"/>
+      <c r="G187" s="32"/>
+      <c r="H187" s="32"/>
+    </row>
+    <row r="188" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B188" s="32"/>
+      <c r="C188" s="32"/>
       <c r="D188" s="34"/>
-      <c r="E188" s="36"/>
+      <c r="E188" s="32"/>
       <c r="F188" s="34"/>
-      <c r="G188" s="34"/>
-    </row>
-    <row r="189" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B189" s="34"/>
-      <c r="C189" s="36"/>
+      <c r="G188" s="32"/>
+      <c r="H188" s="32"/>
+    </row>
+    <row r="189" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B189" s="32"/>
+      <c r="C189" s="32"/>
       <c r="D189" s="34"/>
-      <c r="E189" s="36"/>
+      <c r="E189" s="32"/>
       <c r="F189" s="34"/>
-      <c r="G189" s="34"/>
-    </row>
-    <row r="190" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B190" s="34"/>
-      <c r="C190" s="36"/>
+      <c r="G189" s="32"/>
+      <c r="H189" s="32"/>
+    </row>
+    <row r="190" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B190" s="32"/>
+      <c r="C190" s="32"/>
       <c r="D190" s="34"/>
-      <c r="E190" s="36"/>
+      <c r="E190" s="32"/>
       <c r="F190" s="34"/>
-      <c r="G190" s="34"/>
-    </row>
-    <row r="191" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B191" s="34"/>
-      <c r="C191" s="36"/>
+      <c r="G190" s="32"/>
+      <c r="H190" s="32"/>
+    </row>
+    <row r="191" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B191" s="32"/>
+      <c r="C191" s="32"/>
       <c r="D191" s="34"/>
-      <c r="E191" s="36"/>
+      <c r="E191" s="32"/>
       <c r="F191" s="34"/>
-      <c r="G191" s="34"/>
-    </row>
-    <row r="192" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B192" s="34"/>
-      <c r="C192" s="36"/>
+      <c r="G191" s="32"/>
+      <c r="H191" s="32"/>
+    </row>
+    <row r="192" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B192" s="32"/>
+      <c r="C192" s="32"/>
       <c r="D192" s="34"/>
-      <c r="E192" s="36"/>
+      <c r="E192" s="32"/>
       <c r="F192" s="34"/>
-      <c r="G192" s="34"/>
-    </row>
-    <row r="193" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B193" s="34"/>
-      <c r="C193" s="36"/>
+      <c r="G192" s="32"/>
+      <c r="H192" s="32"/>
+    </row>
+    <row r="193" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B193" s="32"/>
+      <c r="C193" s="32"/>
       <c r="D193" s="34"/>
-      <c r="E193" s="36"/>
+      <c r="E193" s="32"/>
       <c r="F193" s="34"/>
-      <c r="G193" s="34"/>
-    </row>
-    <row r="194" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B194" s="34"/>
-      <c r="C194" s="36"/>
+      <c r="G193" s="32"/>
+      <c r="H193" s="32"/>
+    </row>
+    <row r="194" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B194" s="32"/>
+      <c r="C194" s="32"/>
       <c r="D194" s="34"/>
-      <c r="E194" s="36"/>
+      <c r="E194" s="32"/>
       <c r="F194" s="34"/>
-      <c r="G194" s="34"/>
-    </row>
-    <row r="195" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B195" s="34"/>
-      <c r="C195" s="36"/>
+      <c r="G194" s="32"/>
+      <c r="H194" s="32"/>
+    </row>
+    <row r="195" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B195" s="32"/>
+      <c r="C195" s="32"/>
       <c r="D195" s="34"/>
-      <c r="E195" s="36"/>
+      <c r="E195" s="32"/>
       <c r="F195" s="34"/>
-      <c r="G195" s="34"/>
-    </row>
-    <row r="196" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B196" s="34"/>
-      <c r="C196" s="36"/>
+      <c r="G195" s="32"/>
+      <c r="H195" s="32"/>
+    </row>
+    <row r="196" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B196" s="32"/>
+      <c r="C196" s="32"/>
       <c r="D196" s="34"/>
-      <c r="E196" s="36"/>
+      <c r="E196" s="32"/>
       <c r="F196" s="34"/>
-      <c r="G196" s="34"/>
-    </row>
-    <row r="197" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B197" s="34"/>
-      <c r="C197" s="36"/>
+      <c r="G196" s="32"/>
+      <c r="H196" s="32"/>
+    </row>
+    <row r="197" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B197" s="32"/>
+      <c r="C197" s="32"/>
       <c r="D197" s="34"/>
-      <c r="E197" s="36"/>
+      <c r="E197" s="32"/>
       <c r="F197" s="34"/>
-      <c r="G197" s="34"/>
-    </row>
-    <row r="198" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B198" s="34"/>
-      <c r="C198" s="36"/>
+      <c r="G197" s="32"/>
+      <c r="H197" s="32"/>
+    </row>
+    <row r="198" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B198" s="32"/>
+      <c r="C198" s="32"/>
       <c r="D198" s="34"/>
-      <c r="E198" s="36"/>
+      <c r="E198" s="32"/>
       <c r="F198" s="34"/>
-      <c r="G198" s="34"/>
-    </row>
-    <row r="199" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B199" s="34"/>
-      <c r="C199" s="36"/>
+      <c r="G198" s="32"/>
+      <c r="H198" s="32"/>
+    </row>
+    <row r="199" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B199" s="32"/>
+      <c r="C199" s="32"/>
       <c r="D199" s="34"/>
-      <c r="E199" s="36"/>
+      <c r="E199" s="32"/>
       <c r="F199" s="34"/>
-      <c r="G199" s="34"/>
-    </row>
-    <row r="200" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B200" s="34"/>
-      <c r="C200" s="36"/>
+      <c r="G199" s="32"/>
+      <c r="H199" s="32"/>
+    </row>
+    <row r="200" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B200" s="32"/>
+      <c r="C200" s="32"/>
       <c r="D200" s="34"/>
-      <c r="E200" s="36"/>
+      <c r="E200" s="32"/>
       <c r="F200" s="34"/>
-      <c r="G200" s="34"/>
-    </row>
-    <row r="201" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B201" s="34"/>
-      <c r="C201" s="36"/>
+      <c r="G200" s="32"/>
+      <c r="H200" s="32"/>
+    </row>
+    <row r="201" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B201" s="32"/>
+      <c r="C201" s="32"/>
       <c r="D201" s="34"/>
-      <c r="E201" s="36"/>
+      <c r="E201" s="32"/>
       <c r="F201" s="34"/>
-      <c r="G201" s="34"/>
-    </row>
-    <row r="202" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B202" s="34"/>
-      <c r="C202" s="36"/>
+      <c r="G201" s="32"/>
+      <c r="H201" s="32"/>
+    </row>
+    <row r="202" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B202" s="32"/>
+      <c r="C202" s="32"/>
       <c r="D202" s="34"/>
-      <c r="E202" s="36"/>
+      <c r="E202" s="32"/>
       <c r="F202" s="34"/>
-      <c r="G202" s="34"/>
-    </row>
-    <row r="203" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B203" s="34"/>
-      <c r="C203" s="36"/>
+      <c r="G202" s="32"/>
+      <c r="H202" s="32"/>
+    </row>
+    <row r="203" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B203" s="32"/>
+      <c r="C203" s="32"/>
       <c r="D203" s="34"/>
-      <c r="E203" s="36"/>
+      <c r="E203" s="32"/>
       <c r="F203" s="34"/>
-      <c r="G203" s="34"/>
-    </row>
-    <row r="204" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B204" s="34"/>
-      <c r="C204" s="36"/>
+      <c r="G203" s="32"/>
+      <c r="H203" s="32"/>
+    </row>
+    <row r="204" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B204" s="32"/>
+      <c r="C204" s="32"/>
       <c r="D204" s="34"/>
-      <c r="E204" s="36"/>
+      <c r="E204" s="32"/>
       <c r="F204" s="34"/>
-      <c r="G204" s="34"/>
-    </row>
-    <row r="205" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B205" s="34"/>
-      <c r="C205" s="36"/>
+      <c r="G204" s="32"/>
+      <c r="H204" s="32"/>
+    </row>
+    <row r="205" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B205" s="32"/>
+      <c r="C205" s="32"/>
       <c r="D205" s="34"/>
-      <c r="E205" s="36"/>
+      <c r="E205" s="32"/>
       <c r="F205" s="34"/>
-      <c r="G205" s="34"/>
-    </row>
-    <row r="206" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B206" s="34"/>
-      <c r="C206" s="36"/>
+      <c r="G205" s="32"/>
+      <c r="H205" s="32"/>
+    </row>
+    <row r="206" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B206" s="32"/>
+      <c r="C206" s="32"/>
       <c r="D206" s="34"/>
-      <c r="E206" s="36"/>
+      <c r="E206" s="32"/>
       <c r="F206" s="34"/>
-      <c r="G206" s="34"/>
-    </row>
-    <row r="207" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B207" s="34"/>
-      <c r="C207" s="36"/>
+      <c r="G206" s="32"/>
+      <c r="H206" s="32"/>
+    </row>
+    <row r="207" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B207" s="32"/>
+      <c r="C207" s="32"/>
       <c r="D207" s="34"/>
-      <c r="E207" s="36"/>
+      <c r="E207" s="32"/>
       <c r="F207" s="34"/>
-      <c r="G207" s="34"/>
-    </row>
-    <row r="208" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B208" s="34"/>
-      <c r="C208" s="36"/>
+      <c r="G207" s="32"/>
+      <c r="H207" s="32"/>
+    </row>
+    <row r="208" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B208" s="32"/>
+      <c r="C208" s="32"/>
       <c r="D208" s="34"/>
-      <c r="E208" s="36"/>
+      <c r="E208" s="32"/>
       <c r="F208" s="34"/>
-      <c r="G208" s="34"/>
-    </row>
-    <row r="209" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B209" s="34"/>
-      <c r="C209" s="36"/>
+      <c r="G208" s="32"/>
+      <c r="H208" s="32"/>
+    </row>
+    <row r="209" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B209" s="32"/>
+      <c r="C209" s="32"/>
       <c r="D209" s="34"/>
-      <c r="E209" s="36"/>
+      <c r="E209" s="32"/>
       <c r="F209" s="34"/>
-      <c r="G209" s="34"/>
-    </row>
-    <row r="210" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B210" s="34"/>
-      <c r="C210" s="36"/>
+      <c r="G209" s="32"/>
+      <c r="H209" s="32"/>
+    </row>
+    <row r="210" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B210" s="32"/>
+      <c r="C210" s="32"/>
       <c r="D210" s="34"/>
-      <c r="E210" s="36"/>
+      <c r="E210" s="32"/>
       <c r="F210" s="34"/>
-      <c r="G210" s="34"/>
-    </row>
-    <row r="211" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B211" s="34"/>
-      <c r="C211" s="36"/>
+      <c r="G210" s="32"/>
+      <c r="H210" s="32"/>
+    </row>
+    <row r="211" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B211" s="32"/>
+      <c r="C211" s="32"/>
       <c r="D211" s="34"/>
-      <c r="E211" s="36"/>
+      <c r="E211" s="32"/>
       <c r="F211" s="34"/>
-      <c r="G211" s="34"/>
-    </row>
-    <row r="212" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B212" s="34"/>
-      <c r="C212" s="36"/>
+      <c r="G211" s="32"/>
+      <c r="H211" s="32"/>
+    </row>
+    <row r="212" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B212" s="32"/>
+      <c r="C212" s="32"/>
       <c r="D212" s="34"/>
-      <c r="E212" s="36"/>
+      <c r="E212" s="32"/>
       <c r="F212" s="34"/>
-      <c r="G212" s="34"/>
-    </row>
-    <row r="213" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B213" s="34"/>
-      <c r="C213" s="36"/>
+      <c r="G212" s="32"/>
+      <c r="H212" s="32"/>
+    </row>
+    <row r="213" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B213" s="32"/>
+      <c r="C213" s="32"/>
       <c r="D213" s="34"/>
-      <c r="E213" s="36"/>
+      <c r="E213" s="32"/>
       <c r="F213" s="34"/>
-      <c r="G213" s="34"/>
-    </row>
-    <row r="214" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B214" s="34"/>
-      <c r="C214" s="36"/>
+      <c r="G213" s="32"/>
+      <c r="H213" s="32"/>
+    </row>
+    <row r="214" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B214" s="32"/>
+      <c r="C214" s="32"/>
       <c r="D214" s="34"/>
-      <c r="E214" s="36"/>
+      <c r="E214" s="32"/>
       <c r="F214" s="34"/>
-      <c r="G214" s="34"/>
-    </row>
-    <row r="215" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B215" s="34"/>
-      <c r="C215" s="36"/>
+      <c r="G214" s="32"/>
+      <c r="H214" s="32"/>
+    </row>
+    <row r="215" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B215" s="32"/>
+      <c r="C215" s="32"/>
       <c r="D215" s="34"/>
-      <c r="E215" s="36"/>
+      <c r="E215" s="32"/>
       <c r="F215" s="34"/>
-      <c r="G215" s="34"/>
-    </row>
-    <row r="216" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B216" s="34"/>
-      <c r="C216" s="36"/>
+      <c r="G215" s="32"/>
+      <c r="H215" s="32"/>
+    </row>
+    <row r="216" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B216" s="32"/>
+      <c r="C216" s="32"/>
       <c r="D216" s="34"/>
-      <c r="E216" s="36"/>
+      <c r="E216" s="32"/>
       <c r="F216" s="34"/>
-      <c r="G216" s="34"/>
-    </row>
-    <row r="217" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B217" s="34"/>
-      <c r="C217" s="36"/>
+      <c r="G216" s="32"/>
+      <c r="H216" s="32"/>
+    </row>
+    <row r="217" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B217" s="32"/>
+      <c r="C217" s="32"/>
       <c r="D217" s="34"/>
-      <c r="E217" s="36"/>
+      <c r="E217" s="32"/>
       <c r="F217" s="34"/>
-      <c r="G217" s="34"/>
-    </row>
-    <row r="218" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B218" s="34"/>
-      <c r="C218" s="36"/>
+      <c r="G217" s="32"/>
+      <c r="H217" s="32"/>
+    </row>
+    <row r="218" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B218" s="32"/>
+      <c r="C218" s="32"/>
       <c r="D218" s="34"/>
-      <c r="E218" s="36"/>
+      <c r="E218" s="32"/>
       <c r="F218" s="34"/>
-      <c r="G218" s="34"/>
-    </row>
-    <row r="219" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B219" s="34"/>
-      <c r="C219" s="36"/>
+      <c r="G218" s="32"/>
+      <c r="H218" s="32"/>
+    </row>
+    <row r="219" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B219" s="32"/>
+      <c r="C219" s="32"/>
       <c r="D219" s="34"/>
-      <c r="E219" s="36"/>
+      <c r="E219" s="32"/>
       <c r="F219" s="34"/>
-      <c r="G219" s="34"/>
-    </row>
-    <row r="220" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B220" s="34"/>
-      <c r="C220" s="36"/>
+      <c r="G219" s="32"/>
+      <c r="H219" s="32"/>
+    </row>
+    <row r="220" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B220" s="32"/>
+      <c r="C220" s="32"/>
       <c r="D220" s="34"/>
-      <c r="E220" s="36"/>
+      <c r="E220" s="32"/>
       <c r="F220" s="34"/>
-      <c r="G220" s="34"/>
-    </row>
-    <row r="221" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B221" s="34"/>
-      <c r="C221" s="36"/>
+      <c r="G220" s="32"/>
+      <c r="H220" s="32"/>
+    </row>
+    <row r="221" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B221" s="32"/>
+      <c r="C221" s="32"/>
       <c r="D221" s="34"/>
-      <c r="E221" s="36"/>
+      <c r="E221" s="32"/>
       <c r="F221" s="34"/>
-      <c r="G221" s="34"/>
-    </row>
-    <row r="222" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B222" s="34"/>
-      <c r="C222" s="36"/>
+      <c r="G221" s="32"/>
+      <c r="H221" s="32"/>
+    </row>
+    <row r="222" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B222" s="32"/>
+      <c r="C222" s="32"/>
       <c r="D222" s="34"/>
-      <c r="E222" s="36"/>
+      <c r="E222" s="32"/>
       <c r="F222" s="34"/>
-      <c r="G222" s="34"/>
-    </row>
-    <row r="223" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B223" s="34"/>
-      <c r="C223" s="36"/>
+      <c r="G222" s="32"/>
+      <c r="H222" s="32"/>
+    </row>
+    <row r="223" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B223" s="32"/>
+      <c r="C223" s="32"/>
       <c r="D223" s="34"/>
-      <c r="E223" s="36"/>
+      <c r="E223" s="32"/>
       <c r="F223" s="34"/>
-      <c r="G223" s="34"/>
-    </row>
-    <row r="224" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B224" s="34"/>
-      <c r="C224" s="36"/>
+      <c r="G223" s="32"/>
+      <c r="H223" s="32"/>
+    </row>
+    <row r="224" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B224" s="32"/>
+      <c r="C224" s="32"/>
       <c r="D224" s="34"/>
-      <c r="E224" s="36"/>
+      <c r="E224" s="32"/>
       <c r="F224" s="34"/>
-      <c r="G224" s="34"/>
-    </row>
-    <row r="225" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B225" s="34"/>
-      <c r="C225" s="36"/>
+      <c r="G224" s="32"/>
+      <c r="H224" s="32"/>
+    </row>
+    <row r="225" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B225" s="32"/>
+      <c r="C225" s="32"/>
       <c r="D225" s="34"/>
-      <c r="E225" s="36"/>
+      <c r="E225" s="32"/>
       <c r="F225" s="34"/>
-      <c r="G225" s="34"/>
-    </row>
-    <row r="226" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B226" s="34"/>
-      <c r="C226" s="36"/>
+      <c r="G225" s="32"/>
+      <c r="H225" s="32"/>
+    </row>
+    <row r="226" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B226" s="32"/>
+      <c r="C226" s="32"/>
       <c r="D226" s="34"/>
-      <c r="E226" s="36"/>
+      <c r="E226" s="32"/>
       <c r="F226" s="34"/>
-      <c r="G226" s="34"/>
-    </row>
-    <row r="227" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B227" s="34"/>
-      <c r="C227" s="36"/>
+      <c r="G226" s="32"/>
+      <c r="H226" s="32"/>
+    </row>
+    <row r="227" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B227" s="32"/>
+      <c r="C227" s="32"/>
       <c r="D227" s="34"/>
-      <c r="E227" s="36"/>
+      <c r="E227" s="32"/>
       <c r="F227" s="34"/>
-      <c r="G227" s="34"/>
-    </row>
-    <row r="228" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B228" s="34"/>
-      <c r="C228" s="36"/>
+      <c r="G227" s="32"/>
+      <c r="H227" s="32"/>
+    </row>
+    <row r="228" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B228" s="32"/>
+      <c r="C228" s="32"/>
       <c r="D228" s="34"/>
-      <c r="E228" s="36"/>
+      <c r="E228" s="32"/>
       <c r="F228" s="34"/>
-      <c r="G228" s="34"/>
-    </row>
-    <row r="229" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B229" s="34"/>
-      <c r="C229" s="36"/>
+      <c r="G228" s="32"/>
+      <c r="H228" s="32"/>
+    </row>
+    <row r="229" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B229" s="32"/>
+      <c r="C229" s="32"/>
       <c r="D229" s="34"/>
-      <c r="E229" s="36"/>
+      <c r="E229" s="32"/>
       <c r="F229" s="34"/>
-      <c r="G229" s="34"/>
-    </row>
-    <row r="230" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B230" s="34"/>
-      <c r="C230" s="36"/>
+      <c r="G229" s="32"/>
+      <c r="H229" s="32"/>
+    </row>
+    <row r="230" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B230" s="32"/>
+      <c r="C230" s="32"/>
       <c r="D230" s="34"/>
-      <c r="E230" s="36"/>
+      <c r="E230" s="32"/>
       <c r="F230" s="34"/>
-      <c r="G230" s="34"/>
-    </row>
-    <row r="231" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B231" s="34"/>
-      <c r="C231" s="36"/>
+      <c r="G230" s="32"/>
+      <c r="H230" s="32"/>
+    </row>
+    <row r="231" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B231" s="32"/>
+      <c r="C231" s="32"/>
       <c r="D231" s="34"/>
-      <c r="E231" s="36"/>
+      <c r="E231" s="32"/>
       <c r="F231" s="34"/>
-      <c r="G231" s="34"/>
-    </row>
-    <row r="232" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B232" s="34"/>
-      <c r="C232" s="36"/>
+      <c r="G231" s="32"/>
+      <c r="H231" s="32"/>
+    </row>
+    <row r="232" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B232" s="32"/>
+      <c r="C232" s="32"/>
       <c r="D232" s="34"/>
-      <c r="E232" s="36"/>
+      <c r="E232" s="32"/>
       <c r="F232" s="34"/>
-      <c r="G232" s="34"/>
-    </row>
-    <row r="233" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B233" s="34"/>
-      <c r="C233" s="36"/>
+      <c r="G232" s="32"/>
+      <c r="H232" s="32"/>
+    </row>
+    <row r="233" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B233" s="32"/>
+      <c r="C233" s="32"/>
       <c r="D233" s="34"/>
-      <c r="E233" s="36"/>
+      <c r="E233" s="32"/>
       <c r="F233" s="34"/>
-      <c r="G233" s="34"/>
-    </row>
-    <row r="234" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B234" s="34"/>
-      <c r="C234" s="36"/>
+      <c r="G233" s="32"/>
+      <c r="H233" s="32"/>
+    </row>
+    <row r="234" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B234" s="32"/>
+      <c r="C234" s="32"/>
       <c r="D234" s="34"/>
-      <c r="E234" s="36"/>
+      <c r="E234" s="32"/>
       <c r="F234" s="34"/>
-      <c r="G234" s="34"/>
-    </row>
-    <row r="235" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B235" s="34"/>
-      <c r="C235" s="36"/>
+      <c r="G234" s="32"/>
+      <c r="H234" s="32"/>
+    </row>
+    <row r="235" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B235" s="32"/>
+      <c r="C235" s="32"/>
       <c r="D235" s="34"/>
-      <c r="E235" s="36"/>
+      <c r="E235" s="32"/>
       <c r="F235" s="34"/>
-      <c r="G235" s="34"/>
-    </row>
-    <row r="236" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B236" s="34"/>
-      <c r="C236" s="36"/>
+      <c r="G235" s="32"/>
+      <c r="H235" s="32"/>
+    </row>
+    <row r="236" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B236" s="32"/>
+      <c r="C236" s="32"/>
       <c r="D236" s="34"/>
-      <c r="E236" s="36"/>
+      <c r="E236" s="32"/>
       <c r="F236" s="34"/>
-      <c r="G236" s="34"/>
-    </row>
-    <row r="237" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B237" s="34"/>
-      <c r="C237" s="36"/>
+      <c r="G236" s="32"/>
+      <c r="H236" s="32"/>
+    </row>
+    <row r="237" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B237" s="32"/>
+      <c r="C237" s="32"/>
       <c r="D237" s="34"/>
-      <c r="E237" s="36"/>
+      <c r="E237" s="32"/>
       <c r="F237" s="34"/>
-      <c r="G237" s="34"/>
-    </row>
-    <row r="238" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B238" s="34"/>
-      <c r="C238" s="36"/>
+      <c r="G237" s="32"/>
+      <c r="H237" s="32"/>
+    </row>
+    <row r="238" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B238" s="32"/>
+      <c r="C238" s="32"/>
       <c r="D238" s="34"/>
-      <c r="E238" s="36"/>
+      <c r="E238" s="32"/>
       <c r="F238" s="34"/>
-      <c r="G238" s="34"/>
-    </row>
-    <row r="239" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B239" s="34"/>
-      <c r="C239" s="36"/>
+      <c r="G238" s="32"/>
+      <c r="H238" s="32"/>
+    </row>
+    <row r="239" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B239" s="32"/>
+      <c r="C239" s="32"/>
       <c r="D239" s="34"/>
-      <c r="E239" s="36"/>
+      <c r="E239" s="32"/>
       <c r="F239" s="34"/>
-      <c r="G239" s="34"/>
-    </row>
-    <row r="240" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B240" s="34"/>
-      <c r="C240" s="36"/>
+      <c r="G239" s="32"/>
+      <c r="H239" s="32"/>
+    </row>
+    <row r="240" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B240" s="32"/>
+      <c r="C240" s="32"/>
       <c r="D240" s="34"/>
-      <c r="E240" s="36"/>
+      <c r="E240" s="32"/>
       <c r="F240" s="34"/>
-      <c r="G240" s="34"/>
-    </row>
-    <row r="241" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B241" s="34"/>
-      <c r="C241" s="36"/>
+      <c r="G240" s="32"/>
+      <c r="H240" s="32"/>
+    </row>
+    <row r="241" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B241" s="32"/>
+      <c r="C241" s="32"/>
       <c r="D241" s="34"/>
-      <c r="E241" s="36"/>
+      <c r="E241" s="32"/>
       <c r="F241" s="34"/>
-      <c r="G241" s="34"/>
-    </row>
-    <row r="242" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B242" s="34"/>
-      <c r="C242" s="36"/>
+      <c r="G241" s="32"/>
+      <c r="H241" s="32"/>
+    </row>
+    <row r="242" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B242" s="32"/>
+      <c r="C242" s="32"/>
       <c r="D242" s="34"/>
-      <c r="E242" s="36"/>
+      <c r="E242" s="32"/>
       <c r="F242" s="34"/>
-      <c r="G242" s="34"/>
-    </row>
-    <row r="243" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B243" s="34"/>
-      <c r="C243" s="36"/>
+      <c r="G242" s="32"/>
+      <c r="H242" s="32"/>
+    </row>
+    <row r="243" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B243" s="32"/>
+      <c r="C243" s="32"/>
       <c r="D243" s="34"/>
-      <c r="E243" s="36"/>
+      <c r="E243" s="32"/>
       <c r="F243" s="34"/>
-      <c r="G243" s="34"/>
-    </row>
-    <row r="244" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B244" s="34"/>
-      <c r="C244" s="36"/>
+      <c r="G243" s="32"/>
+      <c r="H243" s="32"/>
+    </row>
+    <row r="244" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B244" s="32"/>
+      <c r="C244" s="32"/>
       <c r="D244" s="34"/>
-      <c r="E244" s="36"/>
+      <c r="E244" s="32"/>
       <c r="F244" s="34"/>
-      <c r="G244" s="34"/>
-    </row>
-    <row r="245" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B245" s="34"/>
-      <c r="C245" s="36"/>
+      <c r="G244" s="32"/>
+      <c r="H244" s="32"/>
+    </row>
+    <row r="245" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B245" s="32"/>
+      <c r="C245" s="32"/>
       <c r="D245" s="34"/>
-      <c r="E245" s="36"/>
+      <c r="E245" s="32"/>
       <c r="F245" s="34"/>
-      <c r="G245" s="34"/>
-    </row>
-    <row r="246" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B246" s="34"/>
-      <c r="C246" s="36"/>
+      <c r="G245" s="32"/>
+      <c r="H245" s="32"/>
+    </row>
+    <row r="246" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B246" s="32"/>
+      <c r="C246" s="32"/>
       <c r="D246" s="34"/>
-      <c r="E246" s="36"/>
+      <c r="E246" s="32"/>
       <c r="F246" s="34"/>
-      <c r="G246" s="34"/>
-    </row>
-    <row r="247" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B247" s="34"/>
-      <c r="C247" s="36"/>
+      <c r="G246" s="32"/>
+      <c r="H246" s="32"/>
+    </row>
+    <row r="247" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B247" s="32"/>
+      <c r="C247" s="32"/>
       <c r="D247" s="34"/>
-      <c r="E247" s="36"/>
+      <c r="E247" s="32"/>
       <c r="F247" s="34"/>
-      <c r="G247" s="34"/>
-    </row>
-    <row r="248" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B248" s="34"/>
-      <c r="C248" s="36"/>
+      <c r="G247" s="32"/>
+      <c r="H247" s="32"/>
+    </row>
+    <row r="248" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B248" s="32"/>
+      <c r="C248" s="32"/>
       <c r="D248" s="34"/>
-      <c r="E248" s="36"/>
+      <c r="E248" s="32"/>
       <c r="F248" s="34"/>
-      <c r="G248" s="34"/>
-    </row>
-    <row r="249" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B249" s="34"/>
-      <c r="C249" s="36"/>
+      <c r="G248" s="32"/>
+      <c r="H248" s="32"/>
+    </row>
+    <row r="249" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B249" s="32"/>
+      <c r="C249" s="32"/>
       <c r="D249" s="34"/>
-      <c r="E249" s="36"/>
+      <c r="E249" s="32"/>
       <c r="F249" s="34"/>
-      <c r="G249" s="34"/>
-    </row>
-    <row r="250" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B250" s="34"/>
-      <c r="C250" s="36"/>
+      <c r="G249" s="32"/>
+      <c r="H249" s="32"/>
+    </row>
+    <row r="250" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B250" s="32"/>
+      <c r="C250" s="32"/>
       <c r="D250" s="34"/>
-      <c r="E250" s="36"/>
+      <c r="E250" s="32"/>
       <c r="F250" s="34"/>
-      <c r="G250" s="34"/>
-    </row>
-    <row r="251" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B251" s="34"/>
-      <c r="C251" s="36"/>
+      <c r="G250" s="32"/>
+      <c r="H250" s="32"/>
+    </row>
+    <row r="251" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B251" s="32"/>
+      <c r="C251" s="32"/>
       <c r="D251" s="34"/>
-      <c r="E251" s="36"/>
+      <c r="E251" s="32"/>
       <c r="F251" s="34"/>
-      <c r="G251" s="34"/>
-    </row>
-    <row r="252" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B252" s="34"/>
-      <c r="C252" s="36"/>
+      <c r="G251" s="32"/>
+      <c r="H251" s="32"/>
+    </row>
+    <row r="252" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B252" s="32"/>
+      <c r="C252" s="32"/>
       <c r="D252" s="34"/>
-      <c r="E252" s="36"/>
+      <c r="E252" s="32"/>
       <c r="F252" s="34"/>
-      <c r="G252" s="34"/>
-    </row>
-    <row r="253" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B253" s="34"/>
-      <c r="C253" s="36"/>
+      <c r="G252" s="32"/>
+      <c r="H252" s="32"/>
+    </row>
+    <row r="253" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B253" s="32"/>
+      <c r="C253" s="32"/>
       <c r="D253" s="34"/>
-      <c r="E253" s="36"/>
+      <c r="E253" s="32"/>
       <c r="F253" s="34"/>
-      <c r="G253" s="34"/>
-    </row>
-    <row r="254" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B254" s="34"/>
-      <c r="C254" s="36"/>
+      <c r="G253" s="32"/>
+      <c r="H253" s="32"/>
+    </row>
+    <row r="254" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B254" s="32"/>
+      <c r="C254" s="32"/>
       <c r="D254" s="34"/>
-      <c r="E254" s="36"/>
+      <c r="E254" s="32"/>
       <c r="F254" s="34"/>
-      <c r="G254" s="34"/>
-    </row>
-    <row r="255" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B255" s="34"/>
-      <c r="C255" s="36"/>
+      <c r="G254" s="32"/>
+      <c r="H254" s="32"/>
+    </row>
+    <row r="255" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B255" s="32"/>
+      <c r="C255" s="32"/>
       <c r="D255" s="34"/>
-      <c r="E255" s="36"/>
+      <c r="E255" s="32"/>
       <c r="F255" s="34"/>
-      <c r="G255" s="34"/>
-    </row>
-    <row r="256" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B256" s="34"/>
-      <c r="C256" s="36"/>
+      <c r="G255" s="32"/>
+      <c r="H255" s="32"/>
+    </row>
+    <row r="256" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B256" s="32"/>
+      <c r="C256" s="32"/>
       <c r="D256" s="34"/>
-      <c r="E256" s="36"/>
+      <c r="E256" s="32"/>
       <c r="F256" s="34"/>
-      <c r="G256" s="34"/>
-    </row>
-    <row r="257" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B257" s="34"/>
-      <c r="C257" s="36"/>
+      <c r="G256" s="32"/>
+      <c r="H256" s="32"/>
+    </row>
+    <row r="257" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B257" s="32"/>
+      <c r="C257" s="32"/>
       <c r="D257" s="34"/>
-      <c r="E257" s="36"/>
+      <c r="E257" s="32"/>
       <c r="F257" s="34"/>
-      <c r="G257" s="34"/>
-    </row>
-    <row r="258" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B258" s="34"/>
-      <c r="C258" s="36"/>
+      <c r="G257" s="32"/>
+      <c r="H257" s="32"/>
+    </row>
+    <row r="258" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B258" s="32"/>
+      <c r="C258" s="32"/>
       <c r="D258" s="34"/>
-      <c r="E258" s="36"/>
+      <c r="E258" s="32"/>
       <c r="F258" s="34"/>
-      <c r="G258" s="34"/>
-    </row>
-    <row r="259" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B259" s="34"/>
-      <c r="C259" s="36"/>
+      <c r="G258" s="32"/>
+      <c r="H258" s="32"/>
+    </row>
+    <row r="259" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B259" s="32"/>
+      <c r="C259" s="32"/>
       <c r="D259" s="34"/>
-      <c r="E259" s="36"/>
+      <c r="E259" s="32"/>
       <c r="F259" s="34"/>
-      <c r="G259" s="34"/>
-    </row>
-    <row r="260" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B260" s="34"/>
-      <c r="C260" s="36"/>
+      <c r="G259" s="32"/>
+      <c r="H259" s="32"/>
+    </row>
+    <row r="260" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B260" s="32"/>
+      <c r="C260" s="32"/>
       <c r="D260" s="34"/>
-      <c r="E260" s="36"/>
+      <c r="E260" s="32"/>
       <c r="F260" s="34"/>
-      <c r="G260" s="34"/>
-    </row>
-    <row r="261" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B261" s="34"/>
-      <c r="C261" s="36"/>
+      <c r="G260" s="32"/>
+      <c r="H260" s="32"/>
+    </row>
+    <row r="261" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B261" s="32"/>
+      <c r="C261" s="32"/>
       <c r="D261" s="34"/>
-      <c r="E261" s="36"/>
+      <c r="E261" s="32"/>
       <c r="F261" s="34"/>
-      <c r="G261" s="34"/>
-    </row>
-    <row r="262" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B262" s="34"/>
-      <c r="C262" s="36"/>
+      <c r="G261" s="32"/>
+      <c r="H261" s="32"/>
+    </row>
+    <row r="262" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B262" s="32"/>
+      <c r="C262" s="32"/>
       <c r="D262" s="34"/>
-      <c r="E262" s="36"/>
+      <c r="E262" s="32"/>
       <c r="F262" s="34"/>
-      <c r="G262" s="34"/>
-    </row>
-    <row r="263" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B263" s="34"/>
-      <c r="C263" s="36"/>
+      <c r="G262" s="32"/>
+      <c r="H262" s="32"/>
+    </row>
+    <row r="263" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B263" s="32"/>
+      <c r="C263" s="32"/>
       <c r="D263" s="34"/>
-      <c r="E263" s="36"/>
+      <c r="E263" s="32"/>
       <c r="F263" s="34"/>
-      <c r="G263" s="34"/>
-    </row>
-    <row r="264" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B264" s="34"/>
-      <c r="C264" s="36"/>
+      <c r="G263" s="32"/>
+      <c r="H263" s="32"/>
+    </row>
+    <row r="264" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B264" s="32"/>
+      <c r="C264" s="32"/>
       <c r="D264" s="34"/>
-      <c r="E264" s="36"/>
+      <c r="E264" s="32"/>
       <c r="F264" s="34"/>
-      <c r="G264" s="34"/>
-    </row>
-    <row r="265" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B265" s="34"/>
-      <c r="C265" s="36"/>
+      <c r="G264" s="32"/>
+      <c r="H264" s="32"/>
+    </row>
+    <row r="265" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B265" s="32"/>
+      <c r="C265" s="32"/>
       <c r="D265" s="34"/>
-      <c r="E265" s="36"/>
+      <c r="E265" s="32"/>
       <c r="F265" s="34"/>
-      <c r="G265" s="34"/>
-    </row>
-    <row r="266" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B266" s="34"/>
-      <c r="C266" s="36"/>
+      <c r="G265" s="32"/>
+      <c r="H265" s="32"/>
+    </row>
+    <row r="266" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B266" s="32"/>
+      <c r="C266" s="32"/>
       <c r="D266" s="34"/>
-      <c r="E266" s="36"/>
+      <c r="E266" s="32"/>
       <c r="F266" s="34"/>
-      <c r="G266" s="34"/>
-    </row>
-    <row r="267" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B267" s="34"/>
-      <c r="C267" s="36"/>
+      <c r="G266" s="32"/>
+      <c r="H266" s="32"/>
+    </row>
+    <row r="267" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B267" s="32"/>
+      <c r="C267" s="32"/>
       <c r="D267" s="34"/>
-      <c r="E267" s="36"/>
+      <c r="E267" s="32"/>
       <c r="F267" s="34"/>
-      <c r="G267" s="34"/>
-    </row>
-    <row r="268" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B268" s="34"/>
-      <c r="C268" s="36"/>
+      <c r="G267" s="32"/>
+      <c r="H267" s="32"/>
+    </row>
+    <row r="268" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B268" s="32"/>
+      <c r="C268" s="32"/>
       <c r="D268" s="34"/>
-      <c r="E268" s="36"/>
+      <c r="E268" s="32"/>
       <c r="F268" s="34"/>
-      <c r="G268" s="34"/>
-    </row>
-    <row r="269" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B269" s="34"/>
-      <c r="C269" s="36"/>
+      <c r="G268" s="32"/>
+      <c r="H268" s="32"/>
+    </row>
+    <row r="269" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B269" s="32"/>
+      <c r="C269" s="32"/>
       <c r="D269" s="34"/>
-      <c r="E269" s="36"/>
+      <c r="E269" s="32"/>
       <c r="F269" s="34"/>
-      <c r="G269" s="34"/>
-    </row>
-    <row r="270" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B270" s="34"/>
-      <c r="C270" s="36"/>
+      <c r="G269" s="32"/>
+      <c r="H269" s="32"/>
+    </row>
+    <row r="270" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B270" s="32"/>
+      <c r="C270" s="32"/>
       <c r="D270" s="34"/>
-      <c r="E270" s="36"/>
+      <c r="E270" s="32"/>
       <c r="F270" s="34"/>
-      <c r="G270" s="34"/>
-    </row>
-    <row r="271" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B271" s="34"/>
-      <c r="C271" s="36"/>
+      <c r="G270" s="32"/>
+      <c r="H270" s="32"/>
+    </row>
+    <row r="271" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B271" s="32"/>
+      <c r="C271" s="32"/>
       <c r="D271" s="34"/>
-      <c r="E271" s="36"/>
+      <c r="E271" s="32"/>
       <c r="F271" s="34"/>
-      <c r="G271" s="34"/>
-    </row>
-    <row r="272" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B272" s="34"/>
-      <c r="C272" s="36"/>
+      <c r="G271" s="32"/>
+      <c r="H271" s="32"/>
+    </row>
+    <row r="272" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B272" s="32"/>
+      <c r="C272" s="32"/>
       <c r="D272" s="34"/>
-      <c r="E272" s="36"/>
+      <c r="E272" s="32"/>
       <c r="F272" s="34"/>
-      <c r="G272" s="34"/>
-    </row>
-    <row r="273" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B273" s="34"/>
-      <c r="C273" s="36"/>
+      <c r="G272" s="32"/>
+      <c r="H272" s="32"/>
+    </row>
+    <row r="273" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B273" s="32"/>
+      <c r="C273" s="32"/>
       <c r="D273" s="34"/>
-      <c r="E273" s="36"/>
+      <c r="E273" s="32"/>
       <c r="F273" s="34"/>
-      <c r="G273" s="34"/>
-    </row>
-    <row r="274" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B274" s="34"/>
-      <c r="C274" s="36"/>
+      <c r="G273" s="32"/>
+      <c r="H273" s="32"/>
+    </row>
+    <row r="274" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B274" s="32"/>
+      <c r="C274" s="32"/>
       <c r="D274" s="34"/>
-      <c r="E274" s="36"/>
+      <c r="E274" s="32"/>
       <c r="F274" s="34"/>
-      <c r="G274" s="34"/>
-    </row>
-    <row r="275" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B275" s="34"/>
-      <c r="C275" s="36"/>
+      <c r="G274" s="32"/>
+      <c r="H274" s="32"/>
+    </row>
+    <row r="275" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B275" s="32"/>
+      <c r="C275" s="32"/>
       <c r="D275" s="34"/>
-      <c r="E275" s="36"/>
+      <c r="E275" s="32"/>
       <c r="F275" s="34"/>
-      <c r="G275" s="34"/>
-    </row>
-    <row r="276" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B276" s="34"/>
-      <c r="C276" s="36"/>
+      <c r="G275" s="32"/>
+      <c r="H275" s="32"/>
+    </row>
+    <row r="276" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B276" s="32"/>
+      <c r="C276" s="32"/>
       <c r="D276" s="34"/>
-      <c r="E276" s="36"/>
+      <c r="E276" s="32"/>
       <c r="F276" s="34"/>
-      <c r="G276" s="34"/>
-    </row>
-    <row r="277" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B277" s="34"/>
-      <c r="C277" s="36"/>
+      <c r="G276" s="32"/>
+      <c r="H276" s="32"/>
+    </row>
+    <row r="277" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B277" s="32"/>
+      <c r="C277" s="32"/>
       <c r="D277" s="34"/>
-      <c r="E277" s="36"/>
+      <c r="E277" s="32"/>
       <c r="F277" s="34"/>
-      <c r="G277" s="34"/>
-    </row>
-    <row r="278" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B278" s="34"/>
-      <c r="C278" s="36"/>
+      <c r="G277" s="32"/>
+      <c r="H277" s="32"/>
+    </row>
+    <row r="278" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B278" s="32"/>
+      <c r="C278" s="32"/>
       <c r="D278" s="34"/>
-      <c r="E278" s="36"/>
+      <c r="E278" s="32"/>
       <c r="F278" s="34"/>
-      <c r="G278" s="34"/>
-    </row>
-    <row r="279" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B279" s="34"/>
-      <c r="C279" s="36"/>
+      <c r="G278" s="32"/>
+      <c r="H278" s="32"/>
+    </row>
+    <row r="279" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B279" s="32"/>
+      <c r="C279" s="32"/>
       <c r="D279" s="34"/>
-      <c r="E279" s="36"/>
+      <c r="E279" s="32"/>
       <c r="F279" s="34"/>
-      <c r="G279" s="44"/>
-    </row>
-    <row r="280" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B280" s="34"/>
-      <c r="C280" s="36"/>
+      <c r="G279" s="32"/>
+      <c r="H279" s="42"/>
+    </row>
+    <row r="280" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B280" s="32"/>
+      <c r="C280" s="32"/>
       <c r="D280" s="34"/>
-      <c r="E280" s="36"/>
+      <c r="E280" s="32"/>
       <c r="F280" s="34"/>
-      <c r="G280" s="44"/>
-    </row>
-    <row r="281" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B281" s="34"/>
-      <c r="C281" s="36"/>
+      <c r="G280" s="32"/>
+      <c r="H280" s="42"/>
+    </row>
+    <row r="281" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B281" s="32"/>
+      <c r="C281" s="32"/>
       <c r="D281" s="34"/>
-      <c r="E281" s="36"/>
+      <c r="E281" s="32"/>
       <c r="F281" s="34"/>
-      <c r="G281" s="44"/>
-    </row>
-    <row r="282" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B282" s="34"/>
-      <c r="C282" s="36"/>
+      <c r="G281" s="32"/>
+      <c r="H281" s="42"/>
+    </row>
+    <row r="282" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B282" s="32"/>
+      <c r="C282" s="32"/>
       <c r="D282" s="34"/>
-      <c r="E282" s="36"/>
+      <c r="E282" s="32"/>
       <c r="F282" s="34"/>
-      <c r="G282" s="44"/>
-    </row>
-    <row r="283" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B283" s="34"/>
-      <c r="C283" s="36"/>
+      <c r="G282" s="32"/>
+      <c r="H282" s="42"/>
+    </row>
+    <row r="283" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B283" s="32"/>
+      <c r="C283" s="32"/>
       <c r="D283" s="34"/>
-      <c r="E283" s="36"/>
+      <c r="E283" s="32"/>
       <c r="F283" s="34"/>
-      <c r="G283" s="44"/>
-    </row>
-    <row r="284" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B284" s="34"/>
-      <c r="C284" s="36"/>
+      <c r="G283" s="32"/>
+      <c r="H283" s="42"/>
+    </row>
+    <row r="284" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B284" s="32"/>
+      <c r="C284" s="32"/>
       <c r="D284" s="34"/>
-      <c r="E284" s="36"/>
+      <c r="E284" s="32"/>
       <c r="F284" s="34"/>
-      <c r="G284" s="44"/>
-    </row>
-    <row r="285" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B285" s="34"/>
-      <c r="C285" s="36"/>
+      <c r="G284" s="32"/>
+      <c r="H284" s="42"/>
+    </row>
+    <row r="285" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B285" s="32"/>
+      <c r="C285" s="32"/>
       <c r="D285" s="34"/>
-      <c r="E285" s="36"/>
+      <c r="E285" s="32"/>
       <c r="F285" s="34"/>
-      <c r="G285" s="44"/>
-    </row>
-    <row r="286" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B286" s="34"/>
-      <c r="C286" s="36"/>
+      <c r="G285" s="32"/>
+      <c r="H285" s="42"/>
+    </row>
+    <row r="286" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B286" s="32"/>
+      <c r="C286" s="32"/>
       <c r="D286" s="34"/>
-      <c r="E286" s="36"/>
+      <c r="E286" s="32"/>
       <c r="F286" s="34"/>
-      <c r="G286" s="44"/>
-    </row>
-    <row r="287" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B287" s="34"/>
-      <c r="C287" s="36"/>
+      <c r="G286" s="32"/>
+      <c r="H286" s="42"/>
+    </row>
+    <row r="287" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B287" s="32"/>
+      <c r="C287" s="32"/>
       <c r="D287" s="34"/>
-      <c r="E287" s="36"/>
+      <c r="E287" s="32"/>
       <c r="F287" s="34"/>
-      <c r="G287" s="44"/>
-    </row>
-    <row r="288" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B288" s="34"/>
-      <c r="C288" s="36"/>
+      <c r="G287" s="32"/>
+      <c r="H287" s="42"/>
+    </row>
+    <row r="288" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B288" s="32"/>
+      <c r="C288" s="32"/>
       <c r="D288" s="34"/>
-      <c r="E288" s="36"/>
+      <c r="E288" s="32"/>
       <c r="F288" s="34"/>
-      <c r="G288" s="44"/>
-    </row>
-    <row r="289" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B289" s="34"/>
-      <c r="C289" s="36"/>
+      <c r="G288" s="32"/>
+      <c r="H288" s="42"/>
+    </row>
+    <row r="289" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B289" s="32"/>
+      <c r="C289" s="32"/>
       <c r="D289" s="34"/>
-      <c r="E289" s="36"/>
+      <c r="E289" s="32"/>
       <c r="F289" s="34"/>
-      <c r="G289" s="44"/>
-    </row>
-    <row r="290" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B290" s="34"/>
-      <c r="C290" s="36"/>
+      <c r="G289" s="32"/>
+      <c r="H289" s="42"/>
+    </row>
+    <row r="290" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B290" s="32"/>
+      <c r="C290" s="32"/>
       <c r="D290" s="34"/>
-      <c r="E290" s="36"/>
+      <c r="E290" s="32"/>
       <c r="F290" s="34"/>
-      <c r="G290" s="44"/>
-    </row>
-    <row r="291" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B291" s="34"/>
-      <c r="C291" s="36"/>
+      <c r="G290" s="32"/>
+      <c r="H290" s="42"/>
+    </row>
+    <row r="291" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B291" s="32"/>
+      <c r="C291" s="32"/>
       <c r="D291" s="34"/>
-      <c r="E291" s="36"/>
+      <c r="E291" s="32"/>
       <c r="F291" s="34"/>
-      <c r="G291" s="44"/>
-    </row>
-    <row r="292" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B292" s="34"/>
-      <c r="C292" s="36"/>
+      <c r="G291" s="32"/>
+      <c r="H291" s="42"/>
+    </row>
+    <row r="292" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B292" s="32"/>
+      <c r="C292" s="32"/>
       <c r="D292" s="34"/>
-      <c r="E292" s="36"/>
+      <c r="E292" s="32"/>
       <c r="F292" s="34"/>
-      <c r="G292" s="44"/>
-    </row>
-    <row r="293" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B293" s="34"/>
-      <c r="C293" s="36"/>
+      <c r="G292" s="32"/>
+      <c r="H292" s="42"/>
+    </row>
+    <row r="293" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B293" s="32"/>
+      <c r="C293" s="32"/>
       <c r="D293" s="34"/>
-      <c r="E293" s="36"/>
+      <c r="E293" s="32"/>
       <c r="F293" s="34"/>
-      <c r="G293" s="44"/>
-    </row>
-    <row r="294" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B294" s="34"/>
-      <c r="C294" s="36"/>
+      <c r="G293" s="32"/>
+      <c r="H293" s="42"/>
+    </row>
+    <row r="294" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B294" s="32"/>
+      <c r="C294" s="32"/>
       <c r="D294" s="34"/>
-      <c r="E294" s="36"/>
+      <c r="E294" s="32"/>
       <c r="F294" s="34"/>
-      <c r="G294" s="44"/>
-    </row>
-    <row r="295" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B295" s="34"/>
-      <c r="C295" s="36"/>
+      <c r="G294" s="32"/>
+      <c r="H294" s="42"/>
+    </row>
+    <row r="295" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B295" s="32"/>
+      <c r="C295" s="32"/>
       <c r="D295" s="34"/>
-      <c r="E295" s="36"/>
+      <c r="E295" s="32"/>
       <c r="F295" s="34"/>
-      <c r="G295" s="44"/>
-    </row>
-    <row r="296" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B296" s="34"/>
-      <c r="C296" s="36"/>
+      <c r="G295" s="32"/>
+      <c r="H295" s="42"/>
+    </row>
+    <row r="296" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B296" s="32"/>
+      <c r="C296" s="32"/>
       <c r="D296" s="34"/>
-      <c r="E296" s="36"/>
+      <c r="E296" s="32"/>
       <c r="F296" s="34"/>
-      <c r="G296" s="44"/>
-    </row>
-    <row r="297" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B297" s="34"/>
-      <c r="C297" s="36"/>
+      <c r="G296" s="32"/>
+      <c r="H296" s="42"/>
+    </row>
+    <row r="297" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B297" s="32"/>
+      <c r="C297" s="32"/>
       <c r="D297" s="34"/>
-      <c r="E297" s="36"/>
+      <c r="E297" s="32"/>
       <c r="F297" s="34"/>
-      <c r="G297" s="44"/>
-    </row>
-    <row r="298" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B298" s="34"/>
-      <c r="C298" s="36"/>
+      <c r="G297" s="32"/>
+      <c r="H297" s="42"/>
+    </row>
+    <row r="298" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B298" s="32"/>
+      <c r="C298" s="32"/>
       <c r="D298" s="34"/>
-      <c r="E298" s="36"/>
+      <c r="E298" s="32"/>
       <c r="F298" s="34"/>
-      <c r="G298" s="44"/>
-    </row>
-    <row r="299" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B299" s="34"/>
-      <c r="C299" s="36"/>
+      <c r="G298" s="32"/>
+      <c r="H298" s="42"/>
+    </row>
+    <row r="299" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B299" s="32"/>
+      <c r="C299" s="32"/>
       <c r="D299" s="34"/>
-      <c r="E299" s="36"/>
+      <c r="E299" s="32"/>
       <c r="F299" s="34"/>
-      <c r="G299" s="44"/>
-    </row>
-    <row r="300" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B300" s="34"/>
-      <c r="C300" s="36"/>
+      <c r="G299" s="32"/>
+      <c r="H299" s="42"/>
+    </row>
+    <row r="300" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B300" s="32"/>
+      <c r="C300" s="32"/>
       <c r="D300" s="34"/>
-      <c r="E300" s="36"/>
+      <c r="E300" s="32"/>
       <c r="F300" s="34"/>
-      <c r="G300" s="44"/>
-    </row>
-    <row r="301" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B301" s="34"/>
-      <c r="C301" s="36"/>
+      <c r="G300" s="32"/>
+      <c r="H300" s="42"/>
+    </row>
+    <row r="301" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B301" s="32"/>
+      <c r="C301" s="32"/>
       <c r="D301" s="34"/>
-      <c r="E301" s="36"/>
+      <c r="E301" s="32"/>
       <c r="F301" s="34"/>
-      <c r="G301" s="44"/>
-    </row>
-    <row r="302" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B302" s="34"/>
-      <c r="C302" s="36"/>
+      <c r="G301" s="32"/>
+      <c r="H301" s="42"/>
+    </row>
+    <row r="302" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B302" s="32"/>
+      <c r="C302" s="32"/>
       <c r="D302" s="34"/>
-      <c r="E302" s="36"/>
+      <c r="E302" s="32"/>
       <c r="F302" s="34"/>
-      <c r="G302" s="44"/>
-    </row>
-    <row r="303" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B303" s="34"/>
-      <c r="C303" s="36"/>
+      <c r="G302" s="32"/>
+      <c r="H302" s="42"/>
+    </row>
+    <row r="303" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B303" s="32"/>
+      <c r="C303" s="32"/>
       <c r="D303" s="34"/>
-      <c r="E303" s="36"/>
+      <c r="E303" s="32"/>
       <c r="F303" s="34"/>
-      <c r="G303" s="44"/>
-    </row>
-    <row r="304" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B304" s="34"/>
-      <c r="C304" s="36"/>
+      <c r="G303" s="32"/>
+      <c r="H303" s="42"/>
+    </row>
+    <row r="304" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B304" s="32"/>
+      <c r="C304" s="32"/>
       <c r="D304" s="34"/>
-      <c r="E304" s="36"/>
+      <c r="E304" s="32"/>
       <c r="F304" s="34"/>
-      <c r="G304" s="44"/>
-    </row>
-    <row r="305" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B305" s="34"/>
-      <c r="C305" s="36"/>
+      <c r="G304" s="32"/>
+      <c r="H304" s="42"/>
+    </row>
+    <row r="305" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B305" s="32"/>
+      <c r="C305" s="32"/>
       <c r="D305" s="34"/>
-      <c r="E305" s="36"/>
+      <c r="E305" s="32"/>
       <c r="F305" s="34"/>
-      <c r="G305" s="44"/>
-    </row>
-    <row r="306" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B306" s="34"/>
-      <c r="C306" s="36"/>
+      <c r="G305" s="32"/>
+      <c r="H305" s="42"/>
+    </row>
+    <row r="306" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B306" s="32"/>
+      <c r="C306" s="32"/>
       <c r="D306" s="34"/>
-      <c r="E306" s="36"/>
+      <c r="E306" s="32"/>
       <c r="F306" s="34"/>
-      <c r="G306" s="44"/>
-    </row>
-    <row r="307" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B307" s="34"/>
-      <c r="C307" s="36"/>
+      <c r="G306" s="32"/>
+      <c r="H306" s="42"/>
+    </row>
+    <row r="307" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B307" s="32"/>
+      <c r="C307" s="32"/>
       <c r="D307" s="34"/>
-      <c r="E307" s="36"/>
+      <c r="E307" s="32"/>
       <c r="F307" s="34"/>
-      <c r="G307" s="44"/>
-    </row>
-    <row r="308" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B308" s="34"/>
-      <c r="C308" s="36"/>
+      <c r="G307" s="32"/>
+      <c r="H307" s="42"/>
+    </row>
+    <row r="308" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B308" s="32"/>
+      <c r="C308" s="32"/>
       <c r="D308" s="34"/>
-      <c r="E308" s="36"/>
+      <c r="E308" s="32"/>
       <c r="F308" s="34"/>
-      <c r="G308" s="44"/>
-    </row>
-    <row r="309" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B309" s="34"/>
-      <c r="C309" s="36"/>
+      <c r="G308" s="32"/>
+      <c r="H308" s="42"/>
+    </row>
+    <row r="309" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B309" s="32"/>
+      <c r="C309" s="32"/>
       <c r="D309" s="34"/>
-      <c r="E309" s="36"/>
+      <c r="E309" s="32"/>
       <c r="F309" s="34"/>
-      <c r="G309" s="44"/>
-    </row>
-    <row r="310" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B310" s="34"/>
-      <c r="C310" s="36"/>
+      <c r="G309" s="32"/>
+      <c r="H309" s="42"/>
+    </row>
+    <row r="310" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B310" s="32"/>
+      <c r="C310" s="32"/>
       <c r="D310" s="34"/>
-      <c r="E310" s="36"/>
+      <c r="E310" s="32"/>
       <c r="F310" s="34"/>
-      <c r="G310" s="44"/>
-    </row>
-    <row r="311" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B311" s="34"/>
-      <c r="C311" s="36"/>
+      <c r="G310" s="32"/>
+      <c r="H310" s="42"/>
+    </row>
+    <row r="311" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B311" s="32"/>
+      <c r="C311" s="32"/>
       <c r="D311" s="34"/>
-      <c r="E311" s="36"/>
+      <c r="E311" s="32"/>
       <c r="F311" s="34"/>
-      <c r="G311" s="44"/>
-    </row>
-    <row r="312" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B312" s="34"/>
-      <c r="C312" s="36"/>
+      <c r="G311" s="32"/>
+      <c r="H311" s="42"/>
+    </row>
+    <row r="312" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B312" s="32"/>
+      <c r="C312" s="32"/>
       <c r="D312" s="34"/>
-      <c r="E312" s="36"/>
+      <c r="E312" s="32"/>
       <c r="F312" s="34"/>
-      <c r="G312" s="44"/>
-    </row>
-    <row r="313" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B313" s="34"/>
-      <c r="C313" s="36"/>
+      <c r="G312" s="32"/>
+      <c r="H312" s="42"/>
+    </row>
+    <row r="313" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B313" s="32"/>
+      <c r="C313" s="32"/>
       <c r="D313" s="34"/>
-      <c r="E313" s="36"/>
+      <c r="E313" s="32"/>
       <c r="F313" s="34"/>
-      <c r="G313" s="44"/>
-    </row>
-    <row r="314" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B314" s="34"/>
-      <c r="C314" s="36"/>
+      <c r="G313" s="32"/>
+      <c r="H313" s="42"/>
+    </row>
+    <row r="314" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B314" s="32"/>
+      <c r="C314" s="32"/>
       <c r="D314" s="34"/>
-      <c r="E314" s="36"/>
+      <c r="E314" s="32"/>
       <c r="F314" s="34"/>
-      <c r="G314" s="44"/>
-    </row>
-    <row r="315" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B315" s="34"/>
-      <c r="C315" s="36"/>
+      <c r="G314" s="32"/>
+      <c r="H314" s="42"/>
+    </row>
+    <row r="315" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B315" s="32"/>
+      <c r="C315" s="32"/>
       <c r="D315" s="34"/>
-      <c r="E315" s="36"/>
+      <c r="E315" s="32"/>
       <c r="F315" s="34"/>
-      <c r="G315" s="44"/>
-    </row>
-    <row r="316" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B316" s="34"/>
-      <c r="C316" s="36"/>
+      <c r="G315" s="32"/>
+      <c r="H315" s="42"/>
+    </row>
+    <row r="316" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B316" s="32"/>
+      <c r="C316" s="32"/>
       <c r="D316" s="34"/>
-      <c r="E316" s="36"/>
+      <c r="E316" s="32"/>
       <c r="F316" s="34"/>
-      <c r="G316" s="44"/>
-    </row>
-    <row r="317" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B317" s="34"/>
-      <c r="C317" s="36"/>
+      <c r="G316" s="32"/>
+      <c r="H316" s="42"/>
+    </row>
+    <row r="317" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B317" s="32"/>
+      <c r="C317" s="32"/>
       <c r="D317" s="34"/>
-      <c r="E317" s="36"/>
+      <c r="E317" s="32"/>
       <c r="F317" s="34"/>
-      <c r="G317" s="44"/>
-    </row>
-    <row r="318" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B318" s="34"/>
-      <c r="C318" s="36"/>
+      <c r="G317" s="32"/>
+      <c r="H317" s="42"/>
+    </row>
+    <row r="318" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B318" s="32"/>
+      <c r="C318" s="32"/>
       <c r="D318" s="34"/>
-      <c r="E318" s="36"/>
+      <c r="E318" s="32"/>
       <c r="F318" s="34"/>
-      <c r="G318" s="44"/>
-    </row>
-    <row r="319" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B319" s="34"/>
-      <c r="C319" s="36"/>
+      <c r="G318" s="32"/>
+      <c r="H318" s="42"/>
+    </row>
+    <row r="319" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B319" s="32"/>
+      <c r="C319" s="32"/>
       <c r="D319" s="34"/>
-      <c r="E319" s="36"/>
+      <c r="E319" s="32"/>
       <c r="F319" s="34"/>
-      <c r="G319" s="44"/>
-    </row>
-    <row r="320" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B320" s="34"/>
-      <c r="C320" s="36"/>
+      <c r="G319" s="32"/>
+      <c r="H319" s="42"/>
+    </row>
+    <row r="320" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B320" s="32"/>
+      <c r="C320" s="32"/>
       <c r="D320" s="34"/>
-      <c r="E320" s="36"/>
+      <c r="E320" s="32"/>
       <c r="F320" s="34"/>
-      <c r="G320" s="44"/>
-    </row>
-    <row r="321" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B321" s="34"/>
-      <c r="C321" s="36"/>
+      <c r="G320" s="32"/>
+      <c r="H320" s="42"/>
+    </row>
+    <row r="321" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B321" s="32"/>
+      <c r="C321" s="32"/>
       <c r="D321" s="34"/>
-      <c r="E321" s="36"/>
+      <c r="E321" s="32"/>
       <c r="F321" s="34"/>
-      <c r="G321" s="44"/>
-    </row>
-    <row r="322" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B322" s="34"/>
-      <c r="C322" s="36"/>
+      <c r="G321" s="32"/>
+      <c r="H321" s="42"/>
+    </row>
+    <row r="322" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B322" s="32"/>
+      <c r="C322" s="32"/>
       <c r="D322" s="34"/>
-      <c r="E322" s="36"/>
+      <c r="E322" s="32"/>
       <c r="F322" s="34"/>
-      <c r="G322" s="44"/>
-    </row>
-    <row r="323" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B323" s="34"/>
-      <c r="C323" s="36"/>
+      <c r="G322" s="32"/>
+      <c r="H322" s="42"/>
+    </row>
+    <row r="323" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B323" s="32"/>
+      <c r="C323" s="32"/>
       <c r="D323" s="34"/>
-      <c r="E323" s="36"/>
+      <c r="E323" s="32"/>
       <c r="F323" s="34"/>
-      <c r="G323" s="44"/>
-    </row>
-    <row r="324" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B324" s="34"/>
-      <c r="C324" s="36"/>
+      <c r="G323" s="32"/>
+      <c r="H323" s="42"/>
+    </row>
+    <row r="324" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B324" s="32"/>
+      <c r="C324" s="32"/>
       <c r="D324" s="34"/>
-      <c r="E324" s="36"/>
+      <c r="E324" s="32"/>
       <c r="F324" s="34"/>
-      <c r="G324" s="44"/>
-    </row>
-    <row r="325" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B325" s="34"/>
-      <c r="C325" s="36"/>
+      <c r="G324" s="32"/>
+      <c r="H324" s="42"/>
+    </row>
+    <row r="325" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B325" s="32"/>
+      <c r="C325" s="32"/>
       <c r="D325" s="34"/>
-      <c r="E325" s="36"/>
+      <c r="E325" s="32"/>
       <c r="F325" s="34"/>
-      <c r="G325" s="44"/>
-    </row>
-    <row r="326" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B326" s="34"/>
-      <c r="C326" s="36"/>
+      <c r="G325" s="32"/>
+      <c r="H325" s="42"/>
+    </row>
+    <row r="326" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B326" s="32"/>
+      <c r="C326" s="32"/>
       <c r="D326" s="34"/>
-      <c r="E326" s="36"/>
+      <c r="E326" s="32"/>
       <c r="F326" s="34"/>
-      <c r="G326" s="44"/>
-    </row>
-    <row r="327" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B327" s="34"/>
-      <c r="C327" s="36"/>
+      <c r="G326" s="32"/>
+      <c r="H326" s="42"/>
+    </row>
+    <row r="327" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B327" s="32"/>
+      <c r="C327" s="32"/>
       <c r="D327" s="34"/>
-      <c r="E327" s="36"/>
+      <c r="E327" s="32"/>
       <c r="F327" s="34"/>
-      <c r="G327" s="44"/>
-    </row>
-    <row r="328" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B328" s="34"/>
-      <c r="C328" s="36"/>
+      <c r="G327" s="32"/>
+      <c r="H327" s="42"/>
+    </row>
+    <row r="328" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B328" s="32"/>
+      <c r="C328" s="32"/>
       <c r="D328" s="34"/>
-      <c r="E328" s="36"/>
+      <c r="E328" s="32"/>
       <c r="F328" s="34"/>
-      <c r="G328" s="44"/>
-    </row>
-    <row r="329" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B329" s="34"/>
-      <c r="C329" s="36"/>
+      <c r="G328" s="32"/>
+      <c r="H328" s="42"/>
+    </row>
+    <row r="329" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B329" s="32"/>
+      <c r="C329" s="32"/>
       <c r="D329" s="34"/>
-      <c r="E329" s="36"/>
+      <c r="E329" s="32"/>
       <c r="F329" s="34"/>
-      <c r="G329" s="44"/>
-    </row>
-    <row r="330" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B330" s="34"/>
-      <c r="C330" s="36"/>
+      <c r="G329" s="32"/>
+      <c r="H329" s="42"/>
+    </row>
+    <row r="330" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B330" s="32"/>
+      <c r="C330" s="32"/>
       <c r="D330" s="34"/>
-      <c r="E330" s="36"/>
+      <c r="E330" s="32"/>
       <c r="F330" s="34"/>
-      <c r="G330" s="44"/>
-    </row>
-    <row r="331" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B331" s="34"/>
-      <c r="C331" s="36"/>
+      <c r="G330" s="32"/>
+      <c r="H330" s="42"/>
+    </row>
+    <row r="331" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B331" s="32"/>
+      <c r="C331" s="32"/>
       <c r="D331" s="34"/>
-      <c r="E331" s="36"/>
+      <c r="E331" s="32"/>
       <c r="F331" s="34"/>
-      <c r="G331" s="44"/>
-    </row>
-    <row r="332" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B332" s="34"/>
-      <c r="C332" s="36"/>
+      <c r="G331" s="32"/>
+      <c r="H331" s="42"/>
+    </row>
+    <row r="332" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B332" s="32"/>
+      <c r="C332" s="32"/>
       <c r="D332" s="34"/>
-      <c r="E332" s="36"/>
+      <c r="E332" s="32"/>
       <c r="F332" s="34"/>
-      <c r="G332" s="44"/>
-    </row>
-    <row r="333" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B333" s="34"/>
-      <c r="C333" s="36"/>
+      <c r="G332" s="32"/>
+      <c r="H332" s="42"/>
+    </row>
+    <row r="333" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B333" s="32"/>
+      <c r="C333" s="32"/>
       <c r="D333" s="34"/>
-      <c r="E333" s="36"/>
+      <c r="E333" s="32"/>
       <c r="F333" s="34"/>
-      <c r="G333" s="44"/>
-    </row>
-    <row r="334" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B334" s="34"/>
-      <c r="C334" s="36"/>
+      <c r="G333" s="32"/>
+      <c r="H333" s="42"/>
+    </row>
+    <row r="334" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B334" s="32"/>
+      <c r="C334" s="32"/>
       <c r="D334" s="34"/>
-      <c r="E334" s="36"/>
+      <c r="E334" s="32"/>
       <c r="F334" s="34"/>
-      <c r="G334" s="44"/>
-    </row>
-    <row r="335" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B335" s="34"/>
-      <c r="C335" s="36"/>
+      <c r="G334" s="32"/>
+      <c r="H334" s="42"/>
+    </row>
+    <row r="335" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B335" s="32"/>
+      <c r="C335" s="32"/>
       <c r="D335" s="34"/>
-      <c r="E335" s="36"/>
+      <c r="E335" s="32"/>
       <c r="F335" s="34"/>
-      <c r="G335" s="44"/>
-    </row>
-    <row r="336" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B336" s="34"/>
-      <c r="C336" s="36"/>
+      <c r="G335" s="32"/>
+      <c r="H335" s="42"/>
+    </row>
+    <row r="336" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B336" s="32"/>
+      <c r="C336" s="32"/>
       <c r="D336" s="34"/>
-      <c r="E336" s="36"/>
+      <c r="E336" s="32"/>
       <c r="F336" s="34"/>
-      <c r="G336" s="44"/>
-    </row>
-    <row r="337" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B337" s="34"/>
-      <c r="C337" s="36"/>
+      <c r="G336" s="32"/>
+      <c r="H336" s="42"/>
+    </row>
+    <row r="337" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B337" s="32"/>
+      <c r="C337" s="32"/>
       <c r="D337" s="34"/>
-      <c r="E337" s="36"/>
+      <c r="E337" s="32"/>
       <c r="F337" s="34"/>
-      <c r="G337" s="44"/>
-    </row>
-    <row r="338" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B338" s="34"/>
-      <c r="C338" s="36"/>
+      <c r="G337" s="32"/>
+      <c r="H337" s="42"/>
+    </row>
+    <row r="338" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B338" s="32"/>
+      <c r="C338" s="32"/>
       <c r="D338" s="34"/>
-      <c r="E338" s="36"/>
+      <c r="E338" s="32"/>
       <c r="F338" s="34"/>
-      <c r="G338" s="44"/>
-    </row>
-    <row r="339" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B339" s="34"/>
-      <c r="C339" s="36"/>
+      <c r="G338" s="32"/>
+      <c r="H338" s="42"/>
+    </row>
+    <row r="339" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B339" s="32"/>
+      <c r="C339" s="32"/>
       <c r="D339" s="34"/>
-      <c r="E339" s="36"/>
+      <c r="E339" s="32"/>
       <c r="F339" s="34"/>
-      <c r="G339" s="44"/>
-    </row>
-    <row r="340" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B340" s="34"/>
-      <c r="C340" s="36"/>
+      <c r="G339" s="32"/>
+      <c r="H339" s="42"/>
+    </row>
+    <row r="340" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B340" s="32"/>
+      <c r="C340" s="32"/>
       <c r="D340" s="34"/>
-      <c r="E340" s="36"/>
+      <c r="E340" s="32"/>
       <c r="F340" s="34"/>
-      <c r="G340" s="44"/>
-    </row>
-    <row r="341" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B341" s="34"/>
-      <c r="C341" s="36"/>
+      <c r="G340" s="32"/>
+      <c r="H340" s="42"/>
+    </row>
+    <row r="341" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B341" s="32"/>
+      <c r="C341" s="32"/>
       <c r="D341" s="34"/>
-      <c r="E341" s="36"/>
+      <c r="E341" s="32"/>
       <c r="F341" s="34"/>
-      <c r="G341" s="44"/>
-    </row>
-    <row r="342" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B342" s="34"/>
-      <c r="C342" s="36"/>
+      <c r="G341" s="32"/>
+      <c r="H341" s="42"/>
+    </row>
+    <row r="342" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B342" s="32"/>
+      <c r="C342" s="32"/>
       <c r="D342" s="34"/>
-      <c r="E342" s="36"/>
+      <c r="E342" s="32"/>
       <c r="F342" s="34"/>
-      <c r="G342" s="44"/>
-    </row>
-    <row r="343" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B343" s="34"/>
-      <c r="C343" s="36"/>
+      <c r="G342" s="32"/>
+      <c r="H342" s="42"/>
+    </row>
+    <row r="343" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B343" s="32"/>
+      <c r="C343" s="32"/>
       <c r="D343" s="34"/>
-      <c r="E343" s="36"/>
+      <c r="E343" s="32"/>
       <c r="F343" s="34"/>
-      <c r="G343" s="44"/>
-    </row>
-    <row r="344" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B344" s="34"/>
-      <c r="C344" s="36"/>
+      <c r="G343" s="32"/>
+      <c r="H343" s="42"/>
+    </row>
+    <row r="344" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B344" s="32"/>
+      <c r="C344" s="32"/>
       <c r="D344" s="34"/>
-      <c r="E344" s="36"/>
+      <c r="E344" s="32"/>
       <c r="F344" s="34"/>
-      <c r="G344" s="44"/>
-    </row>
-    <row r="345" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B345" s="34"/>
-      <c r="C345" s="36"/>
+      <c r="G344" s="32"/>
+      <c r="H344" s="42"/>
+    </row>
+    <row r="345" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B345" s="32"/>
+      <c r="C345" s="32"/>
       <c r="D345" s="34"/>
-      <c r="E345" s="36"/>
+      <c r="E345" s="32"/>
       <c r="F345" s="34"/>
-      <c r="G345" s="44"/>
-    </row>
-    <row r="346" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B346" s="34"/>
-      <c r="C346" s="36"/>
+      <c r="G345" s="32"/>
+      <c r="H345" s="42"/>
+    </row>
+    <row r="346" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B346" s="32"/>
+      <c r="C346" s="32"/>
       <c r="D346" s="34"/>
-      <c r="E346" s="36"/>
+      <c r="E346" s="32"/>
       <c r="F346" s="34"/>
-      <c r="G346" s="44"/>
-    </row>
-    <row r="347" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B347" s="34"/>
-      <c r="C347" s="36"/>
+      <c r="G346" s="32"/>
+      <c r="H346" s="42"/>
+    </row>
+    <row r="347" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B347" s="32"/>
+      <c r="C347" s="32"/>
       <c r="D347" s="34"/>
-      <c r="E347" s="36"/>
+      <c r="E347" s="32"/>
       <c r="F347" s="34"/>
-      <c r="G347" s="44"/>
-    </row>
-    <row r="348" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B348" s="34"/>
-      <c r="C348" s="36"/>
+      <c r="G347" s="32"/>
+      <c r="H347" s="42"/>
+    </row>
+    <row r="348" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B348" s="32"/>
+      <c r="C348" s="32"/>
       <c r="D348" s="34"/>
-      <c r="E348" s="36"/>
+      <c r="E348" s="32"/>
       <c r="F348" s="34"/>
-      <c r="G348" s="44"/>
-    </row>
-    <row r="349" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B349" s="34"/>
-      <c r="C349" s="36"/>
+      <c r="G348" s="32"/>
+      <c r="H348" s="42"/>
+    </row>
+    <row r="349" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B349" s="32"/>
+      <c r="C349" s="32"/>
       <c r="D349" s="34"/>
-      <c r="E349" s="36"/>
+      <c r="E349" s="32"/>
       <c r="F349" s="34"/>
-      <c r="G349" s="44"/>
-    </row>
-    <row r="350" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B350" s="34"/>
-      <c r="C350" s="36"/>
+      <c r="G349" s="32"/>
+      <c r="H349" s="42"/>
+    </row>
+    <row r="350" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B350" s="32"/>
+      <c r="C350" s="32"/>
       <c r="D350" s="34"/>
-      <c r="E350" s="36"/>
+      <c r="E350" s="32"/>
       <c r="F350" s="34"/>
-      <c r="G350" s="44"/>
-    </row>
-    <row r="351" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B351" s="34"/>
-      <c r="C351" s="36"/>
+      <c r="G350" s="32"/>
+      <c r="H350" s="42"/>
+    </row>
+    <row r="351" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B351" s="32"/>
+      <c r="C351" s="32"/>
       <c r="D351" s="34"/>
-      <c r="E351" s="36"/>
+      <c r="E351" s="32"/>
       <c r="F351" s="34"/>
-      <c r="G351" s="44"/>
-    </row>
-    <row r="352" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B352" s="34"/>
-      <c r="C352" s="36"/>
+      <c r="G351" s="32"/>
+      <c r="H351" s="42"/>
+    </row>
+    <row r="352" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B352" s="32"/>
+      <c r="C352" s="32"/>
       <c r="D352" s="34"/>
-      <c r="E352" s="36"/>
+      <c r="E352" s="32"/>
       <c r="F352" s="34"/>
-      <c r="G352" s="44"/>
-    </row>
-    <row r="353" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B353" s="34"/>
-      <c r="C353" s="36"/>
+      <c r="G352" s="32"/>
+      <c r="H352" s="42"/>
+    </row>
+    <row r="353" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B353" s="32"/>
+      <c r="C353" s="32"/>
       <c r="D353" s="34"/>
-      <c r="E353" s="36"/>
+      <c r="E353" s="32"/>
       <c r="F353" s="34"/>
-      <c r="G353" s="44"/>
-    </row>
-    <row r="354" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B354" s="34"/>
-      <c r="C354" s="36"/>
+      <c r="G353" s="32"/>
+      <c r="H353" s="42"/>
+    </row>
+    <row r="354" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B354" s="32"/>
+      <c r="C354" s="32"/>
       <c r="D354" s="34"/>
-      <c r="E354" s="36"/>
+      <c r="E354" s="32"/>
       <c r="F354" s="34"/>
-      <c r="G354" s="44"/>
-    </row>
-    <row r="355" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B355" s="34"/>
-      <c r="C355" s="36"/>
+      <c r="G354" s="32"/>
+      <c r="H354" s="42"/>
+    </row>
+    <row r="355" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B355" s="32"/>
+      <c r="C355" s="32"/>
       <c r="D355" s="34"/>
-      <c r="E355" s="36"/>
+      <c r="E355" s="32"/>
       <c r="F355" s="34"/>
-      <c r="G355" s="44"/>
-    </row>
-    <row r="356" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B356" s="34"/>
-      <c r="C356" s="36"/>
+      <c r="G355" s="32"/>
+      <c r="H355" s="42"/>
+    </row>
+    <row r="356" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B356" s="32"/>
+      <c r="C356" s="32"/>
       <c r="D356" s="34"/>
-      <c r="E356" s="36"/>
+      <c r="E356" s="32"/>
       <c r="F356" s="34"/>
-      <c r="G356" s="44"/>
-    </row>
-    <row r="357" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B357" s="34"/>
-      <c r="C357" s="36"/>
+      <c r="G356" s="32"/>
+      <c r="H356" s="42"/>
+    </row>
+    <row r="357" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B357" s="32"/>
+      <c r="C357" s="32"/>
       <c r="D357" s="34"/>
-      <c r="E357" s="36"/>
+      <c r="E357" s="32"/>
       <c r="F357" s="34"/>
-      <c r="G357" s="44"/>
-    </row>
-    <row r="358" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B358" s="34"/>
-      <c r="C358" s="36"/>
+      <c r="G357" s="32"/>
+      <c r="H357" s="42"/>
+    </row>
+    <row r="358" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B358" s="32"/>
+      <c r="C358" s="32"/>
       <c r="D358" s="34"/>
-      <c r="E358" s="36"/>
+      <c r="E358" s="32"/>
       <c r="F358" s="34"/>
-      <c r="G358" s="44"/>
-    </row>
-    <row r="359" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B359" s="34"/>
-      <c r="C359" s="36"/>
+      <c r="G358" s="32"/>
+      <c r="H358" s="42"/>
+    </row>
+    <row r="359" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B359" s="32"/>
+      <c r="C359" s="32"/>
       <c r="D359" s="34"/>
-      <c r="E359" s="36"/>
+      <c r="E359" s="32"/>
       <c r="F359" s="34"/>
-      <c r="G359" s="44"/>
-    </row>
-    <row r="360" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B360" s="34"/>
-      <c r="C360" s="36"/>
+      <c r="G359" s="32"/>
+      <c r="H359" s="42"/>
+    </row>
+    <row r="360" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B360" s="32"/>
+      <c r="C360" s="32"/>
       <c r="D360" s="34"/>
-      <c r="E360" s="36"/>
+      <c r="E360" s="32"/>
       <c r="F360" s="34"/>
-      <c r="G360" s="44"/>
-    </row>
-    <row r="361" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B361" s="34"/>
-      <c r="C361" s="36"/>
+      <c r="G360" s="32"/>
+      <c r="H360" s="42"/>
+    </row>
+    <row r="361" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B361" s="32"/>
+      <c r="C361" s="32"/>
       <c r="D361" s="34"/>
-      <c r="E361" s="36"/>
+      <c r="E361" s="32"/>
       <c r="F361" s="34"/>
-      <c r="G361" s="44"/>
-    </row>
-    <row r="362" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B362" s="34"/>
-      <c r="C362" s="36"/>
+      <c r="G361" s="32"/>
+      <c r="H361" s="42"/>
+    </row>
+    <row r="362" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B362" s="32"/>
+      <c r="C362" s="32"/>
       <c r="D362" s="34"/>
-      <c r="E362" s="36"/>
+      <c r="E362" s="32"/>
       <c r="F362" s="34"/>
-      <c r="G362" s="44"/>
-    </row>
-    <row r="363" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B363" s="34"/>
-      <c r="C363" s="36"/>
+      <c r="G362" s="32"/>
+      <c r="H362" s="42"/>
+    </row>
+    <row r="363" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B363" s="32"/>
+      <c r="C363" s="32"/>
       <c r="D363" s="34"/>
-      <c r="E363" s="36"/>
+      <c r="E363" s="32"/>
       <c r="F363" s="34"/>
-      <c r="G363" s="44"/>
-    </row>
-    <row r="364" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B364" s="34"/>
-      <c r="C364" s="36"/>
+      <c r="G363" s="32"/>
+      <c r="H363" s="42"/>
+    </row>
+    <row r="364" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B364" s="32"/>
+      <c r="C364" s="32"/>
       <c r="D364" s="34"/>
-      <c r="E364" s="36"/>
+      <c r="E364" s="32"/>
       <c r="F364" s="34"/>
-      <c r="G364" s="44"/>
-    </row>
-    <row r="365" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B365" s="34"/>
-      <c r="C365" s="36"/>
+      <c r="G364" s="32"/>
+      <c r="H364" s="42"/>
+    </row>
+    <row r="365" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B365" s="32"/>
+      <c r="C365" s="32"/>
       <c r="D365" s="34"/>
-      <c r="E365" s="36"/>
+      <c r="E365" s="32"/>
       <c r="F365" s="34"/>
-      <c r="G365" s="44"/>
-    </row>
-    <row r="366" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B366" s="34"/>
-      <c r="C366" s="36"/>
+      <c r="G365" s="32"/>
+      <c r="H365" s="42"/>
+    </row>
+    <row r="366" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B366" s="32"/>
+      <c r="C366" s="32"/>
       <c r="D366" s="34"/>
-      <c r="E366" s="36"/>
+      <c r="E366" s="32"/>
       <c r="F366" s="34"/>
-      <c r="G366" s="44"/>
-    </row>
-    <row r="367" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B367" s="34"/>
-      <c r="C367" s="36"/>
+      <c r="G366" s="32"/>
+      <c r="H366" s="42"/>
+    </row>
+    <row r="367" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B367" s="32"/>
+      <c r="C367" s="32"/>
       <c r="D367" s="34"/>
-      <c r="E367" s="36"/>
+      <c r="E367" s="32"/>
       <c r="F367" s="34"/>
-      <c r="G367" s="44"/>
-    </row>
-    <row r="368" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B368" s="34"/>
-      <c r="C368" s="36"/>
+      <c r="G367" s="32"/>
+      <c r="H367" s="42"/>
+    </row>
+    <row r="368" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B368" s="32"/>
+      <c r="C368" s="32"/>
       <c r="D368" s="34"/>
-      <c r="E368" s="36"/>
+      <c r="E368" s="32"/>
       <c r="F368" s="34"/>
-      <c r="G368" s="44"/>
-    </row>
-    <row r="369" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B369" s="34"/>
-      <c r="C369" s="36"/>
+      <c r="G368" s="32"/>
+      <c r="H368" s="42"/>
+    </row>
+    <row r="369" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B369" s="32"/>
+      <c r="C369" s="32"/>
       <c r="D369" s="34"/>
-      <c r="E369" s="36"/>
+      <c r="E369" s="32"/>
       <c r="F369" s="34"/>
-      <c r="G369" s="44"/>
-    </row>
-    <row r="370" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B370" s="34"/>
-      <c r="C370" s="36"/>
+      <c r="G369" s="32"/>
+      <c r="H369" s="42"/>
+    </row>
+    <row r="370" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B370" s="32"/>
+      <c r="C370" s="32"/>
       <c r="D370" s="34"/>
-      <c r="E370" s="36"/>
+      <c r="E370" s="32"/>
       <c r="F370" s="34"/>
-      <c r="G370" s="44"/>
-    </row>
-    <row r="371" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B371" s="34"/>
-      <c r="C371" s="36"/>
+      <c r="G370" s="32"/>
+      <c r="H370" s="42"/>
+    </row>
+    <row r="371" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B371" s="32"/>
+      <c r="C371" s="32"/>
       <c r="D371" s="34"/>
-      <c r="E371" s="36"/>
+      <c r="E371" s="32"/>
       <c r="F371" s="34"/>
-      <c r="G371" s="44"/>
-    </row>
-    <row r="372" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B372" s="34"/>
-      <c r="C372" s="36"/>
+      <c r="G371" s="32"/>
+      <c r="H371" s="42"/>
+    </row>
+    <row r="372" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B372" s="32"/>
+      <c r="C372" s="32"/>
       <c r="D372" s="34"/>
-      <c r="E372" s="36"/>
+      <c r="E372" s="32"/>
       <c r="F372" s="34"/>
-      <c r="G372" s="44"/>
-    </row>
-    <row r="373" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B373" s="34"/>
-      <c r="C373" s="36"/>
+      <c r="G372" s="32"/>
+      <c r="H372" s="42"/>
+    </row>
+    <row r="373" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B373" s="32"/>
+      <c r="C373" s="32"/>
       <c r="D373" s="34"/>
-      <c r="E373" s="36"/>
+      <c r="E373" s="32"/>
       <c r="F373" s="34"/>
-      <c r="G373" s="44"/>
-    </row>
-    <row r="374" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B374" s="34"/>
-      <c r="C374" s="36"/>
+      <c r="G373" s="32"/>
+      <c r="H373" s="42"/>
+    </row>
+    <row r="374" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B374" s="32"/>
+      <c r="C374" s="32"/>
       <c r="D374" s="34"/>
-      <c r="E374" s="36"/>
+      <c r="E374" s="32"/>
       <c r="F374" s="34"/>
-      <c r="G374" s="44"/>
-    </row>
-    <row r="375" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B375" s="34"/>
-      <c r="C375" s="36"/>
+      <c r="G374" s="32"/>
+      <c r="H374" s="42"/>
+    </row>
+    <row r="375" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B375" s="32"/>
+      <c r="C375" s="32"/>
       <c r="D375" s="34"/>
-      <c r="E375" s="36"/>
+      <c r="E375" s="32"/>
       <c r="F375" s="34"/>
-      <c r="G375" s="44"/>
-    </row>
-    <row r="376" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B376" s="34"/>
-      <c r="C376" s="36"/>
+      <c r="G375" s="32"/>
+      <c r="H375" s="42"/>
+    </row>
+    <row r="376" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B376" s="32"/>
+      <c r="C376" s="32"/>
       <c r="D376" s="34"/>
-      <c r="E376" s="36"/>
+      <c r="E376" s="32"/>
       <c r="F376" s="34"/>
-      <c r="G376" s="44"/>
-    </row>
-    <row r="377" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B377" s="34"/>
-      <c r="C377" s="36"/>
+      <c r="G376" s="32"/>
+      <c r="H376" s="42"/>
+    </row>
+    <row r="377" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B377" s="32"/>
+      <c r="C377" s="32"/>
       <c r="D377" s="34"/>
-      <c r="E377" s="36"/>
+      <c r="E377" s="32"/>
       <c r="F377" s="34"/>
-      <c r="G377" s="44"/>
-    </row>
-    <row r="378" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B378" s="34"/>
-      <c r="C378" s="36"/>
+      <c r="G377" s="32"/>
+      <c r="H377" s="42"/>
+    </row>
+    <row r="378" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B378" s="32"/>
+      <c r="C378" s="32"/>
       <c r="D378" s="34"/>
-      <c r="E378" s="36"/>
+      <c r="E378" s="32"/>
       <c r="F378" s="34"/>
-      <c r="G378" s="44"/>
-    </row>
-    <row r="379" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B379" s="34"/>
-      <c r="C379" s="36"/>
+      <c r="G378" s="32"/>
+      <c r="H378" s="42"/>
+    </row>
+    <row r="379" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B379" s="32"/>
+      <c r="C379" s="32"/>
       <c r="D379" s="34"/>
-      <c r="E379" s="36"/>
+      <c r="E379" s="32"/>
       <c r="F379" s="34"/>
-      <c r="G379" s="44"/>
-    </row>
-    <row r="380" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B380" s="34"/>
-      <c r="C380" s="36"/>
+      <c r="G379" s="32"/>
+      <c r="H379" s="42"/>
+    </row>
+    <row r="380" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B380" s="32"/>
+      <c r="C380" s="32"/>
       <c r="D380" s="34"/>
-      <c r="E380" s="36"/>
+      <c r="E380" s="32"/>
       <c r="F380" s="34"/>
-      <c r="G380" s="44"/>
-    </row>
-    <row r="381" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B381" s="34"/>
-      <c r="C381" s="36"/>
+      <c r="G380" s="32"/>
+      <c r="H380" s="42"/>
+    </row>
+    <row r="381" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B381" s="32"/>
+      <c r="C381" s="32"/>
       <c r="D381" s="34"/>
-      <c r="E381" s="36"/>
+      <c r="E381" s="32"/>
       <c r="F381" s="34"/>
-      <c r="G381" s="44"/>
-    </row>
-    <row r="382" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B382" s="34"/>
-      <c r="C382" s="36"/>
+      <c r="G381" s="32"/>
+      <c r="H381" s="42"/>
+    </row>
+    <row r="382" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B382" s="32"/>
+      <c r="C382" s="32"/>
       <c r="D382" s="34"/>
-      <c r="E382" s="36"/>
+      <c r="E382" s="32"/>
       <c r="F382" s="34"/>
-      <c r="G382" s="44"/>
-    </row>
-    <row r="383" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B383" s="34"/>
-      <c r="C383" s="36"/>
+      <c r="G382" s="32"/>
+      <c r="H382" s="42"/>
+    </row>
+    <row r="383" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B383" s="32"/>
+      <c r="C383" s="32"/>
       <c r="D383" s="34"/>
-      <c r="E383" s="36"/>
+      <c r="E383" s="32"/>
       <c r="F383" s="34"/>
-      <c r="G383" s="44"/>
-    </row>
-    <row r="384" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B384" s="34"/>
-      <c r="C384" s="36"/>
+      <c r="G383" s="32"/>
+      <c r="H383" s="42"/>
+    </row>
+    <row r="384" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B384" s="32"/>
+      <c r="C384" s="32"/>
       <c r="D384" s="34"/>
-      <c r="E384" s="36"/>
+      <c r="E384" s="32"/>
       <c r="F384" s="34"/>
-      <c r="G384" s="44"/>
-    </row>
-    <row r="385" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B385" s="34"/>
-      <c r="C385" s="36"/>
+      <c r="G384" s="32"/>
+      <c r="H384" s="42"/>
+    </row>
+    <row r="385" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B385" s="32"/>
+      <c r="C385" s="32"/>
       <c r="D385" s="34"/>
-      <c r="E385" s="36"/>
+      <c r="E385" s="32"/>
       <c r="F385" s="34"/>
-      <c r="G385" s="44"/>
-    </row>
-    <row r="386" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B386" s="34"/>
-      <c r="C386" s="36"/>
+      <c r="G385" s="32"/>
+      <c r="H385" s="42"/>
+    </row>
+    <row r="386" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B386" s="32"/>
+      <c r="C386" s="32"/>
       <c r="D386" s="34"/>
-      <c r="E386" s="36"/>
+      <c r="E386" s="32"/>
       <c r="F386" s="34"/>
-      <c r="G386" s="44"/>
-    </row>
-    <row r="387" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B387" s="34"/>
-      <c r="C387" s="36"/>
+      <c r="G386" s="32"/>
+      <c r="H386" s="42"/>
+    </row>
+    <row r="387" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B387" s="32"/>
+      <c r="C387" s="32"/>
       <c r="D387" s="34"/>
-      <c r="E387" s="36"/>
+      <c r="E387" s="32"/>
       <c r="F387" s="34"/>
-      <c r="G387" s="44"/>
-    </row>
-    <row r="388" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B388" s="34"/>
-      <c r="C388" s="36"/>
+      <c r="G387" s="32"/>
+      <c r="H387" s="42"/>
+    </row>
+    <row r="388" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B388" s="32"/>
+      <c r="C388" s="32"/>
       <c r="D388" s="34"/>
-      <c r="E388" s="36"/>
+      <c r="E388" s="32"/>
       <c r="F388" s="34"/>
-      <c r="G388" s="44"/>
-    </row>
-    <row r="389" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B389" s="34"/>
-      <c r="C389" s="36"/>
+      <c r="G388" s="32"/>
+      <c r="H388" s="42"/>
+    </row>
+    <row r="389" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B389" s="32"/>
+      <c r="C389" s="32"/>
       <c r="D389" s="34"/>
-      <c r="E389" s="36"/>
+      <c r="E389" s="32"/>
       <c r="F389" s="34"/>
-      <c r="G389" s="44"/>
-    </row>
-    <row r="390" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B390" s="34"/>
-      <c r="C390" s="36"/>
+      <c r="G389" s="32"/>
+      <c r="H389" s="42"/>
+    </row>
+    <row r="390" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B390" s="32"/>
+      <c r="C390" s="32"/>
       <c r="D390" s="34"/>
-      <c r="E390" s="36"/>
+      <c r="E390" s="32"/>
       <c r="F390" s="34"/>
-      <c r="G390" s="44"/>
-    </row>
-    <row r="391" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B391" s="34"/>
-      <c r="C391" s="36"/>
+      <c r="G390" s="32"/>
+      <c r="H390" s="42"/>
+    </row>
+    <row r="391" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B391" s="32"/>
+      <c r="C391" s="32"/>
       <c r="D391" s="34"/>
-      <c r="E391" s="36"/>
+      <c r="E391" s="32"/>
       <c r="F391" s="34"/>
-      <c r="G391" s="44"/>
-    </row>
-    <row r="392" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B392" s="34"/>
-      <c r="C392" s="36"/>
+      <c r="G391" s="32"/>
+      <c r="H391" s="42"/>
+    </row>
+    <row r="392" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B392" s="32"/>
+      <c r="C392" s="32"/>
       <c r="D392" s="34"/>
-      <c r="E392" s="36"/>
+      <c r="E392" s="32"/>
       <c r="F392" s="34"/>
-      <c r="G392" s="44"/>
-    </row>
-    <row r="393" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B393" s="34"/>
-      <c r="C393" s="36"/>
+      <c r="G392" s="32"/>
+      <c r="H392" s="42"/>
+    </row>
+    <row r="393" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B393" s="32"/>
+      <c r="C393" s="32"/>
       <c r="D393" s="34"/>
-      <c r="E393" s="36"/>
+      <c r="E393" s="32"/>
       <c r="F393" s="34"/>
-      <c r="G393" s="44"/>
-    </row>
-    <row r="394" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B394" s="34"/>
-      <c r="C394" s="36"/>
+      <c r="G393" s="32"/>
+      <c r="H393" s="42"/>
+    </row>
+    <row r="394" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B394" s="32"/>
+      <c r="C394" s="32"/>
       <c r="D394" s="34"/>
-      <c r="E394" s="36"/>
+      <c r="E394" s="32"/>
       <c r="F394" s="34"/>
-      <c r="G394" s="44"/>
-    </row>
-    <row r="395" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B395" s="34"/>
-      <c r="C395" s="36"/>
+      <c r="G394" s="32"/>
+      <c r="H394" s="42"/>
+    </row>
+    <row r="395" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B395" s="32"/>
+      <c r="C395" s="32"/>
       <c r="D395" s="34"/>
-      <c r="E395" s="36"/>
+      <c r="E395" s="32"/>
       <c r="F395" s="34"/>
-      <c r="G395" s="44"/>
-    </row>
-    <row r="396" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B396" s="34"/>
-      <c r="C396" s="36"/>
+      <c r="G395" s="32"/>
+      <c r="H395" s="42"/>
+    </row>
+    <row r="396" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B396" s="32"/>
+      <c r="C396" s="32"/>
       <c r="D396" s="34"/>
-      <c r="E396" s="36"/>
+      <c r="E396" s="32"/>
       <c r="F396" s="34"/>
-      <c r="G396" s="44"/>
-    </row>
-    <row r="397" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B397" s="34"/>
-      <c r="C397" s="36"/>
+      <c r="G396" s="32"/>
+      <c r="H396" s="42"/>
+    </row>
+    <row r="397" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B397" s="32"/>
+      <c r="C397" s="32"/>
       <c r="D397" s="34"/>
-      <c r="E397" s="36"/>
+      <c r="E397" s="32"/>
       <c r="F397" s="34"/>
-      <c r="G397" s="44"/>
-    </row>
-    <row r="398" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B398" s="34"/>
-      <c r="C398" s="36"/>
+      <c r="G397" s="32"/>
+      <c r="H397" s="42"/>
+    </row>
+    <row r="398" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B398" s="32"/>
+      <c r="C398" s="32"/>
       <c r="D398" s="34"/>
-      <c r="E398" s="36"/>
+      <c r="E398" s="32"/>
       <c r="F398" s="34"/>
-      <c r="G398" s="44"/>
-    </row>
-    <row r="399" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B399" s="34"/>
-      <c r="C399" s="36"/>
+      <c r="G398" s="32"/>
+      <c r="H398" s="42"/>
+    </row>
+    <row r="399" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B399" s="32"/>
+      <c r="C399" s="32"/>
       <c r="D399" s="34"/>
-      <c r="E399" s="36"/>
+      <c r="E399" s="32"/>
       <c r="F399" s="34"/>
-      <c r="G399" s="44"/>
-    </row>
-    <row r="400" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B400" s="34"/>
-      <c r="C400" s="36"/>
+      <c r="G399" s="32"/>
+      <c r="H399" s="42"/>
+    </row>
+    <row r="400" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B400" s="32"/>
+      <c r="C400" s="32"/>
       <c r="D400" s="34"/>
-      <c r="E400" s="36"/>
+      <c r="E400" s="32"/>
       <c r="F400" s="34"/>
-      <c r="G400" s="44"/>
-    </row>
-    <row r="401" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B401" s="34"/>
-      <c r="C401" s="36"/>
+      <c r="G400" s="32"/>
+      <c r="H400" s="42"/>
+    </row>
+    <row r="401" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B401" s="32"/>
+      <c r="C401" s="32"/>
       <c r="D401" s="34"/>
-      <c r="E401" s="36"/>
+      <c r="E401" s="32"/>
       <c r="F401" s="34"/>
-      <c r="G401" s="44"/>
-    </row>
-    <row r="402" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B402" s="34"/>
-      <c r="C402" s="36"/>
+      <c r="G401" s="32"/>
+      <c r="H401" s="42"/>
+    </row>
+    <row r="402" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B402" s="32"/>
+      <c r="C402" s="32"/>
       <c r="D402" s="34"/>
-      <c r="E402" s="36"/>
+      <c r="E402" s="32"/>
       <c r="F402" s="34"/>
-      <c r="G402" s="44"/>
-    </row>
-    <row r="403" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B403" s="34"/>
-      <c r="C403" s="36"/>
+      <c r="G402" s="32"/>
+      <c r="H402" s="42"/>
+    </row>
+    <row r="403" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B403" s="32"/>
+      <c r="C403" s="32"/>
       <c r="D403" s="34"/>
-      <c r="E403" s="36"/>
+      <c r="E403" s="32"/>
       <c r="F403" s="34"/>
-      <c r="G403" s="44"/>
-    </row>
-    <row r="404" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B404" s="34"/>
-      <c r="C404" s="36"/>
+      <c r="G403" s="32"/>
+      <c r="H403" s="42"/>
+    </row>
+    <row r="404" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B404" s="32"/>
+      <c r="C404" s="32"/>
       <c r="D404" s="34"/>
-      <c r="E404" s="36"/>
+      <c r="E404" s="32"/>
       <c r="F404" s="34"/>
-      <c r="G404" s="44"/>
-    </row>
-    <row r="405" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B405" s="34"/>
-      <c r="C405" s="36"/>
+      <c r="G404" s="32"/>
+      <c r="H404" s="42"/>
+    </row>
+    <row r="405" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B405" s="32"/>
+      <c r="C405" s="32"/>
       <c r="D405" s="34"/>
-      <c r="E405" s="36"/>
+      <c r="E405" s="32"/>
       <c r="F405" s="34"/>
-      <c r="G405" s="44"/>
-    </row>
-    <row r="406" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B406" s="34"/>
-      <c r="C406" s="36"/>
+      <c r="G405" s="32"/>
+      <c r="H405" s="42"/>
+    </row>
+    <row r="406" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B406" s="32"/>
+      <c r="C406" s="32"/>
       <c r="D406" s="34"/>
-      <c r="E406" s="36"/>
+      <c r="E406" s="32"/>
       <c r="F406" s="34"/>
-      <c r="G406" s="44"/>
-    </row>
-    <row r="407" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B407" s="34"/>
-      <c r="C407" s="36"/>
+      <c r="G406" s="32"/>
+      <c r="H406" s="42"/>
+    </row>
+    <row r="407" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B407" s="32"/>
+      <c r="C407" s="32"/>
       <c r="D407" s="34"/>
-      <c r="E407" s="36"/>
+      <c r="E407" s="32"/>
       <c r="F407" s="34"/>
-      <c r="G407" s="44"/>
-    </row>
-    <row r="408" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B408" s="34"/>
-      <c r="C408" s="36"/>
+      <c r="G407" s="32"/>
+      <c r="H407" s="42"/>
+    </row>
+    <row r="408" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B408" s="32"/>
+      <c r="C408" s="32"/>
       <c r="D408" s="34"/>
-      <c r="E408" s="36"/>
+      <c r="E408" s="32"/>
       <c r="F408" s="34"/>
-      <c r="G408" s="44"/>
-    </row>
-    <row r="409" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B409" s="34"/>
-      <c r="C409" s="36"/>
+      <c r="G408" s="32"/>
+      <c r="H408" s="42"/>
+    </row>
+    <row r="409" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B409" s="32"/>
+      <c r="C409" s="32"/>
       <c r="D409" s="34"/>
-      <c r="E409" s="36"/>
+      <c r="E409" s="32"/>
       <c r="F409" s="34"/>
-      <c r="G409" s="44"/>
-    </row>
-    <row r="410" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B410" s="34"/>
-      <c r="C410" s="36"/>
+      <c r="G409" s="32"/>
+      <c r="H409" s="42"/>
+    </row>
+    <row r="410" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B410" s="32"/>
+      <c r="C410" s="32"/>
       <c r="D410" s="34"/>
-      <c r="E410" s="36"/>
+      <c r="E410" s="32"/>
       <c r="F410" s="34"/>
-      <c r="G410" s="44"/>
-    </row>
-    <row r="411" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B411" s="34"/>
-      <c r="C411" s="36"/>
+      <c r="G410" s="32"/>
+      <c r="H410" s="42"/>
+    </row>
+    <row r="411" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B411" s="32"/>
+      <c r="C411" s="32"/>
       <c r="D411" s="34"/>
-      <c r="E411" s="36"/>
+      <c r="E411" s="32"/>
       <c r="F411" s="34"/>
-      <c r="G411" s="44"/>
-    </row>
-    <row r="412" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B412" s="34"/>
-      <c r="C412" s="36"/>
+      <c r="G411" s="32"/>
+      <c r="H411" s="42"/>
+    </row>
+    <row r="412" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B412" s="32"/>
+      <c r="C412" s="32"/>
       <c r="D412" s="34"/>
-      <c r="E412" s="36"/>
+      <c r="E412" s="32"/>
       <c r="F412" s="34"/>
-      <c r="G412" s="44"/>
-    </row>
-    <row r="413" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B413" s="34"/>
-      <c r="C413" s="36"/>
+      <c r="G412" s="32"/>
+      <c r="H412" s="42"/>
+    </row>
+    <row r="413" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B413" s="32"/>
+      <c r="C413" s="32"/>
       <c r="D413" s="34"/>
-      <c r="E413" s="36"/>
+      <c r="E413" s="32"/>
       <c r="F413" s="34"/>
-      <c r="G413" s="44"/>
-    </row>
-    <row r="414" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B414" s="34"/>
-      <c r="C414" s="36"/>
+      <c r="G413" s="32"/>
+      <c r="H413" s="42"/>
+    </row>
+    <row r="414" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B414" s="32"/>
+      <c r="C414" s="32"/>
       <c r="D414" s="34"/>
-      <c r="E414" s="36"/>
+      <c r="E414" s="32"/>
       <c r="F414" s="34"/>
-      <c r="G414" s="44"/>
-    </row>
-    <row r="415" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B415" s="34"/>
-      <c r="C415" s="36"/>
+      <c r="G414" s="32"/>
+      <c r="H414" s="42"/>
+    </row>
+    <row r="415" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B415" s="32"/>
+      <c r="C415" s="32"/>
       <c r="D415" s="34"/>
-      <c r="E415" s="36"/>
+      <c r="E415" s="32"/>
       <c r="F415" s="34"/>
-      <c r="G415" s="44"/>
-    </row>
-    <row r="416" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B416" s="34"/>
-      <c r="C416" s="36"/>
+      <c r="G415" s="32"/>
+      <c r="H415" s="42"/>
+    </row>
+    <row r="416" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B416" s="32"/>
+      <c r="C416" s="32"/>
       <c r="D416" s="34"/>
-      <c r="E416" s="36"/>
+      <c r="E416" s="32"/>
       <c r="F416" s="34"/>
-      <c r="G416" s="44"/>
-    </row>
-    <row r="417" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B417" s="34"/>
-      <c r="C417" s="36"/>
+      <c r="G416" s="32"/>
+      <c r="H416" s="42"/>
+    </row>
+    <row r="417" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B417" s="32"/>
+      <c r="C417" s="32"/>
       <c r="D417" s="34"/>
-      <c r="E417" s="36"/>
+      <c r="E417" s="32"/>
       <c r="F417" s="34"/>
-      <c r="G417" s="44"/>
-    </row>
-    <row r="418" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B418" s="34"/>
-      <c r="C418" s="36"/>
+      <c r="G417" s="32"/>
+      <c r="H417" s="42"/>
+    </row>
+    <row r="418" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B418" s="32"/>
+      <c r="C418" s="32"/>
       <c r="D418" s="34"/>
-      <c r="E418" s="36"/>
+      <c r="E418" s="32"/>
       <c r="F418" s="34"/>
-      <c r="G418" s="44"/>
-    </row>
-    <row r="419" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B419" s="34"/>
-      <c r="C419" s="36"/>
+      <c r="G418" s="32"/>
+      <c r="H418" s="42"/>
+    </row>
+    <row r="419" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B419" s="32"/>
+      <c r="C419" s="32"/>
       <c r="D419" s="34"/>
-      <c r="E419" s="36"/>
+      <c r="E419" s="32"/>
       <c r="F419" s="34"/>
-      <c r="G419" s="44"/>
-    </row>
-    <row r="420" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B420" s="34"/>
-      <c r="C420" s="36"/>
+      <c r="G419" s="32"/>
+      <c r="H419" s="42"/>
+    </row>
+    <row r="420" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B420" s="32"/>
+      <c r="C420" s="32"/>
       <c r="D420" s="34"/>
-      <c r="E420" s="36"/>
+      <c r="E420" s="32"/>
       <c r="F420" s="34"/>
-      <c r="G420" s="44"/>
-    </row>
-    <row r="421" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B421" s="34"/>
-      <c r="C421" s="36"/>
+      <c r="G420" s="32"/>
+      <c r="H420" s="42"/>
+    </row>
+    <row r="421" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B421" s="32"/>
+      <c r="C421" s="32"/>
       <c r="D421" s="34"/>
-      <c r="E421" s="36"/>
+      <c r="E421" s="32"/>
       <c r="F421" s="34"/>
-      <c r="G421" s="44"/>
-    </row>
-    <row r="422" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B422" s="34"/>
-      <c r="C422" s="36"/>
+      <c r="G421" s="32"/>
+      <c r="H421" s="42"/>
+    </row>
+    <row r="422" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B422" s="32"/>
+      <c r="C422" s="32"/>
       <c r="D422" s="34"/>
-      <c r="E422" s="36"/>
+      <c r="E422" s="32"/>
       <c r="F422" s="34"/>
-      <c r="G422" s="44"/>
-    </row>
-    <row r="423" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B423" s="34"/>
-      <c r="C423" s="36"/>
+      <c r="G422" s="32"/>
+      <c r="H422" s="42"/>
+    </row>
+    <row r="423" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B423" s="32"/>
+      <c r="C423" s="32"/>
       <c r="D423" s="34"/>
-      <c r="E423" s="36"/>
+      <c r="E423" s="32"/>
       <c r="F423" s="34"/>
-      <c r="G423" s="44"/>
-    </row>
-    <row r="424" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B424" s="34"/>
-      <c r="C424" s="36"/>
+      <c r="G423" s="32"/>
+      <c r="H423" s="42"/>
+    </row>
+    <row r="424" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B424" s="32"/>
+      <c r="C424" s="32"/>
       <c r="D424" s="34"/>
-      <c r="E424" s="36"/>
+      <c r="E424" s="32"/>
       <c r="F424" s="34"/>
-      <c r="G424" s="44"/>
-    </row>
-    <row r="425" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B425" s="34"/>
-      <c r="C425" s="36"/>
+      <c r="G424" s="32"/>
+      <c r="H424" s="42"/>
+    </row>
+    <row r="425" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B425" s="32"/>
+      <c r="C425" s="32"/>
       <c r="D425" s="34"/>
-      <c r="E425" s="36"/>
+      <c r="E425" s="32"/>
       <c r="F425" s="34"/>
-      <c r="G425" s="44"/>
-    </row>
-    <row r="426" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B426" s="34"/>
-      <c r="C426" s="36"/>
+      <c r="G425" s="32"/>
+      <c r="H425" s="42"/>
+    </row>
+    <row r="426" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B426" s="32"/>
+      <c r="C426" s="32"/>
       <c r="D426" s="34"/>
-      <c r="E426" s="36"/>
+      <c r="E426" s="32"/>
       <c r="F426" s="34"/>
-      <c r="G426" s="44"/>
-    </row>
-    <row r="427" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B427" s="34"/>
-      <c r="C427" s="36"/>
+      <c r="G426" s="32"/>
+      <c r="H426" s="42"/>
+    </row>
+    <row r="427" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B427" s="32"/>
+      <c r="C427" s="32"/>
       <c r="D427" s="34"/>
-      <c r="E427" s="36"/>
+      <c r="E427" s="32"/>
       <c r="F427" s="34"/>
-      <c r="G427" s="44"/>
-    </row>
-    <row r="428" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B428" s="34"/>
-      <c r="C428" s="36"/>
+      <c r="G427" s="32"/>
+      <c r="H427" s="42"/>
+    </row>
+    <row r="428" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B428" s="32"/>
+      <c r="C428" s="32"/>
       <c r="D428" s="34"/>
-      <c r="E428" s="36"/>
+      <c r="E428" s="32"/>
       <c r="F428" s="34"/>
-      <c r="G428" s="44"/>
-    </row>
-    <row r="429" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B429" s="34"/>
-      <c r="C429" s="36"/>
+      <c r="G428" s="32"/>
+      <c r="H428" s="42"/>
+    </row>
+    <row r="429" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B429" s="32"/>
+      <c r="C429" s="32"/>
       <c r="D429" s="34"/>
-      <c r="E429" s="36"/>
+      <c r="E429" s="32"/>
       <c r="F429" s="34"/>
-      <c r="G429" s="44"/>
-    </row>
-    <row r="430" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B430" s="34"/>
-      <c r="C430" s="36"/>
+      <c r="G429" s="32"/>
+      <c r="H429" s="42"/>
+    </row>
+    <row r="430" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B430" s="32"/>
+      <c r="C430" s="32"/>
       <c r="D430" s="34"/>
-      <c r="E430" s="36"/>
+      <c r="E430" s="32"/>
       <c r="F430" s="34"/>
-      <c r="G430" s="44"/>
-    </row>
-    <row r="431" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B431" s="34"/>
-      <c r="C431" s="36"/>
+      <c r="G430" s="32"/>
+      <c r="H430" s="42"/>
+    </row>
+    <row r="431" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B431" s="32"/>
+      <c r="C431" s="32"/>
       <c r="D431" s="34"/>
-      <c r="E431" s="36"/>
+      <c r="E431" s="32"/>
       <c r="F431" s="34"/>
-      <c r="G431" s="44"/>
-    </row>
-    <row r="432" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B432" s="34"/>
-      <c r="C432" s="36"/>
+      <c r="G431" s="32"/>
+      <c r="H431" s="42"/>
+    </row>
+    <row r="432" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B432" s="32"/>
+      <c r="C432" s="32"/>
       <c r="D432" s="34"/>
-      <c r="E432" s="36"/>
+      <c r="E432" s="32"/>
       <c r="F432" s="34"/>
-      <c r="G432" s="44"/>
-    </row>
-    <row r="433" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B433" s="34"/>
-      <c r="C433" s="36"/>
+      <c r="G432" s="32"/>
+      <c r="H432" s="42"/>
+    </row>
+    <row r="433" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B433" s="32"/>
+      <c r="C433" s="32"/>
       <c r="D433" s="34"/>
-      <c r="E433" s="36"/>
+      <c r="E433" s="32"/>
       <c r="F433" s="34"/>
-      <c r="G433" s="44"/>
-    </row>
-    <row r="434" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B434" s="34"/>
-      <c r="C434" s="36"/>
+      <c r="G433" s="32"/>
+      <c r="H433" s="42"/>
+    </row>
+    <row r="434" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B434" s="32"/>
+      <c r="C434" s="32"/>
       <c r="D434" s="34"/>
-      <c r="E434" s="36"/>
+      <c r="E434" s="32"/>
       <c r="F434" s="34"/>
-      <c r="G434" s="44"/>
-    </row>
-    <row r="435" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B435" s="34"/>
-      <c r="C435" s="36"/>
+      <c r="G434" s="32"/>
+      <c r="H434" s="42"/>
+    </row>
+    <row r="435" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B435" s="32"/>
+      <c r="C435" s="32"/>
       <c r="D435" s="34"/>
-      <c r="E435" s="36"/>
+      <c r="E435" s="32"/>
       <c r="F435" s="34"/>
-      <c r="G435" s="44"/>
-    </row>
-    <row r="436" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B436" s="34"/>
-      <c r="C436" s="36"/>
+      <c r="G435" s="32"/>
+      <c r="H435" s="42"/>
+    </row>
+    <row r="436" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B436" s="32"/>
+      <c r="C436" s="32"/>
       <c r="D436" s="34"/>
-      <c r="E436" s="36"/>
+      <c r="E436" s="32"/>
       <c r="F436" s="34"/>
-      <c r="G436" s="44"/>
-    </row>
-    <row r="437" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B437" s="34"/>
-      <c r="C437" s="36"/>
+      <c r="G436" s="32"/>
+      <c r="H436" s="42"/>
+    </row>
+    <row r="437" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B437" s="32"/>
+      <c r="C437" s="32"/>
       <c r="D437" s="34"/>
-      <c r="E437" s="36"/>
+      <c r="E437" s="32"/>
       <c r="F437" s="34"/>
-      <c r="G437" s="44"/>
-    </row>
-    <row r="438" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B438" s="34"/>
-      <c r="C438" s="36"/>
+      <c r="G437" s="32"/>
+      <c r="H437" s="42"/>
+    </row>
+    <row r="438" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B438" s="32"/>
+      <c r="C438" s="32"/>
       <c r="D438" s="34"/>
-      <c r="E438" s="36"/>
+      <c r="E438" s="32"/>
       <c r="F438" s="34"/>
-      <c r="G438" s="44"/>
-    </row>
-    <row r="439" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B439" s="34"/>
-      <c r="C439" s="36"/>
+      <c r="G438" s="32"/>
+      <c r="H438" s="42"/>
+    </row>
+    <row r="439" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B439" s="32"/>
+      <c r="C439" s="32"/>
       <c r="D439" s="34"/>
-      <c r="E439" s="36"/>
+      <c r="E439" s="32"/>
       <c r="F439" s="34"/>
-      <c r="G439" s="44"/>
-    </row>
-    <row r="440" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B440" s="34"/>
-      <c r="C440" s="36"/>
+      <c r="G439" s="32"/>
+      <c r="H439" s="42"/>
+    </row>
+    <row r="440" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B440" s="32"/>
+      <c r="C440" s="32"/>
       <c r="D440" s="34"/>
-      <c r="E440" s="36"/>
+      <c r="E440" s="32"/>
       <c r="F440" s="34"/>
-      <c r="G440" s="44"/>
-    </row>
-    <row r="441" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B441" s="34"/>
-      <c r="C441" s="36"/>
+      <c r="G440" s="32"/>
+      <c r="H440" s="42"/>
+    </row>
+    <row r="441" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B441" s="32"/>
+      <c r="C441" s="32"/>
       <c r="D441" s="34"/>
-      <c r="E441" s="36"/>
+      <c r="E441" s="32"/>
       <c r="F441" s="34"/>
-      <c r="G441" s="44"/>
-    </row>
-    <row r="442" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B442" s="34"/>
-      <c r="C442" s="36"/>
+      <c r="G441" s="32"/>
+      <c r="H441" s="42"/>
+    </row>
+    <row r="442" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B442" s="32"/>
+      <c r="C442" s="32"/>
       <c r="D442" s="34"/>
-      <c r="E442" s="36"/>
+      <c r="E442" s="32"/>
       <c r="F442" s="34"/>
-      <c r="G442" s="44"/>
-    </row>
-    <row r="443" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B443" s="34"/>
-      <c r="C443" s="36"/>
+      <c r="G442" s="32"/>
+      <c r="H442" s="42"/>
+    </row>
+    <row r="443" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B443" s="32"/>
+      <c r="C443" s="32"/>
       <c r="D443" s="34"/>
-      <c r="E443" s="36"/>
+      <c r="E443" s="32"/>
       <c r="F443" s="34"/>
-      <c r="G443" s="44"/>
-    </row>
-    <row r="444" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B444" s="34"/>
-      <c r="C444" s="36"/>
+      <c r="G443" s="32"/>
+      <c r="H443" s="42"/>
+    </row>
+    <row r="444" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B444" s="32"/>
+      <c r="C444" s="32"/>
       <c r="D444" s="34"/>
-      <c r="E444" s="36"/>
+      <c r="E444" s="32"/>
       <c r="F444" s="34"/>
-      <c r="G444" s="44"/>
-    </row>
-    <row r="445" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B445" s="34"/>
-      <c r="C445" s="36"/>
+      <c r="G444" s="32"/>
+      <c r="H444" s="42"/>
+    </row>
+    <row r="445" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B445" s="32"/>
+      <c r="C445" s="32"/>
       <c r="D445" s="34"/>
-      <c r="E445" s="36"/>
+      <c r="E445" s="32"/>
       <c r="F445" s="34"/>
-      <c r="G445" s="44"/>
-    </row>
-    <row r="446" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B446" s="34"/>
-      <c r="C446" s="36"/>
+      <c r="G445" s="32"/>
+      <c r="H445" s="42"/>
+    </row>
+    <row r="446" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B446" s="32"/>
+      <c r="C446" s="32"/>
       <c r="D446" s="34"/>
-      <c r="E446" s="36"/>
+      <c r="E446" s="32"/>
       <c r="F446" s="34"/>
-      <c r="G446" s="44"/>
-    </row>
-    <row r="447" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B447" s="34"/>
-      <c r="C447" s="36"/>
+      <c r="G446" s="32"/>
+      <c r="H446" s="42"/>
+    </row>
+    <row r="447" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B447" s="32"/>
+      <c r="C447" s="32"/>
       <c r="D447" s="34"/>
-      <c r="E447" s="36"/>
+      <c r="E447" s="32"/>
       <c r="F447" s="34"/>
-      <c r="G447" s="44"/>
-    </row>
-    <row r="448" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B448" s="34"/>
-      <c r="C448" s="36"/>
+      <c r="G447" s="32"/>
+      <c r="H447" s="42"/>
+    </row>
+    <row r="448" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B448" s="32"/>
+      <c r="C448" s="32"/>
       <c r="D448" s="34"/>
-      <c r="E448" s="36"/>
+      <c r="E448" s="32"/>
       <c r="F448" s="34"/>
-      <c r="G448" s="44"/>
-    </row>
-    <row r="449" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B449" s="34"/>
-      <c r="C449" s="36"/>
+      <c r="G448" s="32"/>
+      <c r="H448" s="42"/>
+    </row>
+    <row r="449" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B449" s="32"/>
+      <c r="C449" s="32"/>
       <c r="D449" s="34"/>
-      <c r="E449" s="36"/>
+      <c r="E449" s="32"/>
       <c r="F449" s="34"/>
-      <c r="G449" s="44"/>
-    </row>
-    <row r="450" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B450" s="34"/>
-      <c r="C450" s="36"/>
+      <c r="G449" s="32"/>
+      <c r="H449" s="42"/>
+    </row>
+    <row r="450" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B450" s="32"/>
+      <c r="C450" s="32"/>
       <c r="D450" s="34"/>
-      <c r="E450" s="36"/>
+      <c r="E450" s="32"/>
       <c r="F450" s="34"/>
-      <c r="G450" s="44"/>
-    </row>
-    <row r="451" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G451" s="46"/>
-    </row>
-    <row r="452" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G452" s="46"/>
-    </row>
-    <row r="453" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G453" s="46"/>
-    </row>
-    <row r="454" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G454" s="46"/>
-    </row>
-    <row r="455" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G455" s="46"/>
-    </row>
-    <row r="456" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G456" s="46"/>
-    </row>
-    <row r="457" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G457" s="46"/>
-    </row>
-    <row r="458" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G458" s="46"/>
-    </row>
-    <row r="459" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G459" s="46"/>
-    </row>
-    <row r="460" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G460" s="46"/>
-    </row>
-    <row r="461" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G461" s="46"/>
-    </row>
-    <row r="462" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G462" s="46"/>
-    </row>
-    <row r="463" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G463" s="46"/>
-    </row>
-    <row r="464" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G464" s="46"/>
-    </row>
-    <row r="465" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G465" s="46"/>
-    </row>
-    <row r="466" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G466" s="46"/>
-    </row>
-    <row r="467" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G467" s="46"/>
-    </row>
-    <row r="468" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G468" s="46"/>
-    </row>
-    <row r="469" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G469" s="46"/>
-    </row>
-    <row r="470" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G470" s="46"/>
-    </row>
-    <row r="471" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G471" s="46"/>
-    </row>
-    <row r="472" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G472" s="46"/>
-    </row>
-    <row r="473" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G473" s="46"/>
-    </row>
-    <row r="474" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G474" s="46"/>
-    </row>
-    <row r="475" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G475" s="46"/>
-    </row>
-    <row r="476" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G476" s="46"/>
-    </row>
-    <row r="477" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G477" s="46"/>
-    </row>
-    <row r="478" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G478" s="46"/>
-    </row>
-    <row r="479" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G479" s="46"/>
-    </row>
-    <row r="480" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G480" s="46"/>
-    </row>
-    <row r="481" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G481" s="46"/>
-    </row>
-    <row r="482" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G482" s="46"/>
-    </row>
-    <row r="483" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G483" s="46"/>
-    </row>
-    <row r="484" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G484" s="46"/>
-    </row>
-    <row r="485" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G485" s="46"/>
-    </row>
-    <row r="486" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G486" s="46"/>
-    </row>
-    <row r="487" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G487" s="46"/>
-    </row>
-    <row r="488" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G488" s="46"/>
-    </row>
-    <row r="489" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G489" s="46"/>
-    </row>
-    <row r="490" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G490" s="46"/>
-    </row>
-    <row r="491" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G491" s="46"/>
-    </row>
-    <row r="492" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G492" s="46"/>
-    </row>
-    <row r="493" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G493" s="46"/>
-    </row>
-    <row r="494" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G494" s="46"/>
-    </row>
-    <row r="495" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G495" s="46"/>
-    </row>
-    <row r="496" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G496" s="46"/>
-    </row>
-    <row r="497" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G497" s="46"/>
-    </row>
-    <row r="498" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G498" s="46"/>
-    </row>
-    <row r="499" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G499" s="46"/>
-    </row>
-    <row r="500" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G500" s="46"/>
-    </row>
-    <row r="501" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G501" s="46"/>
-    </row>
-    <row r="502" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G502" s="46"/>
-    </row>
-    <row r="503" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G503" s="46"/>
-    </row>
-    <row r="504" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G504" s="46"/>
-    </row>
-    <row r="505" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G505" s="46"/>
-    </row>
-    <row r="506" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G506" s="46"/>
-    </row>
-    <row r="507" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G507" s="46"/>
-    </row>
-    <row r="508" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G508" s="46"/>
-    </row>
-    <row r="509" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G509" s="46"/>
-    </row>
-    <row r="510" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G510" s="46"/>
-    </row>
-    <row r="511" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G511" s="46"/>
-    </row>
-    <row r="512" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G512" s="46"/>
-    </row>
-    <row r="513" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G513" s="46"/>
-    </row>
-    <row r="514" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G514" s="46"/>
-    </row>
-    <row r="515" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G515" s="46"/>
-    </row>
-    <row r="516" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G516" s="46"/>
-    </row>
-    <row r="517" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G517" s="46"/>
-    </row>
-    <row r="518" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G518" s="46"/>
-    </row>
-    <row r="519" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G519" s="46"/>
-    </row>
-    <row r="520" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G520" s="46"/>
-    </row>
-    <row r="521" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G521" s="46"/>
-    </row>
-    <row r="522" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G522" s="46"/>
-    </row>
-    <row r="523" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G523" s="46"/>
-    </row>
-    <row r="524" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G524" s="46"/>
-    </row>
-    <row r="525" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G525" s="46"/>
-    </row>
-    <row r="526" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G526" s="46"/>
-    </row>
-    <row r="527" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G527" s="46"/>
-    </row>
-    <row r="528" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G528" s="46"/>
-    </row>
-    <row r="529" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G529" s="46"/>
-    </row>
-    <row r="530" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G530" s="46"/>
-    </row>
-    <row r="531" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G531" s="46"/>
-    </row>
-    <row r="532" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G532" s="46"/>
-    </row>
-    <row r="533" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G533" s="46"/>
-    </row>
-    <row r="534" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G534" s="46"/>
-    </row>
-    <row r="535" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G535" s="46"/>
-    </row>
-    <row r="536" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G536" s="46"/>
-    </row>
-    <row r="537" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G537" s="46"/>
-    </row>
-    <row r="538" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G538" s="46"/>
-    </row>
-    <row r="539" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G539" s="46"/>
-    </row>
-    <row r="540" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G540" s="46"/>
-    </row>
-    <row r="541" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G541" s="46"/>
-    </row>
-    <row r="542" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G542" s="46"/>
-    </row>
-    <row r="543" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G543" s="46"/>
-    </row>
-    <row r="544" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G544" s="46"/>
-    </row>
-    <row r="545" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G545" s="46"/>
-    </row>
-    <row r="546" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G546" s="46"/>
-    </row>
-    <row r="547" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G547" s="46"/>
-    </row>
-    <row r="548" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G548" s="46"/>
-    </row>
-    <row r="549" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G549" s="46"/>
-    </row>
-    <row r="550" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G550" s="46"/>
-    </row>
-    <row r="551" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G551" s="46"/>
-    </row>
-    <row r="552" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G552" s="46"/>
-    </row>
-    <row r="553" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G553" s="46"/>
-    </row>
-    <row r="554" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G554" s="46"/>
-    </row>
-    <row r="555" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G555" s="46"/>
-    </row>
-    <row r="556" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G556" s="46"/>
-    </row>
-    <row r="557" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G557" s="46"/>
-    </row>
-    <row r="558" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G558" s="46"/>
-    </row>
-    <row r="559" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G559" s="46"/>
-    </row>
-    <row r="560" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G560" s="46"/>
-    </row>
-    <row r="561" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G561" s="46"/>
-    </row>
-    <row r="562" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G562" s="46"/>
-    </row>
-    <row r="563" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G563" s="46"/>
-    </row>
-    <row r="564" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G564" s="46"/>
-    </row>
-    <row r="565" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G565" s="46"/>
-    </row>
-    <row r="566" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G566" s="46"/>
-    </row>
-    <row r="567" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G567" s="46"/>
-    </row>
-    <row r="568" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G568" s="46"/>
-    </row>
-    <row r="569" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G569" s="46"/>
-    </row>
-    <row r="570" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G570" s="46"/>
-    </row>
-    <row r="571" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G571" s="46"/>
-    </row>
-    <row r="572" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G572" s="46"/>
-    </row>
-    <row r="573" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G573" s="46"/>
-    </row>
-    <row r="574" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G574" s="46"/>
-    </row>
-    <row r="575" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G575" s="46"/>
-    </row>
-    <row r="576" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G576" s="46"/>
-    </row>
-    <row r="577" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G577" s="46"/>
-    </row>
-    <row r="578" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G578" s="46"/>
-    </row>
-    <row r="579" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G579" s="46"/>
-    </row>
-    <row r="580" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G580" s="46"/>
-    </row>
-    <row r="581" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G581" s="46"/>
-    </row>
-    <row r="582" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G582" s="46"/>
-    </row>
-    <row r="583" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G583" s="46"/>
-    </row>
-    <row r="584" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G584" s="46"/>
-    </row>
-    <row r="585" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G585" s="46"/>
-    </row>
-    <row r="586" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G586" s="46"/>
-    </row>
-    <row r="587" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G587" s="46"/>
-    </row>
-    <row r="588" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G588" s="46"/>
-    </row>
-    <row r="589" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G589" s="46"/>
-    </row>
-    <row r="590" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G590" s="46"/>
-    </row>
-    <row r="591" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G591" s="46"/>
-    </row>
-    <row r="592" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G592" s="46"/>
-    </row>
-    <row r="593" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G593" s="46"/>
-    </row>
-    <row r="594" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G594" s="46"/>
-    </row>
-    <row r="595" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G595" s="46"/>
-    </row>
-    <row r="596" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G596" s="46"/>
-    </row>
-    <row r="597" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G597" s="46"/>
-    </row>
-    <row r="598" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G598" s="46"/>
-    </row>
-    <row r="599" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G599" s="46"/>
-    </row>
-    <row r="600" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G600" s="46"/>
-    </row>
-    <row r="601" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G601" s="46"/>
-    </row>
-    <row r="602" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G602" s="46"/>
-    </row>
-    <row r="603" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G603" s="46"/>
-    </row>
-    <row r="604" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G604" s="46"/>
-    </row>
-    <row r="605" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G605" s="46"/>
-    </row>
-    <row r="606" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G606" s="46"/>
-    </row>
-    <row r="607" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G607" s="46"/>
-    </row>
-    <row r="608" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G608" s="46"/>
-    </row>
-    <row r="609" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G609" s="46"/>
-    </row>
-    <row r="610" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G610" s="46"/>
-    </row>
-    <row r="611" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G611" s="46"/>
-    </row>
-    <row r="612" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G612" s="46"/>
-    </row>
-    <row r="613" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G613" s="46"/>
-    </row>
-    <row r="614" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G614" s="46"/>
-    </row>
-    <row r="615" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G615" s="46"/>
-    </row>
-    <row r="616" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G616" s="46"/>
-    </row>
-    <row r="617" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G617" s="46"/>
-    </row>
-    <row r="618" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G618" s="46"/>
-    </row>
-    <row r="619" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G619" s="46"/>
-    </row>
-    <row r="620" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G620" s="46"/>
-    </row>
-    <row r="621" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G621" s="46"/>
-    </row>
-    <row r="622" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G622" s="46"/>
-    </row>
-    <row r="623" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G623" s="46"/>
-    </row>
-    <row r="624" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G624" s="46"/>
-    </row>
-    <row r="625" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G625" s="46"/>
-    </row>
-    <row r="626" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G626" s="46"/>
-    </row>
-    <row r="627" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G627" s="46"/>
-    </row>
-    <row r="628" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G628" s="46"/>
-    </row>
-    <row r="629" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G629" s="46"/>
-    </row>
-    <row r="630" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G630" s="46"/>
-    </row>
-    <row r="631" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G631" s="46"/>
-    </row>
-    <row r="632" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G632" s="46"/>
-    </row>
-    <row r="633" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G633" s="46"/>
-    </row>
-    <row r="634" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G634" s="46"/>
-    </row>
-    <row r="635" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G635" s="46"/>
-    </row>
-    <row r="636" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G636" s="46"/>
-    </row>
-    <row r="637" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G637" s="46"/>
-    </row>
-    <row r="638" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G638" s="46"/>
-    </row>
-    <row r="639" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G639" s="46"/>
-    </row>
-    <row r="640" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G640" s="46"/>
-    </row>
-    <row r="641" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G641" s="46"/>
-    </row>
-    <row r="642" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G642" s="46"/>
-    </row>
-    <row r="643" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G643" s="46"/>
-    </row>
-    <row r="644" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G644" s="46"/>
-    </row>
-    <row r="645" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G645" s="46"/>
-    </row>
-    <row r="646" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G646" s="46"/>
-    </row>
-    <row r="647" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G647" s="46"/>
-    </row>
-    <row r="648" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G648" s="46"/>
-    </row>
-    <row r="649" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G649" s="46"/>
-    </row>
-    <row r="650" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G650" s="46"/>
-    </row>
-    <row r="651" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G651" s="46"/>
-    </row>
-    <row r="652" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G652" s="46"/>
-    </row>
-    <row r="653" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G653" s="46"/>
-    </row>
-    <row r="654" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G654" s="46"/>
-    </row>
-    <row r="655" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G655" s="46"/>
-    </row>
-    <row r="656" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G656" s="46"/>
-    </row>
-    <row r="657" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G657" s="46"/>
-    </row>
-    <row r="658" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G658" s="46"/>
-    </row>
-    <row r="659" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G659" s="46"/>
-    </row>
-    <row r="660" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G660" s="46"/>
-    </row>
-    <row r="661" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G661" s="46"/>
-    </row>
-    <row r="662" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G662" s="46"/>
-    </row>
-    <row r="663" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G663" s="46"/>
-    </row>
-    <row r="664" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G664" s="46"/>
-    </row>
-    <row r="665" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G665" s="46"/>
-    </row>
-    <row r="666" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G666" s="46"/>
-    </row>
-    <row r="667" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G667" s="46"/>
-    </row>
-    <row r="668" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G668" s="46"/>
-    </row>
-    <row r="669" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G669" s="46"/>
-    </row>
-    <row r="670" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G670" s="46"/>
-    </row>
-    <row r="671" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G671" s="46"/>
-    </row>
-    <row r="672" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G672" s="46"/>
-    </row>
-    <row r="673" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G673" s="46"/>
-    </row>
-    <row r="674" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G674" s="46"/>
-    </row>
-    <row r="675" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G675" s="46"/>
-    </row>
-    <row r="676" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G676" s="46"/>
-    </row>
-    <row r="677" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G677" s="46"/>
-    </row>
-    <row r="678" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G678" s="46"/>
-    </row>
-    <row r="679" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G679" s="46"/>
-    </row>
-    <row r="680" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G680" s="46"/>
-    </row>
-    <row r="681" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G681" s="46"/>
-    </row>
-    <row r="682" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G682" s="46"/>
-    </row>
-    <row r="683" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G683" s="46"/>
-    </row>
-    <row r="684" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G684" s="46"/>
-    </row>
-    <row r="685" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G685" s="46"/>
-    </row>
-    <row r="686" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G686" s="46"/>
-    </row>
-    <row r="687" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G687" s="46"/>
-    </row>
-    <row r="688" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G688" s="46"/>
-    </row>
-    <row r="689" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G689" s="46"/>
-    </row>
-    <row r="690" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G690" s="46"/>
-    </row>
-    <row r="691" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G691" s="46"/>
-    </row>
-    <row r="692" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G692" s="46"/>
-    </row>
-    <row r="693" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G693" s="46"/>
-    </row>
-    <row r="694" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G694" s="46"/>
-    </row>
-    <row r="695" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G695" s="46"/>
-    </row>
-    <row r="696" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G696" s="46"/>
-    </row>
-    <row r="697" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G697" s="46"/>
-    </row>
-    <row r="698" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G698" s="46"/>
-    </row>
-    <row r="699" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G699" s="46"/>
-    </row>
-    <row r="700" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G700" s="46"/>
-    </row>
-    <row r="701" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G701" s="46"/>
-    </row>
-    <row r="702" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G702" s="46"/>
-    </row>
-    <row r="703" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G703" s="46"/>
-    </row>
-    <row r="704" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G704" s="46"/>
-    </row>
-    <row r="705" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G705" s="46"/>
-    </row>
-    <row r="706" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G706" s="46"/>
-    </row>
-    <row r="707" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G707" s="46"/>
-    </row>
-    <row r="708" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G708" s="46"/>
-    </row>
-    <row r="709" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G709" s="46"/>
-    </row>
-    <row r="710" spans="7:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G710" s="46"/>
+      <c r="G450" s="32"/>
+      <c r="H450" s="42"/>
+    </row>
+    <row r="451" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H451" s="44"/>
+    </row>
+    <row r="452" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H452" s="44"/>
+    </row>
+    <row r="453" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H453" s="44"/>
+    </row>
+    <row r="454" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H454" s="44"/>
+    </row>
+    <row r="455" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H455" s="44"/>
+    </row>
+    <row r="456" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H456" s="44"/>
+    </row>
+    <row r="457" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H457" s="44"/>
+    </row>
+    <row r="458" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H458" s="44"/>
+    </row>
+    <row r="459" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H459" s="44"/>
+    </row>
+    <row r="460" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H460" s="44"/>
+    </row>
+    <row r="461" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H461" s="44"/>
+    </row>
+    <row r="462" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H462" s="44"/>
+    </row>
+    <row r="463" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H463" s="44"/>
+    </row>
+    <row r="464" spans="2:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H464" s="44"/>
+    </row>
+    <row r="465" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H465" s="44"/>
+    </row>
+    <row r="466" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H466" s="44"/>
+    </row>
+    <row r="467" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H467" s="44"/>
+    </row>
+    <row r="468" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H468" s="44"/>
+    </row>
+    <row r="469" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H469" s="44"/>
+    </row>
+    <row r="470" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H470" s="44"/>
+    </row>
+    <row r="471" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H471" s="44"/>
+    </row>
+    <row r="472" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H472" s="44"/>
+    </row>
+    <row r="473" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H473" s="44"/>
+    </row>
+    <row r="474" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H474" s="44"/>
+    </row>
+    <row r="475" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H475" s="44"/>
+    </row>
+    <row r="476" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H476" s="44"/>
+    </row>
+    <row r="477" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H477" s="44"/>
+    </row>
+    <row r="478" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H478" s="44"/>
+    </row>
+    <row r="479" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H479" s="44"/>
+    </row>
+    <row r="480" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H480" s="44"/>
+    </row>
+    <row r="481" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H481" s="44"/>
+    </row>
+    <row r="482" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H482" s="44"/>
+    </row>
+    <row r="483" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H483" s="44"/>
+    </row>
+    <row r="484" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H484" s="44"/>
+    </row>
+    <row r="485" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H485" s="44"/>
+    </row>
+    <row r="486" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H486" s="44"/>
+    </row>
+    <row r="487" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H487" s="44"/>
+    </row>
+    <row r="488" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H488" s="44"/>
+    </row>
+    <row r="489" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H489" s="44"/>
+    </row>
+    <row r="490" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H490" s="44"/>
+    </row>
+    <row r="491" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H491" s="44"/>
+    </row>
+    <row r="492" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H492" s="44"/>
+    </row>
+    <row r="493" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H493" s="44"/>
+    </row>
+    <row r="494" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H494" s="44"/>
+    </row>
+    <row r="495" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H495" s="44"/>
+    </row>
+    <row r="496" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H496" s="44"/>
+    </row>
+    <row r="497" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H497" s="44"/>
+    </row>
+    <row r="498" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H498" s="44"/>
+    </row>
+    <row r="499" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H499" s="44"/>
+    </row>
+    <row r="500" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H500" s="44"/>
+    </row>
+    <row r="501" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H501" s="44"/>
+    </row>
+    <row r="502" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H502" s="44"/>
+    </row>
+    <row r="503" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H503" s="44"/>
+    </row>
+    <row r="504" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H504" s="44"/>
+    </row>
+    <row r="505" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H505" s="44"/>
+    </row>
+    <row r="506" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H506" s="44"/>
+    </row>
+    <row r="507" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H507" s="44"/>
+    </row>
+    <row r="508" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H508" s="44"/>
+    </row>
+    <row r="509" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H509" s="44"/>
+    </row>
+    <row r="510" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H510" s="44"/>
+    </row>
+    <row r="511" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H511" s="44"/>
+    </row>
+    <row r="512" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H512" s="44"/>
+    </row>
+    <row r="513" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H513" s="44"/>
+    </row>
+    <row r="514" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H514" s="44"/>
+    </row>
+    <row r="515" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H515" s="44"/>
+    </row>
+    <row r="516" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H516" s="44"/>
+    </row>
+    <row r="517" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H517" s="44"/>
+    </row>
+    <row r="518" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H518" s="44"/>
+    </row>
+    <row r="519" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H519" s="44"/>
+    </row>
+    <row r="520" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H520" s="44"/>
+    </row>
+    <row r="521" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H521" s="44"/>
+    </row>
+    <row r="522" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H522" s="44"/>
+    </row>
+    <row r="523" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H523" s="44"/>
+    </row>
+    <row r="524" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H524" s="44"/>
+    </row>
+    <row r="525" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H525" s="44"/>
+    </row>
+    <row r="526" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H526" s="44"/>
+    </row>
+    <row r="527" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H527" s="44"/>
+    </row>
+    <row r="528" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H528" s="44"/>
+    </row>
+    <row r="529" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H529" s="44"/>
+    </row>
+    <row r="530" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H530" s="44"/>
+    </row>
+    <row r="531" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H531" s="44"/>
+    </row>
+    <row r="532" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H532" s="44"/>
+    </row>
+    <row r="533" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H533" s="44"/>
+    </row>
+    <row r="534" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H534" s="44"/>
+    </row>
+    <row r="535" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H535" s="44"/>
+    </row>
+    <row r="536" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H536" s="44"/>
+    </row>
+    <row r="537" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H537" s="44"/>
+    </row>
+    <row r="538" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H538" s="44"/>
+    </row>
+    <row r="539" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H539" s="44"/>
+    </row>
+    <row r="540" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H540" s="44"/>
+    </row>
+    <row r="541" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H541" s="44"/>
+    </row>
+    <row r="542" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H542" s="44"/>
+    </row>
+    <row r="543" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H543" s="44"/>
+    </row>
+    <row r="544" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H544" s="44"/>
+    </row>
+    <row r="545" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H545" s="44"/>
+    </row>
+    <row r="546" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H546" s="44"/>
+    </row>
+    <row r="547" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H547" s="44"/>
+    </row>
+    <row r="548" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H548" s="44"/>
+    </row>
+    <row r="549" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H549" s="44"/>
+    </row>
+    <row r="550" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H550" s="44"/>
+    </row>
+    <row r="551" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H551" s="44"/>
+    </row>
+    <row r="552" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H552" s="44"/>
+    </row>
+    <row r="553" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H553" s="44"/>
+    </row>
+    <row r="554" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H554" s="44"/>
+    </row>
+    <row r="555" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H555" s="44"/>
+    </row>
+    <row r="556" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H556" s="44"/>
+    </row>
+    <row r="557" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H557" s="44"/>
+    </row>
+    <row r="558" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H558" s="44"/>
+    </row>
+    <row r="559" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H559" s="44"/>
+    </row>
+    <row r="560" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H560" s="44"/>
+    </row>
+    <row r="561" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H561" s="44"/>
+    </row>
+    <row r="562" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H562" s="44"/>
+    </row>
+    <row r="563" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H563" s="44"/>
+    </row>
+    <row r="564" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H564" s="44"/>
+    </row>
+    <row r="565" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H565" s="44"/>
+    </row>
+    <row r="566" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H566" s="44"/>
+    </row>
+    <row r="567" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H567" s="44"/>
+    </row>
+    <row r="568" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H568" s="44"/>
+    </row>
+    <row r="569" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H569" s="44"/>
+    </row>
+    <row r="570" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H570" s="44"/>
+    </row>
+    <row r="571" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H571" s="44"/>
+    </row>
+    <row r="572" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H572" s="44"/>
+    </row>
+    <row r="573" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H573" s="44"/>
+    </row>
+    <row r="574" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H574" s="44"/>
+    </row>
+    <row r="575" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H575" s="44"/>
+    </row>
+    <row r="576" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H576" s="44"/>
+    </row>
+    <row r="577" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H577" s="44"/>
+    </row>
+    <row r="578" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H578" s="44"/>
+    </row>
+    <row r="579" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H579" s="44"/>
+    </row>
+    <row r="580" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H580" s="44"/>
+    </row>
+    <row r="581" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H581" s="44"/>
+    </row>
+    <row r="582" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H582" s="44"/>
+    </row>
+    <row r="583" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H583" s="44"/>
+    </row>
+    <row r="584" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H584" s="44"/>
+    </row>
+    <row r="585" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H585" s="44"/>
+    </row>
+    <row r="586" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H586" s="44"/>
+    </row>
+    <row r="587" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H587" s="44"/>
+    </row>
+    <row r="588" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H588" s="44"/>
+    </row>
+    <row r="589" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H589" s="44"/>
+    </row>
+    <row r="590" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H590" s="44"/>
+    </row>
+    <row r="591" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H591" s="44"/>
+    </row>
+    <row r="592" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H592" s="44"/>
+    </row>
+    <row r="593" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H593" s="44"/>
+    </row>
+    <row r="594" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H594" s="44"/>
+    </row>
+    <row r="595" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H595" s="44"/>
+    </row>
+    <row r="596" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H596" s="44"/>
+    </row>
+    <row r="597" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H597" s="44"/>
+    </row>
+    <row r="598" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H598" s="44"/>
+    </row>
+    <row r="599" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H599" s="44"/>
+    </row>
+    <row r="600" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H600" s="44"/>
+    </row>
+    <row r="601" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H601" s="44"/>
+    </row>
+    <row r="602" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H602" s="44"/>
+    </row>
+    <row r="603" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H603" s="44"/>
+    </row>
+    <row r="604" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H604" s="44"/>
+    </row>
+    <row r="605" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H605" s="44"/>
+    </row>
+    <row r="606" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H606" s="44"/>
+    </row>
+    <row r="607" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H607" s="44"/>
+    </row>
+    <row r="608" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H608" s="44"/>
+    </row>
+    <row r="609" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H609" s="44"/>
+    </row>
+    <row r="610" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H610" s="44"/>
+    </row>
+    <row r="611" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H611" s="44"/>
+    </row>
+    <row r="612" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H612" s="44"/>
+    </row>
+    <row r="613" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H613" s="44"/>
+    </row>
+    <row r="614" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H614" s="44"/>
+    </row>
+    <row r="615" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H615" s="44"/>
+    </row>
+    <row r="616" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H616" s="44"/>
+    </row>
+    <row r="617" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H617" s="44"/>
+    </row>
+    <row r="618" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H618" s="44"/>
+    </row>
+    <row r="619" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H619" s="44"/>
+    </row>
+    <row r="620" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H620" s="44"/>
+    </row>
+    <row r="621" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H621" s="44"/>
+    </row>
+    <row r="622" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H622" s="44"/>
+    </row>
+    <row r="623" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H623" s="44"/>
+    </row>
+    <row r="624" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H624" s="44"/>
+    </row>
+    <row r="625" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H625" s="44"/>
+    </row>
+    <row r="626" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H626" s="44"/>
+    </row>
+    <row r="627" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H627" s="44"/>
+    </row>
+    <row r="628" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H628" s="44"/>
+    </row>
+    <row r="629" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H629" s="44"/>
+    </row>
+    <row r="630" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H630" s="44"/>
+    </row>
+    <row r="631" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H631" s="44"/>
+    </row>
+    <row r="632" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H632" s="44"/>
+    </row>
+    <row r="633" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H633" s="44"/>
+    </row>
+    <row r="634" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H634" s="44"/>
+    </row>
+    <row r="635" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H635" s="44"/>
+    </row>
+    <row r="636" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H636" s="44"/>
+    </row>
+    <row r="637" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H637" s="44"/>
+    </row>
+    <row r="638" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H638" s="44"/>
+    </row>
+    <row r="639" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H639" s="44"/>
+    </row>
+    <row r="640" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H640" s="44"/>
+    </row>
+    <row r="641" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H641" s="44"/>
+    </row>
+    <row r="642" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H642" s="44"/>
+    </row>
+    <row r="643" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H643" s="44"/>
+    </row>
+    <row r="644" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H644" s="44"/>
+    </row>
+    <row r="645" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H645" s="44"/>
+    </row>
+    <row r="646" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H646" s="44"/>
+    </row>
+    <row r="647" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H647" s="44"/>
+    </row>
+    <row r="648" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H648" s="44"/>
+    </row>
+    <row r="649" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H649" s="44"/>
+    </row>
+    <row r="650" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H650" s="44"/>
+    </row>
+    <row r="651" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H651" s="44"/>
+    </row>
+    <row r="652" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H652" s="44"/>
+    </row>
+    <row r="653" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H653" s="44"/>
+    </row>
+    <row r="654" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H654" s="44"/>
+    </row>
+    <row r="655" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H655" s="44"/>
+    </row>
+    <row r="656" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H656" s="44"/>
+    </row>
+    <row r="657" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H657" s="44"/>
+    </row>
+    <row r="658" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H658" s="44"/>
+    </row>
+    <row r="659" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H659" s="44"/>
+    </row>
+    <row r="660" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H660" s="44"/>
+    </row>
+    <row r="661" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H661" s="44"/>
+    </row>
+    <row r="662" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H662" s="44"/>
+    </row>
+    <row r="663" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H663" s="44"/>
+    </row>
+    <row r="664" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H664" s="44"/>
+    </row>
+    <row r="665" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H665" s="44"/>
+    </row>
+    <row r="666" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H666" s="44"/>
+    </row>
+    <row r="667" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H667" s="44"/>
+    </row>
+    <row r="668" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H668" s="44"/>
+    </row>
+    <row r="669" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H669" s="44"/>
+    </row>
+    <row r="670" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H670" s="44"/>
+    </row>
+    <row r="671" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H671" s="44"/>
+    </row>
+    <row r="672" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H672" s="44"/>
+    </row>
+    <row r="673" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H673" s="44"/>
+    </row>
+    <row r="674" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H674" s="44"/>
+    </row>
+    <row r="675" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H675" s="44"/>
+    </row>
+    <row r="676" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H676" s="44"/>
+    </row>
+    <row r="677" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H677" s="44"/>
+    </row>
+    <row r="678" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H678" s="44"/>
+    </row>
+    <row r="679" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H679" s="44"/>
+    </row>
+    <row r="680" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H680" s="44"/>
+    </row>
+    <row r="681" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H681" s="44"/>
+    </row>
+    <row r="682" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H682" s="44"/>
+    </row>
+    <row r="683" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H683" s="44"/>
+    </row>
+    <row r="684" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H684" s="44"/>
+    </row>
+    <row r="685" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H685" s="44"/>
+    </row>
+    <row r="686" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H686" s="44"/>
+    </row>
+    <row r="687" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H687" s="44"/>
+    </row>
+    <row r="688" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H688" s="44"/>
+    </row>
+    <row r="689" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H689" s="44"/>
+    </row>
+    <row r="690" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H690" s="44"/>
+    </row>
+    <row r="691" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H691" s="44"/>
+    </row>
+    <row r="692" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H692" s="44"/>
+    </row>
+    <row r="693" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H693" s="44"/>
+    </row>
+    <row r="694" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H694" s="44"/>
+    </row>
+    <row r="695" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H695" s="44"/>
+    </row>
+    <row r="696" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H696" s="44"/>
+    </row>
+    <row r="697" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H697" s="44"/>
+    </row>
+    <row r="698" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H698" s="44"/>
+    </row>
+    <row r="699" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H699" s="44"/>
+    </row>
+    <row r="700" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H700" s="44"/>
+    </row>
+    <row r="701" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H701" s="44"/>
+    </row>
+    <row r="702" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H702" s="44"/>
+    </row>
+    <row r="703" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H703" s="44"/>
+    </row>
+    <row r="704" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H704" s="44"/>
+    </row>
+    <row r="705" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H705" s="44"/>
+    </row>
+    <row r="706" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H706" s="44"/>
+    </row>
+    <row r="707" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H707" s="44"/>
+    </row>
+    <row r="708" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H708" s="44"/>
+    </row>
+    <row r="709" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H709" s="44"/>
+    </row>
+    <row r="710" spans="8:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H710" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:G2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="C2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="17" type="noConversion"/>
-  <conditionalFormatting sqref="C3:E27">
+  <conditionalFormatting sqref="D3:F27">
     <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="Closed">
-      <formula>NOT(ISERROR(SEARCH("Closed",C3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Closed",D3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="31" priority="10" operator="containsText" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",C3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="Open">
-      <formula>NOT(ISERROR(SEARCH("Open",C3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D27">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="Request">
-      <formula>NOT(ISERROR(SEARCH("Request",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="Task">
-      <formula>NOT(ISERROR(SEARCH("Task",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="Feature">
-      <formula>NOT(ISERROR(SEARCH("Feature",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="Bug">
-      <formula>NOT(ISERROR(SEARCH("Bug",D3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Open",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E27">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="Request">
+      <formula>NOT(ISERROR(SEARCH("Request",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="Task">
+      <formula>NOT(ISERROR(SEARCH("Task",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="Feature">
+      <formula>NOT(ISERROR(SEARCH("Feature",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="Bug">
+      <formula>NOT(ISERROR(SEARCH("Bug",E3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F27">
     <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Critical">
-      <formula>NOT(ISERROR(SEARCH("Critical",E3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Critical",F3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("High",F3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Medium",F3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Low",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0" footer="0"/>
@@ -5973,19 +6433,19 @@
           <x14:formula1>
             <xm:f>'Key - Do Not Delete'!$D$4:$D$7</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E27</xm:sqref>
+          <xm:sqref>F3:F27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1F940809-3D47-438D-8CB1-D74B7C055D52}">
           <x14:formula1>
             <xm:f>'Key - Do Not Delete'!$C$4:$C$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D3:D27</xm:sqref>
+          <xm:sqref>E3:E27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F499DE9E-388C-4FE3-96A1-CE14ABE25F5D}">
           <x14:formula1>
             <xm:f>'Key - Do Not Delete'!$B$4:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:E27</xm:sqref>
+          <xm:sqref>D3:F27</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6032,12 +6492,12 @@
       <c r="L1" s="14"/>
     </row>
     <row r="2" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
       <c r="F2" s="21"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -6049,12 +6509,12 @@
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
       <c r="F3" s="21"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -6066,12 +6526,12 @@
       <c r="S3" s="2"/>
     </row>
     <row r="4" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="21"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -6083,12 +6543,12 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="21"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415AF05E-8993-4B2B-AD7C-A910D8800FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2F4C9B-4F65-4CD3-B493-B5129F969D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="39">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -140,13 +140,28 @@
     <t>metric in timeline (total) different from __perf.csv</t>
   </si>
   <si>
-    <t>must match</t>
-  </si>
-  <si>
     <t>Issue No</t>
   </si>
   <si>
     <t>iss01</t>
+  </si>
+  <si>
+    <t>2026.02.24</t>
+  </si>
+  <si>
+    <t>iss02</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>iss03</t>
+  </si>
+  <si>
+    <t>draw text for video visualization (using custom font slow)</t>
+  </si>
+  <si>
+    <t>legend in timeline.html do not having note; add custom text to timeline cfg</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="46" t="s">
         <v>2</v>
@@ -1218,10 +1233,10 @@
         <v>29</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="48" t="s">
         <v>20</v>
@@ -1233,7 +1248,7 @@
         <v>30</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" s="36"/>
       <c r="J3" s="36"/>
@@ -1245,8 +1260,12 @@
     </row>
     <row r="4" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
+      <c r="B4" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>34</v>
+      </c>
       <c r="D4" s="48" t="s">
         <v>17</v>
       </c>
@@ -1256,7 +1275,9 @@
       <c r="F4" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="39"/>
+      <c r="G4" s="39" t="s">
+        <v>38</v>
+      </c>
       <c r="H4" s="41"/>
       <c r="I4" s="36"/>
       <c r="J4" s="36"/>
@@ -1268,8 +1289,12 @@
     </row>
     <row r="5" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
+      <c r="B5" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>36</v>
+      </c>
       <c r="D5" s="48" t="s">
         <v>17</v>
       </c>
@@ -1279,7 +1304,9 @@
       <c r="F5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="39"/>
+      <c r="G5" s="39" t="s">
+        <v>37</v>
+      </c>
       <c r="H5" s="41"/>
       <c r="I5" s="36"/>
       <c r="J5" s="36"/>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2F4C9B-4F65-4CD3-B493-B5129F969D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C76931-4BD1-469B-94AA-050110AB7564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C76931-4BD1-469B-94AA-050110AB7564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21D6062-130C-45FA-A61E-F0AB2C16F36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="40">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>legend in timeline.html do not having note; add custom text to timeline cfg</t>
+  </si>
+  <si>
+    <t>done</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1270,7 @@
         <v>34</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="48" t="s">
         <v>20</v>
@@ -1278,7 +1281,9 @@
       <c r="G4" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="41"/>
+      <c r="H4" s="41" t="s">
+        <v>39</v>
+      </c>
       <c r="I4" s="36"/>
       <c r="J4" s="36"/>
       <c r="K4" s="36"/>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21D6062-130C-45FA-A61E-F0AB2C16F36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF46929-2FD7-44C1-930A-573EC119074A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,13 +158,13 @@
     <t>iss03</t>
   </si>
   <si>
-    <t>draw text for video visualization (using custom font slow)</t>
-  </si>
-  <si>
     <t>legend in timeline.html do not having note; add custom text to timeline cfg</t>
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>slow speed when drawing text for video visualization when using custom</t>
   </si>
 </sst>
 </file>
@@ -1279,10 +1279,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I4" s="36"/>
       <c r="J4" s="36"/>
@@ -1310,7 +1310,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H5" s="41"/>
       <c r="I5" s="36"/>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF46929-2FD7-44C1-930A-573EC119074A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE4B377-3B62-4957-A90D-8E416F8DB426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE4B377-3B62-4957-A90D-8E416F8DB426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292BA7F9-4C0A-40C7-B0D9-CBA3FB144A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="16440" windowHeight="28035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="45">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -165,6 +165,21 @@
   </si>
   <si>
     <t>slow speed when drawing text for video visualization when using custom</t>
+  </si>
+  <si>
+    <t>2026.03.06</t>
+  </si>
+  <si>
+    <t>iss04</t>
+  </si>
+  <si>
+    <t>some labels in videos is INCORRECT (need to re-annotate)</t>
+  </si>
+  <si>
+    <t>iss05</t>
+  </si>
+  <si>
+    <t>current Code can not compared with external exp (results from cls or od models)</t>
   </si>
 </sst>
 </file>
@@ -595,7 +610,161 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="5" xr:uid="{C1547B1A-ACFD-7E4D-8269-7F11392CAD83}"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="55">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFED2B38"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF3EB8EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE54B1B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF3EB8EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -831,6 +1000,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
+      <color rgb="FFED2B38"/>
+      <color rgb="FFFF9966"/>
       <color rgb="FFE54B1B"/>
       <color rgb="FF3EB8EE"/>
       <color rgb="FF00BD32"/>
@@ -1301,7 +1472,7 @@
         <v>36</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="48" t="s">
         <v>20</v>
@@ -1323,8 +1494,12 @@
     </row>
     <row r="6" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>41</v>
+      </c>
       <c r="D6" s="48" t="s">
         <v>17</v>
       </c>
@@ -1332,9 +1507,11 @@
         <v>20</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
-      <c r="G6" s="39"/>
+      <c r="G6" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="H6" s="41"/>
       <c r="I6" s="36"/>
       <c r="J6" s="36"/>
@@ -1346,10 +1523,14 @@
     </row>
     <row r="7" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>43</v>
+      </c>
       <c r="D7" s="48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="48" t="s">
         <v>20</v>
@@ -1357,7 +1538,9 @@
       <c r="F7" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="39"/>
+      <c r="G7" s="39" t="s">
+        <v>44</v>
+      </c>
       <c r="H7" s="41"/>
       <c r="I7" s="36"/>
       <c r="J7" s="36"/>
@@ -6418,41 +6601,41 @@
   <autoFilter ref="C2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="D3:F27">
-    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="10" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E27">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="Request">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="Task">
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Task">
       <formula>NOT(ISERROR(SEARCH("Task",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="Feature">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Feature">
       <formula>NOT(ISERROR(SEARCH("Feature",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="Bug">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Bug">
       <formula>NOT(ISERROR(SEARCH("Bug",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F27">
-    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13470,41 +13653,41 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:C32">
-    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="54" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",C8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="10" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="53" priority="10" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",C8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="52" priority="11" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",C8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E32">
-    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Request">
+    <cfRule type="containsText" dxfId="51" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",E8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Task">
+    <cfRule type="containsText" dxfId="50" priority="6" operator="containsText" text="Task">
       <formula>NOT(ISERROR(SEARCH("Task",E8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="Feature">
+    <cfRule type="containsText" dxfId="49" priority="7" operator="containsText" text="Feature">
       <formula>NOT(ISERROR(SEARCH("Feature",E8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Bug">
+    <cfRule type="containsText" dxfId="48" priority="8" operator="containsText" text="Bug">
       <formula>NOT(ISERROR(SEARCH("Bug",E8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F32">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="46" priority="2" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",F8)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13627,41 +13810,41 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B6">
-    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="43" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",B4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="42" priority="10" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",B4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="41" priority="11" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",B4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C7">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Request">
+    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Task">
+    <cfRule type="containsText" dxfId="39" priority="6" operator="containsText" text="Task">
       <formula>NOT(ISERROR(SEARCH("Task",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Feature">
+    <cfRule type="containsText" dxfId="38" priority="7" operator="containsText" text="Feature">
       <formula>NOT(ISERROR(SEARCH("Feature",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Bug">
+    <cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="Bug">
       <formula>NOT(ISERROR(SEARCH("Bug",C4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D7">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",D4)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292BA7F9-4C0A-40C7-B0D9-CBA3FB144A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C844106-1A86-40B4-8F11-B2D08B58FBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="16440" windowHeight="28035" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="46">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>current Code can not compared with external exp (results from cls or od models)</t>
+  </si>
+  <si>
+    <t>done (ignore using draw by font, but use native opencv2 text draw)</t>
   </si>
 </sst>
 </file>
@@ -610,161 +613,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="5" xr:uid="{C1547B1A-ACFD-7E4D-8269-7F11392CAD83}"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFED2B38"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF3EB8EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE54B1B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF3EB8EE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <fill>
         <patternFill>
@@ -943,7 +792,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE54B1B"/>
+          <bgColor rgb="FFED2B38"/>
         </patternFill>
       </fill>
     </dxf>
@@ -978,21 +827,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFF9966"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1355,7 +1204,7 @@
     <col min="5" max="5" width="11.125" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="43" customWidth="1"/>
     <col min="7" max="7" width="61.25" style="35" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="35" customWidth="1"/>
+    <col min="8" max="8" width="51.625" style="35" customWidth="1"/>
     <col min="9" max="9" width="3.625" style="32" customWidth="1"/>
     <col min="10" max="15" width="11" style="32"/>
     <col min="16" max="16384" width="11" style="35"/>
@@ -1483,7 +1332,9 @@
       <c r="G5" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="41" t="s">
+        <v>45</v>
+      </c>
       <c r="I5" s="36"/>
       <c r="J5" s="36"/>
       <c r="K5" s="36"/>
@@ -1530,7 +1381,7 @@
         <v>43</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="48" t="s">
         <v>20</v>
@@ -1541,7 +1392,9 @@
       <c r="G7" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="41"/>
+      <c r="H7" s="41" t="s">
+        <v>38</v>
+      </c>
       <c r="I7" s="36"/>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -6601,41 +6454,41 @@
   <autoFilter ref="C2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="D3:F27">
-    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="31" priority="10" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E27">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Request">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Task">
+    <cfRule type="containsText" dxfId="28" priority="6" operator="containsText" text="Task">
       <formula>NOT(ISERROR(SEARCH("Task",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Feature">
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="Feature">
       <formula>NOT(ISERROR(SEARCH("Feature",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Bug">
+    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="Bug">
       <formula>NOT(ISERROR(SEARCH("Bug",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F27">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13653,41 +13506,41 @@
     <mergeCell ref="D5:E5"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:C32">
-    <cfRule type="containsText" dxfId="54" priority="9" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",C8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="53" priority="10" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="20" priority="10" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",C8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="11" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",C8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E32">
-    <cfRule type="containsText" dxfId="51" priority="5" operator="containsText" text="Request">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",E8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="6" operator="containsText" text="Task">
+    <cfRule type="containsText" dxfId="17" priority="6" operator="containsText" text="Task">
       <formula>NOT(ISERROR(SEARCH("Task",E8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="7" operator="containsText" text="Feature">
+    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="Feature">
       <formula>NOT(ISERROR(SEARCH("Feature",E8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="8" operator="containsText" text="Bug">
+    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="Bug">
       <formula>NOT(ISERROR(SEARCH("Bug",E8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:F32">
-    <cfRule type="containsText" dxfId="47" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="2" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="45" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",F8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",F8)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13810,41 +13663,41 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B6">
-    <cfRule type="containsText" dxfId="43" priority="9" operator="containsText" text="Closed">
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="Closed">
       <formula>NOT(ISERROR(SEARCH("Closed",B4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="10" operator="containsText" text="In Progress">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",B4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="41" priority="11" operator="containsText" text="Open">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Open">
       <formula>NOT(ISERROR(SEARCH("Open",B4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C7">
-    <cfRule type="containsText" dxfId="40" priority="5" operator="containsText" text="Request">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Request">
       <formula>NOT(ISERROR(SEARCH("Request",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="39" priority="6" operator="containsText" text="Task">
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Task">
       <formula>NOT(ISERROR(SEARCH("Task",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="7" operator="containsText" text="Feature">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Feature">
       <formula>NOT(ISERROR(SEARCH("Feature",C4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="Bug">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Bug">
       <formula>NOT(ISERROR(SEARCH("Bug",C4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D7">
-    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="High">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="High">
       <formula>NOT(ISERROR(SEARCH("High",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="Low">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",D4)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C844106-1A86-40B4-8F11-B2D08B58FBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E82A4C3-9D81-4BA9-8797-3B4EA3710FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="48">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -152,9 +152,6 @@
     <t>iss02</t>
   </si>
   <si>
-    <t>fixed</t>
-  </si>
-  <si>
     <t>iss03</t>
   </si>
   <si>
@@ -183,6 +180,15 @@
   </si>
   <si>
     <t>done (ignore using draw by font, but use native opencv2 text draw)</t>
+  </si>
+  <si>
+    <t>2026.03.09</t>
+  </si>
+  <si>
+    <t>iss06</t>
+  </si>
+  <si>
+    <t>incorrect per-frame and per-video resutls (between test code and exp metric calc code)</t>
   </si>
 </sst>
 </file>
@@ -313,7 +319,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Roboto"/>
     </font>
   </fonts>
@@ -594,15 +599,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="7" fontId="18" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="7" fontId="18" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1270,8 +1275,8 @@
       <c r="G3" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="49" t="s">
-        <v>35</v>
+      <c r="H3" s="51" t="s">
+        <v>37</v>
       </c>
       <c r="I3" s="36"/>
       <c r="J3" s="36"/>
@@ -1299,10 +1304,10 @@
         <v>24</v>
       </c>
       <c r="G4" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="41" t="s">
         <v>37</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>38</v>
       </c>
       <c r="I4" s="36"/>
       <c r="J4" s="36"/>
@@ -1318,7 +1323,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="48" t="s">
         <v>19</v>
@@ -1330,10 +1335,10 @@
         <v>24</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5" s="36"/>
       <c r="J5" s="36"/>
@@ -1346,24 +1351,26 @@
     <row r="6" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36"/>
       <c r="B6" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" s="48" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="41"/>
+        <v>43</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>37</v>
+      </c>
       <c r="I6" s="36"/>
       <c r="J6" s="36"/>
       <c r="K6" s="36"/>
@@ -1372,13 +1379,13 @@
       <c r="N6" s="36"/>
       <c r="O6" s="36"/>
     </row>
-    <row r="7" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="37" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="36"/>
       <c r="B7" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="48" t="s">
         <v>19</v>
@@ -1387,13 +1394,13 @@
         <v>20</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G7" s="39" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I7" s="36"/>
       <c r="J7" s="36"/>
@@ -1403,10 +1410,14 @@
       <c r="N7" s="36"/>
       <c r="O7" s="36"/>
     </row>
-    <row r="8" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="37" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>40</v>
+      </c>
       <c r="D8" s="48" t="s">
         <v>17</v>
       </c>
@@ -1414,9 +1425,11 @@
         <v>20</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="39"/>
+        <v>27</v>
+      </c>
+      <c r="G8" s="39" t="s">
+        <v>41</v>
+      </c>
       <c r="H8" s="41"/>
       <c r="I8" s="36"/>
       <c r="J8" s="36"/>
@@ -1426,7 +1439,7 @@
       <c r="N8" s="36"/>
       <c r="O8" s="36"/>
     </row>
-    <row r="9" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="37" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36"/>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
@@ -6451,7 +6464,11 @@
       <c r="H710" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="C2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="C2:H2" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H27">
+      <sortCondition ref="D2"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="D3:F27">
     <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="Closed">
@@ -6560,12 +6577,12 @@
       <c r="L1" s="14"/>
     </row>
     <row r="2" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
       <c r="F2" s="21"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -6577,12 +6594,12 @@
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
       <c r="F3" s="21"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -6594,12 +6611,12 @@
       <c r="S3" s="2"/>
     </row>
     <row r="4" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
       <c r="F4" s="21"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -6611,12 +6628,12 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
       <c r="F5" s="21"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>

--- a/_issue_track.xlsx
+++ b/_issue_track.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8738E8EC-B6F5-406B-89C7-D726AE9D09DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D73213-30D2-4C4C-90A2-44AA8BCC2249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="825" windowWidth="16440" windowHeight="27495" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Issue Tracking" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="56">
   <si>
     <t xml:space="preserve">Any articles, templates, or information provided by Smartsheet on the website are for reference only. While we strive to keep the information up to date and correct, we make no representations or warranties of any kind, express or implied, about the completeness, accuracy, reliability, suitability, or availability with respect to the website or the information, articles, templates, or related graphics contained on the website. Any reliance you place on such information is therefore strictly at your own risk. </t>
   </si>
@@ -214,6 +214,15 @@
   </si>
   <si>
     <t>update code to chose the BEST hyper params SET</t>
+  </si>
+  <si>
+    <t>2026.03.17</t>
+  </si>
+  <si>
+    <t>iss09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infer for SKIP method using CACHED infer research from NO_SKIP method </t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1498,9 @@
       <c r="G9" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="41"/>
+      <c r="H9" s="41" t="s">
+        <v>37</v>
+      </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36"/>
       <c r="K9" s="36"/>
@@ -1507,7 +1518,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" s="48" t="s">
         <v>22</v>
@@ -1518,7 +1529,9 @@
       <c r="G10" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="41"/>
+      <c r="H10" s="41" t="s">
+        <v>37</v>
+      </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
       <c r="K10" s="36"/>
@@ -1529,8 +1542,12 @@
     </row>
     <row r="11" spans="1:15" s="37" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
+      <c r="B11" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>54</v>
+      </c>
       <c r="D11" s="48" t="s">
         <v>17</v>
       </c>
@@ -1540,7 +1557,9 @@
       <c r="F11" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="39"/>
+      <c r="G11" s="39" t="s">
+        <v>55</v>
+      </c>
       <c r="H11" s="41"/>
       <c r="I11" s="36"/>
       <c r="J11" s="36"/>
